--- a/app/translations.xlsx
+++ b/app/translations.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Translations" r:id="rId3" sheetId="1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">Translations!$A$1:$AG$393</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">Translations!$A$1:$AG$394</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -15380,7 +15380,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A368" authorId="0">
+    <comment ref="A369" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15392,7 +15392,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B368" authorId="0">
+    <comment ref="B369" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15404,7 +15404,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C368" authorId="0">
+    <comment ref="C369" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15416,7 +15416,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D368" authorId="0">
+    <comment ref="D369" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15428,7 +15428,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E368" authorId="0">
+    <comment ref="E369" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15440,7 +15440,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F368" authorId="0">
+    <comment ref="F369" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15452,7 +15452,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G368" authorId="0">
+    <comment ref="G369" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15464,7 +15464,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H368" authorId="0">
+    <comment ref="H369" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15476,7 +15476,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I368" authorId="0">
+    <comment ref="I369" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15488,7 +15488,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J368" authorId="0">
+    <comment ref="J369" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15500,7 +15500,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K368" authorId="0">
+    <comment ref="K369" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15512,7 +15512,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L368" authorId="0">
+    <comment ref="L369" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15524,7 +15524,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M368" authorId="0">
+    <comment ref="M369" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15536,7 +15536,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N368" authorId="0">
+    <comment ref="N369" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15548,7 +15548,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O368" authorId="0">
+    <comment ref="O369" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15560,7 +15560,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P368" authorId="0">
+    <comment ref="P369" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15572,7 +15572,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q368" authorId="0">
+    <comment ref="Q369" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15584,7 +15584,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R368" authorId="0">
+    <comment ref="R369" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15596,7 +15596,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S368" authorId="0">
+    <comment ref="S369" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15608,7 +15608,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T368" authorId="0">
+    <comment ref="T369" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15620,7 +15620,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U368" authorId="0">
+    <comment ref="U369" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15632,7 +15632,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V368" authorId="0">
+    <comment ref="V369" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15644,7 +15644,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W368" authorId="0">
+    <comment ref="W369" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15656,7 +15656,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X368" authorId="0">
+    <comment ref="X369" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15668,7 +15668,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y368" authorId="0">
+    <comment ref="Y369" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15680,7 +15680,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z368" authorId="0">
+    <comment ref="Z369" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15692,7 +15692,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA368" authorId="0">
+    <comment ref="AA369" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15704,7 +15704,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB368" authorId="0">
+    <comment ref="AB369" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15716,7 +15716,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC368" authorId="0">
+    <comment ref="AC369" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15728,7 +15728,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD368" authorId="0">
+    <comment ref="AD369" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15740,7 +15740,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE368" authorId="0">
+    <comment ref="AE369" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15752,7 +15752,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF368" authorId="0">
+    <comment ref="AF369" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15764,7 +15764,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A369" authorId="0">
+    <comment ref="A370" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15776,7 +15776,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B369" authorId="0">
+    <comment ref="B370" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15788,7 +15788,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C369" authorId="0">
+    <comment ref="C370" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15800,7 +15800,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D369" authorId="0">
+    <comment ref="D370" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15812,7 +15812,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E369" authorId="0">
+    <comment ref="E370" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15824,7 +15824,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F369" authorId="0">
+    <comment ref="F370" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15836,7 +15836,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G369" authorId="0">
+    <comment ref="G370" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15848,7 +15848,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H369" authorId="0">
+    <comment ref="H370" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15860,7 +15860,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I369" authorId="0">
+    <comment ref="I370" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15872,7 +15872,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J369" authorId="0">
+    <comment ref="J370" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15884,7 +15884,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K369" authorId="0">
+    <comment ref="K370" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15896,7 +15896,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L369" authorId="0">
+    <comment ref="L370" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15908,7 +15908,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M369" authorId="0">
+    <comment ref="M370" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15920,7 +15920,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N369" authorId="0">
+    <comment ref="N370" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15932,7 +15932,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O369" authorId="0">
+    <comment ref="O370" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15944,7 +15944,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P369" authorId="0">
+    <comment ref="P370" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15956,7 +15956,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q369" authorId="0">
+    <comment ref="Q370" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15968,7 +15968,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R369" authorId="0">
+    <comment ref="R370" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15980,7 +15980,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S369" authorId="0">
+    <comment ref="S370" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15992,7 +15992,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T369" authorId="0">
+    <comment ref="T370" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16004,7 +16004,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U369" authorId="0">
+    <comment ref="U370" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16016,7 +16016,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V369" authorId="0">
+    <comment ref="V370" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16028,7 +16028,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W369" authorId="0">
+    <comment ref="W370" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16040,7 +16040,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X369" authorId="0">
+    <comment ref="X370" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16052,7 +16052,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y369" authorId="0">
+    <comment ref="Y370" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16064,7 +16064,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z369" authorId="0">
+    <comment ref="Z370" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16076,7 +16076,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA369" authorId="0">
+    <comment ref="AA370" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16088,7 +16088,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB369" authorId="0">
+    <comment ref="AB370" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16100,7 +16100,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC369" authorId="0">
+    <comment ref="AC370" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16112,7 +16112,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD369" authorId="0">
+    <comment ref="AD370" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16124,7 +16124,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE369" authorId="0">
+    <comment ref="AE370" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16136,7 +16136,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF369" authorId="0">
+    <comment ref="AF370" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16148,7 +16148,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A372" authorId="0">
+    <comment ref="A373" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16160,7 +16160,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B372" authorId="0">
+    <comment ref="B373" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16172,7 +16172,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C372" authorId="0">
+    <comment ref="C373" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16184,7 +16184,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D372" authorId="0">
+    <comment ref="D373" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16196,7 +16196,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E372" authorId="0">
+    <comment ref="E373" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16208,7 +16208,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F372" authorId="0">
+    <comment ref="F373" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16220,7 +16220,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G372" authorId="0">
+    <comment ref="G373" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16232,7 +16232,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H372" authorId="0">
+    <comment ref="H373" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16244,7 +16244,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I372" authorId="0">
+    <comment ref="I373" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16256,7 +16256,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J372" authorId="0">
+    <comment ref="J373" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16268,7 +16268,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K372" authorId="0">
+    <comment ref="K373" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16280,7 +16280,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L372" authorId="0">
+    <comment ref="L373" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16292,7 +16292,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M372" authorId="0">
+    <comment ref="M373" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16304,7 +16304,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N372" authorId="0">
+    <comment ref="N373" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16316,7 +16316,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O372" authorId="0">
+    <comment ref="O373" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16328,7 +16328,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P372" authorId="0">
+    <comment ref="P373" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16340,7 +16340,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q372" authorId="0">
+    <comment ref="Q373" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16352,7 +16352,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R372" authorId="0">
+    <comment ref="R373" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16364,7 +16364,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S372" authorId="0">
+    <comment ref="S373" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16376,7 +16376,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T372" authorId="0">
+    <comment ref="T373" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16388,7 +16388,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U372" authorId="0">
+    <comment ref="U373" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16400,7 +16400,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V372" authorId="0">
+    <comment ref="V373" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16412,7 +16412,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W372" authorId="0">
+    <comment ref="W373" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16424,7 +16424,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X372" authorId="0">
+    <comment ref="X373" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16436,7 +16436,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y372" authorId="0">
+    <comment ref="Y373" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16448,7 +16448,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z372" authorId="0">
+    <comment ref="Z373" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16460,7 +16460,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA372" authorId="0">
+    <comment ref="AA373" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16472,7 +16472,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB372" authorId="0">
+    <comment ref="AB373" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16484,7 +16484,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC372" authorId="0">
+    <comment ref="AC373" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16496,7 +16496,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD372" authorId="0">
+    <comment ref="AD373" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16508,7 +16508,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE372" authorId="0">
+    <comment ref="AE373" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16520,7 +16520,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF372" authorId="0">
+    <comment ref="AF373" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16532,7 +16532,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A373" authorId="0">
+    <comment ref="A374" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16544,7 +16544,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B373" authorId="0">
+    <comment ref="B374" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16556,7 +16556,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C373" authorId="0">
+    <comment ref="C374" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16568,7 +16568,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D373" authorId="0">
+    <comment ref="D374" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16580,7 +16580,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E373" authorId="0">
+    <comment ref="E374" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16592,7 +16592,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F373" authorId="0">
+    <comment ref="F374" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16604,7 +16604,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G373" authorId="0">
+    <comment ref="G374" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16616,7 +16616,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H373" authorId="0">
+    <comment ref="H374" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16628,7 +16628,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I373" authorId="0">
+    <comment ref="I374" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16640,7 +16640,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J373" authorId="0">
+    <comment ref="J374" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16652,7 +16652,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K373" authorId="0">
+    <comment ref="K374" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16664,7 +16664,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L373" authorId="0">
+    <comment ref="L374" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16676,7 +16676,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M373" authorId="0">
+    <comment ref="M374" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16688,7 +16688,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N373" authorId="0">
+    <comment ref="N374" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16700,7 +16700,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O373" authorId="0">
+    <comment ref="O374" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16712,7 +16712,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P373" authorId="0">
+    <comment ref="P374" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16724,7 +16724,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q373" authorId="0">
+    <comment ref="Q374" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16736,7 +16736,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R373" authorId="0">
+    <comment ref="R374" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16748,7 +16748,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S373" authorId="0">
+    <comment ref="S374" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16760,7 +16760,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T373" authorId="0">
+    <comment ref="T374" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16772,7 +16772,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U373" authorId="0">
+    <comment ref="U374" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16784,7 +16784,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V373" authorId="0">
+    <comment ref="V374" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16796,7 +16796,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W373" authorId="0">
+    <comment ref="W374" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16808,7 +16808,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X373" authorId="0">
+    <comment ref="X374" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16820,7 +16820,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y373" authorId="0">
+    <comment ref="Y374" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16832,7 +16832,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z373" authorId="0">
+    <comment ref="Z374" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16844,7 +16844,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA373" authorId="0">
+    <comment ref="AA374" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16856,7 +16856,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB373" authorId="0">
+    <comment ref="AB374" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16868,7 +16868,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC373" authorId="0">
+    <comment ref="AC374" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16880,7 +16880,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD373" authorId="0">
+    <comment ref="AD374" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16892,7 +16892,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE373" authorId="0">
+    <comment ref="AE374" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16904,7 +16904,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF373" authorId="0">
+    <comment ref="AF374" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16943,7 +16943,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12576" uniqueCount="5743">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12608" uniqueCount="5745">
   <si>
     <t>Key</t>
   </si>
@@ -32611,6 +32611,12 @@
   </si>
   <si>
     <t>Noir</t>
+  </si>
+  <si>
+    <t>swap_action</t>
+  </si>
+  <si>
+    <t>Swap Action</t>
   </si>
   <si>
     <t>take_note</t>
@@ -40129,7 +40135,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AF393"/>
+  <dimension ref="A1:AF394"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="50"/>
   <cols>
     <col min="1" max="1" width="40.0" customWidth="true"/>
@@ -75132,1077 +75138,1077 @@
       <c r="C358" t="s" s="1">
         <v>5167</v>
       </c>
-      <c r="D358" t="s" s="1">
-        <v>5168</v>
-      </c>
-      <c r="E358" t="s" s="1">
-        <v>5169</v>
-      </c>
-      <c r="F358" t="s" s="1">
-        <v>5170</v>
-      </c>
-      <c r="G358" t="s" s="1">
-        <v>5171</v>
-      </c>
-      <c r="H358" t="s" s="1">
-        <v>5172</v>
-      </c>
-      <c r="I358" t="s" s="1">
-        <v>5173</v>
-      </c>
-      <c r="J358" t="s" s="1">
-        <v>5174</v>
-      </c>
-      <c r="K358" t="s" s="1">
-        <v>5175</v>
-      </c>
-      <c r="L358" t="s" s="1">
-        <v>5176</v>
-      </c>
-      <c r="M358" t="s" s="1">
-        <v>5177</v>
-      </c>
-      <c r="N358" t="s" s="1">
-        <v>3971</v>
-      </c>
-      <c r="O358" t="s" s="1">
-        <v>3972</v>
-      </c>
-      <c r="P358" t="s" s="1">
-        <v>5178</v>
-      </c>
-      <c r="Q358" t="s" s="1">
-        <v>5179</v>
-      </c>
-      <c r="R358" t="s" s="1">
-        <v>5180</v>
-      </c>
-      <c r="S358" t="s" s="1">
-        <v>5181</v>
-      </c>
-      <c r="T358" t="s" s="1">
-        <v>5182</v>
-      </c>
-      <c r="U358" t="s" s="1">
-        <v>5183</v>
-      </c>
-      <c r="V358" t="s" s="1">
-        <v>5184</v>
-      </c>
-      <c r="W358" t="s" s="1">
-        <v>5185</v>
-      </c>
-      <c r="X358" t="s" s="1">
-        <v>5186</v>
-      </c>
-      <c r="Y358" t="s" s="1">
-        <v>5187</v>
-      </c>
-      <c r="Z358" t="s" s="1">
-        <v>5188</v>
-      </c>
-      <c r="AA358" t="s" s="1">
-        <v>5189</v>
-      </c>
-      <c r="AB358" t="s" s="1">
-        <v>5190</v>
-      </c>
-      <c r="AC358" t="s" s="1">
-        <v>5191</v>
-      </c>
-      <c r="AD358" t="s" s="1">
-        <v>3983</v>
-      </c>
-      <c r="AE358" t="s" s="1">
-        <v>5192</v>
-      </c>
-      <c r="AF358" t="s" s="1">
-        <v>3985</v>
+      <c r="D358" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E358" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="F358" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="G358" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="H358" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="I358" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="J358" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="K358" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="L358" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M358" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="N358" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="O358" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="P358" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Q358" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="R358" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="S358" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="T358" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="U358" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="V358" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="W358" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="X358" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Y358" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Z358" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AA358" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AB358" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AC358" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AD358" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AE358" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AF358" t="s" s="2">
+        <v>63</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="s" s="1">
-        <v>5193</v>
+        <v>5168</v>
       </c>
       <c r="B359" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C359" t="s" s="1">
+        <v>5169</v>
+      </c>
+      <c r="D359" t="s" s="1">
+        <v>5170</v>
+      </c>
+      <c r="E359" t="s" s="1">
+        <v>5171</v>
+      </c>
+      <c r="F359" t="s" s="1">
+        <v>5172</v>
+      </c>
+      <c r="G359" t="s" s="1">
+        <v>5173</v>
+      </c>
+      <c r="H359" t="s" s="1">
+        <v>5174</v>
+      </c>
+      <c r="I359" t="s" s="1">
+        <v>5175</v>
+      </c>
+      <c r="J359" t="s" s="1">
+        <v>5176</v>
+      </c>
+      <c r="K359" t="s" s="1">
+        <v>5177</v>
+      </c>
+      <c r="L359" t="s" s="1">
+        <v>5178</v>
+      </c>
+      <c r="M359" t="s" s="1">
+        <v>5179</v>
+      </c>
+      <c r="N359" t="s" s="1">
+        <v>3971</v>
+      </c>
+      <c r="O359" t="s" s="1">
+        <v>3972</v>
+      </c>
+      <c r="P359" t="s" s="1">
+        <v>5180</v>
+      </c>
+      <c r="Q359" t="s" s="1">
+        <v>5181</v>
+      </c>
+      <c r="R359" t="s" s="1">
+        <v>5182</v>
+      </c>
+      <c r="S359" t="s" s="1">
+        <v>5183</v>
+      </c>
+      <c r="T359" t="s" s="1">
+        <v>5184</v>
+      </c>
+      <c r="U359" t="s" s="1">
+        <v>5185</v>
+      </c>
+      <c r="V359" t="s" s="1">
+        <v>5186</v>
+      </c>
+      <c r="W359" t="s" s="1">
+        <v>5187</v>
+      </c>
+      <c r="X359" t="s" s="1">
+        <v>5188</v>
+      </c>
+      <c r="Y359" t="s" s="1">
+        <v>5189</v>
+      </c>
+      <c r="Z359" t="s" s="1">
+        <v>5190</v>
+      </c>
+      <c r="AA359" t="s" s="1">
+        <v>5191</v>
+      </c>
+      <c r="AB359" t="s" s="1">
+        <v>5192</v>
+      </c>
+      <c r="AC359" t="s" s="1">
+        <v>5193</v>
+      </c>
+      <c r="AD359" t="s" s="1">
+        <v>3983</v>
+      </c>
+      <c r="AE359" t="s" s="1">
         <v>5194</v>
       </c>
-      <c r="D359" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="E359" t="s" s="1">
-        <v>5195</v>
-      </c>
-      <c r="F359" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="G359" t="s" s="1">
-        <v>5196</v>
-      </c>
-      <c r="H359" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="I359" t="s" s="1">
-        <v>5197</v>
-      </c>
-      <c r="J359" t="s" s="1">
-        <v>5198</v>
-      </c>
-      <c r="K359" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="L359" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="M359" t="s" s="1">
-        <v>5199</v>
-      </c>
-      <c r="N359" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O359" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="P359" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Q359" t="s" s="1">
-        <v>5200</v>
-      </c>
-      <c r="R359" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="S359" t="s" s="1">
-        <v>5201</v>
-      </c>
-      <c r="T359" t="s" s="1">
-        <v>5202</v>
-      </c>
-      <c r="U359" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="V359" t="s" s="1">
-        <v>5203</v>
-      </c>
-      <c r="W359" t="s" s="1">
-        <v>5204</v>
-      </c>
-      <c r="X359" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Y359" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Z359" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AA359" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AB359" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AC359" t="s" s="1">
-        <v>5205</v>
-      </c>
-      <c r="AD359" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AE359" t="s" s="1">
-        <v>5206</v>
-      </c>
       <c r="AF359" t="s" s="1">
-        <v>5207</v>
+        <v>3985</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="s" s="1">
-        <v>5208</v>
+        <v>5195</v>
       </c>
       <c r="B360" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C360" t="s" s="1">
+        <v>5196</v>
+      </c>
+      <c r="D360" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E360" t="s" s="1">
+        <v>5197</v>
+      </c>
+      <c r="F360" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="G360" t="s" s="1">
+        <v>5198</v>
+      </c>
+      <c r="H360" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="I360" t="s" s="1">
+        <v>5199</v>
+      </c>
+      <c r="J360" t="s" s="1">
+        <v>5200</v>
+      </c>
+      <c r="K360" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="L360" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M360" t="s" s="1">
+        <v>5201</v>
+      </c>
+      <c r="N360" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="O360" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="P360" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Q360" t="s" s="1">
+        <v>5202</v>
+      </c>
+      <c r="R360" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="S360" t="s" s="1">
+        <v>5203</v>
+      </c>
+      <c r="T360" t="s" s="1">
+        <v>5204</v>
+      </c>
+      <c r="U360" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="V360" t="s" s="1">
+        <v>5205</v>
+      </c>
+      <c r="W360" t="s" s="1">
+        <v>5206</v>
+      </c>
+      <c r="X360" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Y360" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Z360" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AA360" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AB360" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AC360" t="s" s="1">
+        <v>5207</v>
+      </c>
+      <c r="AD360" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AE360" t="s" s="1">
+        <v>5208</v>
+      </c>
+      <c r="AF360" t="s" s="1">
         <v>5209</v>
-      </c>
-      <c r="D360" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="E360" t="s" s="1">
-        <v>5210</v>
-      </c>
-      <c r="F360" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="G360" t="s" s="1">
-        <v>5211</v>
-      </c>
-      <c r="H360" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="I360" t="s" s="1">
-        <v>5212</v>
-      </c>
-      <c r="J360" t="s" s="1">
-        <v>5213</v>
-      </c>
-      <c r="K360" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="L360" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="M360" t="s" s="1">
-        <v>5214</v>
-      </c>
-      <c r="N360" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O360" t="s" s="1">
-        <v>5215</v>
-      </c>
-      <c r="P360" t="s" s="1">
-        <v>5216</v>
-      </c>
-      <c r="Q360" t="s" s="1">
-        <v>5217</v>
-      </c>
-      <c r="R360" t="s" s="1">
-        <v>5218</v>
-      </c>
-      <c r="S360" t="s" s="1">
-        <v>5219</v>
-      </c>
-      <c r="T360" t="s" s="1">
-        <v>5212</v>
-      </c>
-      <c r="U360" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="V360" t="s" s="1">
-        <v>5220</v>
-      </c>
-      <c r="W360" t="s" s="1">
-        <v>5221</v>
-      </c>
-      <c r="X360" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Y360" t="s" s="1">
-        <v>5222</v>
-      </c>
-      <c r="Z360" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AA360" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AB360" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AC360" t="s" s="1">
-        <v>5223</v>
-      </c>
-      <c r="AD360" t="s" s="1">
-        <v>5224</v>
-      </c>
-      <c r="AE360" t="s" s="1">
-        <v>5225</v>
-      </c>
-      <c r="AF360" t="s" s="1">
-        <v>5226</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="s" s="1">
-        <v>5227</v>
+        <v>5210</v>
       </c>
       <c r="B361" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C361" t="s" s="1">
+        <v>5211</v>
+      </c>
+      <c r="D361" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E361" t="s" s="1">
+        <v>5212</v>
+      </c>
+      <c r="F361" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="G361" t="s" s="1">
+        <v>5213</v>
+      </c>
+      <c r="H361" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="I361" t="s" s="1">
+        <v>5214</v>
+      </c>
+      <c r="J361" t="s" s="1">
+        <v>5215</v>
+      </c>
+      <c r="K361" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="L361" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M361" t="s" s="1">
+        <v>5216</v>
+      </c>
+      <c r="N361" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="O361" t="s" s="1">
+        <v>5217</v>
+      </c>
+      <c r="P361" t="s" s="1">
+        <v>5218</v>
+      </c>
+      <c r="Q361" t="s" s="1">
+        <v>5219</v>
+      </c>
+      <c r="R361" t="s" s="1">
+        <v>5220</v>
+      </c>
+      <c r="S361" t="s" s="1">
+        <v>5221</v>
+      </c>
+      <c r="T361" t="s" s="1">
+        <v>5214</v>
+      </c>
+      <c r="U361" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="V361" t="s" s="1">
+        <v>5222</v>
+      </c>
+      <c r="W361" t="s" s="1">
+        <v>5223</v>
+      </c>
+      <c r="X361" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Y361" t="s" s="1">
+        <v>5224</v>
+      </c>
+      <c r="Z361" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AA361" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AB361" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AC361" t="s" s="1">
+        <v>5225</v>
+      </c>
+      <c r="AD361" t="s" s="1">
+        <v>5226</v>
+      </c>
+      <c r="AE361" t="s" s="1">
+        <v>5227</v>
+      </c>
+      <c r="AF361" t="s" s="1">
         <v>5228</v>
-      </c>
-      <c r="D361" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="E361" t="s" s="1">
-        <v>5229</v>
-      </c>
-      <c r="F361" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="G361" t="s" s="1">
-        <v>5230</v>
-      </c>
-      <c r="H361" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="I361" t="s" s="1">
-        <v>5231</v>
-      </c>
-      <c r="J361" t="s" s="1">
-        <v>5232</v>
-      </c>
-      <c r="K361" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="L361" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="M361" t="s" s="1">
-        <v>5233</v>
-      </c>
-      <c r="N361" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O361" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="P361" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Q361" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="R361" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="S361" t="s" s="1">
-        <v>5234</v>
-      </c>
-      <c r="T361" t="s" s="1">
-        <v>5235</v>
-      </c>
-      <c r="U361" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="V361" t="s" s="1">
-        <v>5236</v>
-      </c>
-      <c r="W361" t="s" s="1">
-        <v>5237</v>
-      </c>
-      <c r="X361" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Y361" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Z361" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AA361" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AB361" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AC361" t="s" s="1">
-        <v>5238</v>
-      </c>
-      <c r="AD361" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AE361" t="s" s="1">
-        <v>5239</v>
-      </c>
-      <c r="AF361" t="s" s="1">
-        <v>5240</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="s" s="1">
-        <v>5241</v>
+        <v>5229</v>
       </c>
       <c r="B362" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C362" t="s" s="1">
+        <v>5230</v>
+      </c>
+      <c r="D362" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E362" t="s" s="1">
+        <v>5231</v>
+      </c>
+      <c r="F362" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="G362" t="s" s="1">
+        <v>5232</v>
+      </c>
+      <c r="H362" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="I362" t="s" s="1">
+        <v>5233</v>
+      </c>
+      <c r="J362" t="s" s="1">
+        <v>5234</v>
+      </c>
+      <c r="K362" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="L362" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M362" t="s" s="1">
+        <v>5235</v>
+      </c>
+      <c r="N362" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="O362" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="P362" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Q362" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="R362" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="S362" t="s" s="1">
+        <v>5236</v>
+      </c>
+      <c r="T362" t="s" s="1">
+        <v>5237</v>
+      </c>
+      <c r="U362" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="V362" t="s" s="1">
+        <v>5238</v>
+      </c>
+      <c r="W362" t="s" s="1">
+        <v>5239</v>
+      </c>
+      <c r="X362" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Y362" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Z362" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AA362" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AB362" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AC362" t="s" s="1">
+        <v>5240</v>
+      </c>
+      <c r="AD362" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AE362" t="s" s="1">
+        <v>5241</v>
+      </c>
+      <c r="AF362" t="s" s="1">
         <v>5242</v>
-      </c>
-      <c r="D362" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="E362" t="s" s="1">
-        <v>5243</v>
-      </c>
-      <c r="F362" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="G362" t="s" s="1">
-        <v>5244</v>
-      </c>
-      <c r="H362" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="I362" t="s" s="1">
-        <v>5245</v>
-      </c>
-      <c r="J362" t="s" s="1">
-        <v>5246</v>
-      </c>
-      <c r="K362" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="L362" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="M362" t="s" s="1">
-        <v>5247</v>
-      </c>
-      <c r="N362" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O362" t="s" s="1">
-        <v>5248</v>
-      </c>
-      <c r="P362" t="s" s="1">
-        <v>5249</v>
-      </c>
-      <c r="Q362" t="s" s="1">
-        <v>5250</v>
-      </c>
-      <c r="R362" t="s" s="1">
-        <v>5251</v>
-      </c>
-      <c r="S362" t="s" s="1">
-        <v>5252</v>
-      </c>
-      <c r="T362" t="s" s="1">
-        <v>5253</v>
-      </c>
-      <c r="U362" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="V362" t="s" s="1">
-        <v>5254</v>
-      </c>
-      <c r="W362" t="s" s="1">
-        <v>5255</v>
-      </c>
-      <c r="X362" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Y362" t="s" s="1">
-        <v>5256</v>
-      </c>
-      <c r="Z362" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AA362" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AB362" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AC362" t="s" s="1">
-        <v>5257</v>
-      </c>
-      <c r="AD362" t="s" s="1">
-        <v>5258</v>
-      </c>
-      <c r="AE362" t="s" s="1">
-        <v>5259</v>
-      </c>
-      <c r="AF362" t="s" s="1">
-        <v>5260</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="s" s="1">
-        <v>5261</v>
+        <v>5243</v>
       </c>
       <c r="B363" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C363" t="s" s="1">
+        <v>5244</v>
+      </c>
+      <c r="D363" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E363" t="s" s="1">
+        <v>5245</v>
+      </c>
+      <c r="F363" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="G363" t="s" s="1">
+        <v>5246</v>
+      </c>
+      <c r="H363" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="I363" t="s" s="1">
+        <v>5247</v>
+      </c>
+      <c r="J363" t="s" s="1">
+        <v>5248</v>
+      </c>
+      <c r="K363" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="L363" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M363" t="s" s="1">
+        <v>5249</v>
+      </c>
+      <c r="N363" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="O363" t="s" s="1">
+        <v>5250</v>
+      </c>
+      <c r="P363" t="s" s="1">
+        <v>5251</v>
+      </c>
+      <c r="Q363" t="s" s="1">
+        <v>5252</v>
+      </c>
+      <c r="R363" t="s" s="1">
+        <v>5253</v>
+      </c>
+      <c r="S363" t="s" s="1">
+        <v>5254</v>
+      </c>
+      <c r="T363" t="s" s="1">
+        <v>5255</v>
+      </c>
+      <c r="U363" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="V363" t="s" s="1">
+        <v>5256</v>
+      </c>
+      <c r="W363" t="s" s="1">
+        <v>5257</v>
+      </c>
+      <c r="X363" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Y363" t="s" s="1">
+        <v>5258</v>
+      </c>
+      <c r="Z363" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AA363" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AB363" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AC363" t="s" s="1">
+        <v>5259</v>
+      </c>
+      <c r="AD363" t="s" s="1">
+        <v>5260</v>
+      </c>
+      <c r="AE363" t="s" s="1">
+        <v>5261</v>
+      </c>
+      <c r="AF363" t="s" s="1">
         <v>5262</v>
-      </c>
-      <c r="D363" t="s" s="1">
-        <v>5263</v>
-      </c>
-      <c r="E363" t="s" s="1">
-        <v>5264</v>
-      </c>
-      <c r="F363" t="s" s="1">
-        <v>5263</v>
-      </c>
-      <c r="G363" t="s" s="1">
-        <v>5265</v>
-      </c>
-      <c r="H363" t="s" s="1">
-        <v>5266</v>
-      </c>
-      <c r="I363" t="s" s="1">
-        <v>5263</v>
-      </c>
-      <c r="J363" t="s" s="1">
-        <v>5267</v>
-      </c>
-      <c r="K363" t="s" s="1">
-        <v>5264</v>
-      </c>
-      <c r="L363" t="s" s="1">
-        <v>5263</v>
-      </c>
-      <c r="M363" t="s" s="1">
-        <v>5263</v>
-      </c>
-      <c r="N363" t="s" s="1">
-        <v>5268</v>
-      </c>
-      <c r="O363" t="s" s="1">
-        <v>5269</v>
-      </c>
-      <c r="P363" t="s" s="1">
-        <v>5263</v>
-      </c>
-      <c r="Q363" t="s" s="1">
-        <v>5270</v>
-      </c>
-      <c r="R363" t="s" s="1">
-        <v>5263</v>
-      </c>
-      <c r="S363" t="s" s="1">
-        <v>5271</v>
-      </c>
-      <c r="T363" t="s" s="1">
-        <v>5263</v>
-      </c>
-      <c r="U363" t="s" s="1">
-        <v>5263</v>
-      </c>
-      <c r="V363" t="s" s="1">
-        <v>5263</v>
-      </c>
-      <c r="W363" t="s" s="1">
-        <v>5272</v>
-      </c>
-      <c r="X363" t="s" s="1">
-        <v>5264</v>
-      </c>
-      <c r="Y363" t="s" s="1">
-        <v>5263</v>
-      </c>
-      <c r="Z363" t="s" s="1">
-        <v>5263</v>
-      </c>
-      <c r="AA363" t="s" s="1">
-        <v>5263</v>
-      </c>
-      <c r="AB363" t="s" s="1">
-        <v>5263</v>
-      </c>
-      <c r="AC363" t="s" s="1">
-        <v>5272</v>
-      </c>
-      <c r="AD363" t="s" s="1">
-        <v>5273</v>
-      </c>
-      <c r="AE363" t="s" s="1">
-        <v>5274</v>
-      </c>
-      <c r="AF363" t="s" s="1">
-        <v>5275</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="s" s="1">
-        <v>5276</v>
+        <v>5263</v>
       </c>
       <c r="B364" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C364" t="s" s="1">
+        <v>5264</v>
+      </c>
+      <c r="D364" t="s" s="1">
+        <v>5265</v>
+      </c>
+      <c r="E364" t="s" s="1">
+        <v>5266</v>
+      </c>
+      <c r="F364" t="s" s="1">
+        <v>5265</v>
+      </c>
+      <c r="G364" t="s" s="1">
+        <v>5267</v>
+      </c>
+      <c r="H364" t="s" s="1">
+        <v>5268</v>
+      </c>
+      <c r="I364" t="s" s="1">
+        <v>5265</v>
+      </c>
+      <c r="J364" t="s" s="1">
+        <v>5269</v>
+      </c>
+      <c r="K364" t="s" s="1">
+        <v>5266</v>
+      </c>
+      <c r="L364" t="s" s="1">
+        <v>5265</v>
+      </c>
+      <c r="M364" t="s" s="1">
+        <v>5265</v>
+      </c>
+      <c r="N364" t="s" s="1">
+        <v>5270</v>
+      </c>
+      <c r="O364" t="s" s="1">
+        <v>5271</v>
+      </c>
+      <c r="P364" t="s" s="1">
+        <v>5265</v>
+      </c>
+      <c r="Q364" t="s" s="1">
+        <v>5272</v>
+      </c>
+      <c r="R364" t="s" s="1">
+        <v>5265</v>
+      </c>
+      <c r="S364" t="s" s="1">
+        <v>5273</v>
+      </c>
+      <c r="T364" t="s" s="1">
+        <v>5265</v>
+      </c>
+      <c r="U364" t="s" s="1">
+        <v>5265</v>
+      </c>
+      <c r="V364" t="s" s="1">
+        <v>5265</v>
+      </c>
+      <c r="W364" t="s" s="1">
+        <v>5274</v>
+      </c>
+      <c r="X364" t="s" s="1">
+        <v>5266</v>
+      </c>
+      <c r="Y364" t="s" s="1">
+        <v>5265</v>
+      </c>
+      <c r="Z364" t="s" s="1">
+        <v>5265</v>
+      </c>
+      <c r="AA364" t="s" s="1">
+        <v>5265</v>
+      </c>
+      <c r="AB364" t="s" s="1">
+        <v>5265</v>
+      </c>
+      <c r="AC364" t="s" s="1">
+        <v>5274</v>
+      </c>
+      <c r="AD364" t="s" s="1">
+        <v>5275</v>
+      </c>
+      <c r="AE364" t="s" s="1">
+        <v>5276</v>
+      </c>
+      <c r="AF364" t="s" s="1">
         <v>5277</v>
-      </c>
-      <c r="D364" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="E364" t="s" s="1">
-        <v>5278</v>
-      </c>
-      <c r="F364" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="G364" t="s" s="1">
-        <v>5279</v>
-      </c>
-      <c r="H364" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="I364" t="s" s="1">
-        <v>5280</v>
-      </c>
-      <c r="J364" t="s" s="1">
-        <v>5281</v>
-      </c>
-      <c r="K364" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="L364" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="M364" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="N364" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O364" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="P364" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Q364" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="R364" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="S364" t="s" s="1">
-        <v>5282</v>
-      </c>
-      <c r="T364" t="s" s="1">
-        <v>5283</v>
-      </c>
-      <c r="U364" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="V364" t="s" s="1">
-        <v>5284</v>
-      </c>
-      <c r="W364" t="s" s="1">
-        <v>5285</v>
-      </c>
-      <c r="X364" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Y364" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Z364" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AA364" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AB364" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AC364" t="s" s="1">
-        <v>5286</v>
-      </c>
-      <c r="AD364" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AE364" t="s" s="1">
-        <v>5287</v>
-      </c>
-      <c r="AF364" t="s" s="1">
-        <v>5288</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="s" s="1">
-        <v>5289</v>
+        <v>5278</v>
       </c>
       <c r="B365" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C365" t="s" s="1">
+        <v>5279</v>
+      </c>
+      <c r="D365" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E365" t="s" s="1">
+        <v>5280</v>
+      </c>
+      <c r="F365" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="G365" t="s" s="1">
+        <v>5281</v>
+      </c>
+      <c r="H365" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="I365" t="s" s="1">
+        <v>5282</v>
+      </c>
+      <c r="J365" t="s" s="1">
+        <v>5283</v>
+      </c>
+      <c r="K365" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="L365" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M365" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="N365" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="O365" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="P365" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Q365" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="R365" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="S365" t="s" s="1">
+        <v>5284</v>
+      </c>
+      <c r="T365" t="s" s="1">
+        <v>5285</v>
+      </c>
+      <c r="U365" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="V365" t="s" s="1">
+        <v>5286</v>
+      </c>
+      <c r="W365" t="s" s="1">
+        <v>5287</v>
+      </c>
+      <c r="X365" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Y365" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Z365" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AA365" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AB365" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AC365" t="s" s="1">
+        <v>5288</v>
+      </c>
+      <c r="AD365" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AE365" t="s" s="1">
+        <v>5289</v>
+      </c>
+      <c r="AF365" t="s" s="1">
         <v>5290</v>
-      </c>
-      <c r="D365" t="s" s="1">
-        <v>5291</v>
-      </c>
-      <c r="E365" t="s" s="1">
-        <v>5292</v>
-      </c>
-      <c r="F365" t="s" s="1">
-        <v>5293</v>
-      </c>
-      <c r="G365" t="s" s="1">
-        <v>5293</v>
-      </c>
-      <c r="H365" t="s" s="1">
-        <v>5294</v>
-      </c>
-      <c r="I365" t="s" s="1">
-        <v>5295</v>
-      </c>
-      <c r="J365" t="s" s="1">
-        <v>5296</v>
-      </c>
-      <c r="K365" t="s" s="1">
-        <v>5297</v>
-      </c>
-      <c r="L365" t="s" s="1">
-        <v>5298</v>
-      </c>
-      <c r="M365" t="s" s="1">
-        <v>5299</v>
-      </c>
-      <c r="N365" t="s" s="1">
-        <v>5300</v>
-      </c>
-      <c r="O365" t="s" s="1">
-        <v>5301</v>
-      </c>
-      <c r="P365" t="s" s="1">
-        <v>5302</v>
-      </c>
-      <c r="Q365" t="s" s="1">
-        <v>5293</v>
-      </c>
-      <c r="R365" t="s" s="1">
-        <v>5302</v>
-      </c>
-      <c r="S365" t="s" s="1">
-        <v>5303</v>
-      </c>
-      <c r="T365" t="s" s="1">
-        <v>5295</v>
-      </c>
-      <c r="U365" t="s" s="1">
-        <v>5295</v>
-      </c>
-      <c r="V365" t="s" s="1">
-        <v>5304</v>
-      </c>
-      <c r="W365" t="s" s="1">
-        <v>5305</v>
-      </c>
-      <c r="X365" t="s" s="1">
-        <v>5306</v>
-      </c>
-      <c r="Y365" t="s" s="1">
-        <v>5307</v>
-      </c>
-      <c r="Z365" t="s" s="1">
-        <v>5293</v>
-      </c>
-      <c r="AA365" t="s" s="1">
-        <v>5308</v>
-      </c>
-      <c r="AB365" t="s" s="1">
-        <v>5309</v>
-      </c>
-      <c r="AC365" t="s" s="1">
-        <v>5310</v>
-      </c>
-      <c r="AD365" t="s" s="1">
-        <v>5311</v>
-      </c>
-      <c r="AE365" t="s" s="1">
-        <v>5312</v>
-      </c>
-      <c r="AF365" t="s" s="1">
-        <v>5313</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="s" s="1">
-        <v>5314</v>
+        <v>5291</v>
       </c>
       <c r="B366" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C366" t="s" s="1">
+        <v>5292</v>
+      </c>
+      <c r="D366" t="s" s="1">
+        <v>5293</v>
+      </c>
+      <c r="E366" t="s" s="1">
+        <v>5294</v>
+      </c>
+      <c r="F366" t="s" s="1">
+        <v>5295</v>
+      </c>
+      <c r="G366" t="s" s="1">
+        <v>5295</v>
+      </c>
+      <c r="H366" t="s" s="1">
+        <v>5296</v>
+      </c>
+      <c r="I366" t="s" s="1">
+        <v>5297</v>
+      </c>
+      <c r="J366" t="s" s="1">
+        <v>5298</v>
+      </c>
+      <c r="K366" t="s" s="1">
+        <v>5299</v>
+      </c>
+      <c r="L366" t="s" s="1">
+        <v>5300</v>
+      </c>
+      <c r="M366" t="s" s="1">
+        <v>5301</v>
+      </c>
+      <c r="N366" t="s" s="1">
+        <v>5302</v>
+      </c>
+      <c r="O366" t="s" s="1">
+        <v>5303</v>
+      </c>
+      <c r="P366" t="s" s="1">
+        <v>5304</v>
+      </c>
+      <c r="Q366" t="s" s="1">
+        <v>5295</v>
+      </c>
+      <c r="R366" t="s" s="1">
+        <v>5304</v>
+      </c>
+      <c r="S366" t="s" s="1">
+        <v>5305</v>
+      </c>
+      <c r="T366" t="s" s="1">
+        <v>5297</v>
+      </c>
+      <c r="U366" t="s" s="1">
+        <v>5297</v>
+      </c>
+      <c r="V366" t="s" s="1">
+        <v>5306</v>
+      </c>
+      <c r="W366" t="s" s="1">
+        <v>5307</v>
+      </c>
+      <c r="X366" t="s" s="1">
+        <v>5308</v>
+      </c>
+      <c r="Y366" t="s" s="1">
+        <v>5309</v>
+      </c>
+      <c r="Z366" t="s" s="1">
+        <v>5295</v>
+      </c>
+      <c r="AA366" t="s" s="1">
+        <v>5310</v>
+      </c>
+      <c r="AB366" t="s" s="1">
+        <v>5311</v>
+      </c>
+      <c r="AC366" t="s" s="1">
+        <v>5312</v>
+      </c>
+      <c r="AD366" t="s" s="1">
+        <v>5313</v>
+      </c>
+      <c r="AE366" t="s" s="1">
+        <v>5314</v>
+      </c>
+      <c r="AF366" t="s" s="1">
         <v>5315</v>
-      </c>
-      <c r="D366" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="E366" t="s" s="1">
-        <v>5316</v>
-      </c>
-      <c r="F366" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="G366" t="s" s="1">
-        <v>5317</v>
-      </c>
-      <c r="H366" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="I366" t="s" s="1">
-        <v>5318</v>
-      </c>
-      <c r="J366" t="s" s="1">
-        <v>5319</v>
-      </c>
-      <c r="K366" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="L366" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="M366" t="s" s="1">
-        <v>5320</v>
-      </c>
-      <c r="N366" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O366" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="P366" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Q366" t="s" s="1">
-        <v>5321</v>
-      </c>
-      <c r="R366" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="S366" t="s" s="1">
-        <v>5322</v>
-      </c>
-      <c r="T366" t="s" s="1">
-        <v>5323</v>
-      </c>
-      <c r="U366" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="V366" t="s" s="1">
-        <v>5324</v>
-      </c>
-      <c r="W366" t="s" s="1">
-        <v>5325</v>
-      </c>
-      <c r="X366" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Y366" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Z366" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AA366" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AB366" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AC366" t="s" s="1">
-        <v>5326</v>
-      </c>
-      <c r="AD366" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AE366" t="s" s="1">
-        <v>5327</v>
-      </c>
-      <c r="AF366" t="s" s="1">
-        <v>5328</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="s" s="1">
-        <v>5329</v>
+        <v>5316</v>
       </c>
       <c r="B367" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C367" t="s" s="1">
+        <v>5317</v>
+      </c>
+      <c r="D367" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E367" t="s" s="1">
+        <v>5318</v>
+      </c>
+      <c r="F367" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="G367" t="s" s="1">
+        <v>5319</v>
+      </c>
+      <c r="H367" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="I367" t="s" s="1">
+        <v>5320</v>
+      </c>
+      <c r="J367" t="s" s="1">
+        <v>5321</v>
+      </c>
+      <c r="K367" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="L367" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M367" t="s" s="1">
+        <v>5322</v>
+      </c>
+      <c r="N367" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="O367" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="P367" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Q367" t="s" s="1">
+        <v>5323</v>
+      </c>
+      <c r="R367" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="S367" t="s" s="1">
+        <v>5324</v>
+      </c>
+      <c r="T367" t="s" s="1">
+        <v>5325</v>
+      </c>
+      <c r="U367" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="V367" t="s" s="1">
+        <v>5326</v>
+      </c>
+      <c r="W367" t="s" s="1">
+        <v>5327</v>
+      </c>
+      <c r="X367" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Y367" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Z367" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AA367" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AB367" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AC367" t="s" s="1">
+        <v>5328</v>
+      </c>
+      <c r="AD367" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AE367" t="s" s="1">
+        <v>5329</v>
+      </c>
+      <c r="AF367" t="s" s="1">
         <v>5330</v>
-      </c>
-      <c r="D367" t="s" s="1">
-        <v>5331</v>
-      </c>
-      <c r="E367" t="s" s="1">
-        <v>5332</v>
-      </c>
-      <c r="F367" t="s" s="1">
-        <v>5333</v>
-      </c>
-      <c r="G367" t="s" s="1">
-        <v>5334</v>
-      </c>
-      <c r="H367" t="s" s="1">
-        <v>5335</v>
-      </c>
-      <c r="I367" t="s" s="1">
-        <v>5336</v>
-      </c>
-      <c r="J367" t="s" s="1">
-        <v>4584</v>
-      </c>
-      <c r="K367" t="s" s="1">
-        <v>5337</v>
-      </c>
-      <c r="L367" t="s" s="1">
-        <v>5338</v>
-      </c>
-      <c r="M367" t="s" s="1">
-        <v>5339</v>
-      </c>
-      <c r="N367" t="s" s="1">
-        <v>5340</v>
-      </c>
-      <c r="O367" t="s" s="1">
-        <v>5341</v>
-      </c>
-      <c r="P367" t="s" s="1">
-        <v>5342</v>
-      </c>
-      <c r="Q367" t="s" s="1">
-        <v>5343</v>
-      </c>
-      <c r="R367" t="s" s="1">
-        <v>5344</v>
-      </c>
-      <c r="S367" t="s" s="1">
-        <v>5345</v>
-      </c>
-      <c r="T367" t="s" s="1">
-        <v>5346</v>
-      </c>
-      <c r="U367" t="s" s="1">
-        <v>5346</v>
-      </c>
-      <c r="V367" t="s" s="1">
-        <v>5347</v>
-      </c>
-      <c r="W367" t="s" s="1">
-        <v>5348</v>
-      </c>
-      <c r="X367" t="s" s="1">
-        <v>5349</v>
-      </c>
-      <c r="Y367" t="s" s="1">
-        <v>5350</v>
-      </c>
-      <c r="Z367" t="s" s="1">
-        <v>5351</v>
-      </c>
-      <c r="AA367" t="s" s="1">
-        <v>5352</v>
-      </c>
-      <c r="AB367" t="s" s="1">
-        <v>5353</v>
-      </c>
-      <c r="AC367" t="s" s="1">
-        <v>5354</v>
-      </c>
-      <c r="AD367" t="s" s="1">
-        <v>5355</v>
-      </c>
-      <c r="AE367" t="s" s="1">
-        <v>5356</v>
-      </c>
-      <c r="AF367" t="s" s="1">
-        <v>5357</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="s" s="1">
-        <v>5358</v>
+        <v>5331</v>
       </c>
       <c r="B368" t="s" s="1">
         <v>33</v>
       </c>
-      <c r="C368" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="D368" t="s" s="3">
-        <v>63</v>
+      <c r="C368" t="s" s="1">
+        <v>5332</v>
+      </c>
+      <c r="D368" t="s" s="1">
+        <v>5333</v>
       </c>
       <c r="E368" t="s" s="1">
-        <v>4605</v>
-      </c>
-      <c r="F368" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="G368" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="H368" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="I368" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="J368" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="K368" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="L368" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="M368" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="N368" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="O368" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="P368" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="Q368" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="R368" t="s" s="3">
-        <v>63</v>
+        <v>5334</v>
+      </c>
+      <c r="F368" t="s" s="1">
+        <v>5335</v>
+      </c>
+      <c r="G368" t="s" s="1">
+        <v>5336</v>
+      </c>
+      <c r="H368" t="s" s="1">
+        <v>5337</v>
+      </c>
+      <c r="I368" t="s" s="1">
+        <v>5338</v>
+      </c>
+      <c r="J368" t="s" s="1">
+        <v>4584</v>
+      </c>
+      <c r="K368" t="s" s="1">
+        <v>5339</v>
+      </c>
+      <c r="L368" t="s" s="1">
+        <v>5340</v>
+      </c>
+      <c r="M368" t="s" s="1">
+        <v>5341</v>
+      </c>
+      <c r="N368" t="s" s="1">
+        <v>5342</v>
+      </c>
+      <c r="O368" t="s" s="1">
+        <v>5343</v>
+      </c>
+      <c r="P368" t="s" s="1">
+        <v>5344</v>
+      </c>
+      <c r="Q368" t="s" s="1">
+        <v>5345</v>
+      </c>
+      <c r="R368" t="s" s="1">
+        <v>5346</v>
       </c>
       <c r="S368" t="s" s="1">
+        <v>5347</v>
+      </c>
+      <c r="T368" t="s" s="1">
+        <v>5348</v>
+      </c>
+      <c r="U368" t="s" s="1">
+        <v>5348</v>
+      </c>
+      <c r="V368" t="s" s="1">
+        <v>5349</v>
+      </c>
+      <c r="W368" t="s" s="1">
+        <v>5350</v>
+      </c>
+      <c r="X368" t="s" s="1">
+        <v>5351</v>
+      </c>
+      <c r="Y368" t="s" s="1">
+        <v>5352</v>
+      </c>
+      <c r="Z368" t="s" s="1">
+        <v>5353</v>
+      </c>
+      <c r="AA368" t="s" s="1">
+        <v>5354</v>
+      </c>
+      <c r="AB368" t="s" s="1">
+        <v>5355</v>
+      </c>
+      <c r="AC368" t="s" s="1">
+        <v>5356</v>
+      </c>
+      <c r="AD368" t="s" s="1">
+        <v>5357</v>
+      </c>
+      <c r="AE368" t="s" s="1">
+        <v>5358</v>
+      </c>
+      <c r="AF368" t="s" s="1">
         <v>5359</v>
-      </c>
-      <c r="T368" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="U368" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="V368" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="W368" t="s" s="1">
-        <v>5360</v>
-      </c>
-      <c r="X368" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="Y368" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="Z368" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AA368" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AB368" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AC368" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AD368" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AE368" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AF368" t="s" s="3">
-        <v>63</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="s" s="1">
-        <v>5361</v>
+        <v>5360</v>
       </c>
       <c r="B369" t="s" s="1">
         <v>33</v>
@@ -76214,7 +76220,7 @@
         <v>63</v>
       </c>
       <c r="E369" t="s" s="1">
-        <v>4609</v>
+        <v>4605</v>
       </c>
       <c r="F369" t="s" s="3">
         <v>63</v>
@@ -76256,19 +76262,19 @@
         <v>63</v>
       </c>
       <c r="S369" t="s" s="1">
+        <v>5361</v>
+      </c>
+      <c r="T369" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="U369" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="V369" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="W369" t="s" s="1">
         <v>5362</v>
-      </c>
-      <c r="T369" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="U369" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="V369" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="W369" t="s" s="3">
-        <v>63</v>
       </c>
       <c r="X369" t="s" s="3">
         <v>63</v>
@@ -76305,296 +76311,296 @@
       <c r="B370" t="s" s="1">
         <v>33</v>
       </c>
-      <c r="C370" t="s" s="1">
+      <c r="C370" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="D370" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="E370" t="s" s="1">
+        <v>4609</v>
+      </c>
+      <c r="F370" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="G370" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="H370" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="I370" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="J370" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="K370" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="L370" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="M370" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="N370" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="O370" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="P370" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="Q370" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="R370" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="S370" t="s" s="1">
         <v>5364</v>
       </c>
-      <c r="D370" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="E370" t="s" s="1">
-        <v>4605</v>
-      </c>
-      <c r="F370" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="G370" t="s" s="1">
-        <v>5365</v>
-      </c>
-      <c r="H370" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="I370" t="s" s="1">
-        <v>5366</v>
-      </c>
-      <c r="J370" t="s" s="1">
-        <v>5367</v>
-      </c>
-      <c r="K370" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="L370" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="M370" t="s" s="1">
-        <v>5368</v>
-      </c>
-      <c r="N370" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O370" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="P370" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Q370" t="s" s="1">
-        <v>5369</v>
-      </c>
-      <c r="R370" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="S370" t="s" s="1">
-        <v>5370</v>
-      </c>
-      <c r="T370" t="s" s="1">
-        <v>5371</v>
-      </c>
-      <c r="U370" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="V370" t="s" s="1">
-        <v>5372</v>
-      </c>
-      <c r="W370" t="s" s="1">
-        <v>5373</v>
-      </c>
-      <c r="X370" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Y370" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Z370" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AA370" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AB370" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AC370" t="s" s="1">
-        <v>5374</v>
-      </c>
-      <c r="AD370" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AE370" t="s" s="1">
-        <v>5375</v>
-      </c>
-      <c r="AF370" t="s" s="1">
-        <v>5376</v>
+      <c r="T370" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="U370" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="V370" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="W370" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="X370" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="Y370" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="Z370" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AA370" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AB370" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AC370" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AD370" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AE370" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AF370" t="s" s="3">
+        <v>63</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="s" s="1">
-        <v>5377</v>
+        <v>5365</v>
       </c>
       <c r="B371" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C371" t="s" s="1">
+        <v>5366</v>
+      </c>
+      <c r="D371" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E371" t="s" s="1">
+        <v>4605</v>
+      </c>
+      <c r="F371" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="G371" t="s" s="1">
+        <v>5367</v>
+      </c>
+      <c r="H371" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="I371" t="s" s="1">
+        <v>5368</v>
+      </c>
+      <c r="J371" t="s" s="1">
+        <v>5369</v>
+      </c>
+      <c r="K371" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="L371" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M371" t="s" s="1">
+        <v>5370</v>
+      </c>
+      <c r="N371" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="O371" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="P371" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Q371" t="s" s="1">
+        <v>5371</v>
+      </c>
+      <c r="R371" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="S371" t="s" s="1">
+        <v>5372</v>
+      </c>
+      <c r="T371" t="s" s="1">
+        <v>5373</v>
+      </c>
+      <c r="U371" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="V371" t="s" s="1">
+        <v>5374</v>
+      </c>
+      <c r="W371" t="s" s="1">
+        <v>5375</v>
+      </c>
+      <c r="X371" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Y371" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Z371" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AA371" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AB371" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AC371" t="s" s="1">
+        <v>5376</v>
+      </c>
+      <c r="AD371" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AE371" t="s" s="1">
+        <v>5377</v>
+      </c>
+      <c r="AF371" t="s" s="1">
         <v>5378</v>
-      </c>
-      <c r="D371" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="E371" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="F371" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="G371" t="s" s="1">
-        <v>5379</v>
-      </c>
-      <c r="H371" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="I371" t="s" s="1">
-        <v>5380</v>
-      </c>
-      <c r="J371" t="s" s="1">
-        <v>5381</v>
-      </c>
-      <c r="K371" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="L371" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="M371" t="s" s="1">
-        <v>5382</v>
-      </c>
-      <c r="N371" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O371" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="P371" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Q371" t="s" s="1">
-        <v>5383</v>
-      </c>
-      <c r="R371" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="S371" t="s" s="1">
-        <v>5362</v>
-      </c>
-      <c r="T371" t="s" s="1">
-        <v>5384</v>
-      </c>
-      <c r="U371" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="V371" t="s" s="1">
-        <v>5385</v>
-      </c>
-      <c r="W371" t="s" s="1">
-        <v>5386</v>
-      </c>
-      <c r="X371" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Y371" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Z371" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AA371" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AB371" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AC371" t="s" s="1">
-        <v>5374</v>
-      </c>
-      <c r="AD371" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AE371" t="s" s="1">
-        <v>5375</v>
-      </c>
-      <c r="AF371" t="s" s="1">
-        <v>5376</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="s" s="1">
-        <v>5387</v>
+        <v>5379</v>
       </c>
       <c r="B372" t="s" s="1">
         <v>33</v>
       </c>
-      <c r="C372" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="D372" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="E372" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="F372" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="G372" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="H372" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="I372" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="J372" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="K372" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="L372" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="M372" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="N372" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="O372" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="P372" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="Q372" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="R372" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="S372" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="T372" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="U372" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="V372" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="W372" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="X372" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="Y372" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="Z372" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AA372" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AB372" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AC372" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AD372" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AE372" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AF372" t="s" s="3">
-        <v>63</v>
+      <c r="C372" t="s" s="1">
+        <v>5380</v>
+      </c>
+      <c r="D372" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E372" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="F372" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="G372" t="s" s="1">
+        <v>5381</v>
+      </c>
+      <c r="H372" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="I372" t="s" s="1">
+        <v>5382</v>
+      </c>
+      <c r="J372" t="s" s="1">
+        <v>5383</v>
+      </c>
+      <c r="K372" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="L372" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M372" t="s" s="1">
+        <v>5384</v>
+      </c>
+      <c r="N372" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="O372" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="P372" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Q372" t="s" s="1">
+        <v>5385</v>
+      </c>
+      <c r="R372" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="S372" t="s" s="1">
+        <v>5364</v>
+      </c>
+      <c r="T372" t="s" s="1">
+        <v>5386</v>
+      </c>
+      <c r="U372" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="V372" t="s" s="1">
+        <v>5387</v>
+      </c>
+      <c r="W372" t="s" s="1">
+        <v>5388</v>
+      </c>
+      <c r="X372" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Y372" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Z372" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AA372" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AB372" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AC372" t="s" s="1">
+        <v>5376</v>
+      </c>
+      <c r="AD372" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AE372" t="s" s="1">
+        <v>5377</v>
+      </c>
+      <c r="AF372" t="s" s="1">
+        <v>5378</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="s" s="1">
-        <v>5388</v>
+        <v>5389</v>
       </c>
       <c r="B373" t="s" s="1">
         <v>33</v>
@@ -76692,1966 +76698,2064 @@
     </row>
     <row r="374">
       <c r="A374" t="s" s="1">
-        <v>5389</v>
+        <v>5390</v>
       </c>
       <c r="B374" t="s" s="1">
         <v>33</v>
       </c>
-      <c r="C374" t="s" s="1">
-        <v>5390</v>
-      </c>
-      <c r="D374" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="E374" t="s" s="1">
-        <v>5391</v>
-      </c>
-      <c r="F374" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="G374" t="s" s="1">
-        <v>5392</v>
-      </c>
-      <c r="H374" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="I374" t="s" s="1">
-        <v>5393</v>
-      </c>
-      <c r="J374" t="s" s="1">
-        <v>5394</v>
-      </c>
-      <c r="K374" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="L374" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="M374" t="s" s="1">
-        <v>5395</v>
-      </c>
-      <c r="N374" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O374" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="P374" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Q374" t="s" s="1">
-        <v>5396</v>
-      </c>
-      <c r="R374" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="S374" t="s" s="1">
-        <v>5397</v>
-      </c>
-      <c r="T374" t="s" s="1">
-        <v>5398</v>
-      </c>
-      <c r="U374" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="V374" t="s" s="1">
-        <v>5399</v>
-      </c>
-      <c r="W374" t="s" s="1">
-        <v>5400</v>
-      </c>
-      <c r="X374" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Y374" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Z374" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AA374" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AB374" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AC374" t="s" s="1">
-        <v>5401</v>
-      </c>
-      <c r="AD374" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AE374" t="s" s="1">
-        <v>5402</v>
-      </c>
-      <c r="AF374" t="s" s="1">
-        <v>5403</v>
+      <c r="C374" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="D374" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="E374" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="F374" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="G374" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="H374" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="I374" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="J374" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="K374" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="L374" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="M374" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="N374" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="O374" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="P374" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="Q374" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="R374" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="S374" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="T374" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="U374" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="V374" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="W374" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="X374" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="Y374" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="Z374" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AA374" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AB374" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AC374" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AD374" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AE374" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AF374" t="s" s="3">
+        <v>63</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="s" s="1">
-        <v>5404</v>
+        <v>5391</v>
       </c>
       <c r="B375" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C375" t="s" s="1">
+        <v>5392</v>
+      </c>
+      <c r="D375" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E375" t="s" s="1">
+        <v>5393</v>
+      </c>
+      <c r="F375" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="G375" t="s" s="1">
+        <v>5394</v>
+      </c>
+      <c r="H375" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="I375" t="s" s="1">
+        <v>5395</v>
+      </c>
+      <c r="J375" t="s" s="1">
+        <v>5396</v>
+      </c>
+      <c r="K375" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="L375" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M375" t="s" s="1">
+        <v>5397</v>
+      </c>
+      <c r="N375" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="O375" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="P375" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Q375" t="s" s="1">
+        <v>5398</v>
+      </c>
+      <c r="R375" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="S375" t="s" s="1">
+        <v>5399</v>
+      </c>
+      <c r="T375" t="s" s="1">
+        <v>5400</v>
+      </c>
+      <c r="U375" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="V375" t="s" s="1">
+        <v>5401</v>
+      </c>
+      <c r="W375" t="s" s="1">
+        <v>5402</v>
+      </c>
+      <c r="X375" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Y375" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Z375" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AA375" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AB375" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AC375" t="s" s="1">
+        <v>5403</v>
+      </c>
+      <c r="AD375" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AE375" t="s" s="1">
+        <v>5404</v>
+      </c>
+      <c r="AF375" t="s" s="1">
         <v>5405</v>
-      </c>
-      <c r="D375" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="E375" t="s" s="1">
-        <v>566</v>
-      </c>
-      <c r="F375" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="G375" t="s" s="1">
-        <v>5406</v>
-      </c>
-      <c r="H375" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="I375" t="s" s="1">
-        <v>5407</v>
-      </c>
-      <c r="J375" t="s" s="1">
-        <v>865</v>
-      </c>
-      <c r="K375" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="L375" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="M375" t="s" s="1">
-        <v>868</v>
-      </c>
-      <c r="N375" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O375" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="P375" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Q375" t="s" s="1">
-        <v>5408</v>
-      </c>
-      <c r="R375" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="S375" t="s" s="1">
-        <v>571</v>
-      </c>
-      <c r="T375" t="s" s="1">
-        <v>5409</v>
-      </c>
-      <c r="U375" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="V375" t="s" s="1">
-        <v>5410</v>
-      </c>
-      <c r="W375" t="s" s="1">
-        <v>4401</v>
-      </c>
-      <c r="X375" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Y375" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Z375" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AA375" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AB375" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AC375" t="s" s="1">
-        <v>5411</v>
-      </c>
-      <c r="AD375" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AE375" t="s" s="1">
-        <v>5412</v>
-      </c>
-      <c r="AF375" t="s" s="1">
-        <v>5413</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="s" s="1">
-        <v>5414</v>
+        <v>5406</v>
       </c>
       <c r="B376" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C376" t="s" s="1">
+        <v>5407</v>
+      </c>
+      <c r="D376" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E376" t="s" s="1">
+        <v>566</v>
+      </c>
+      <c r="F376" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="G376" t="s" s="1">
+        <v>5408</v>
+      </c>
+      <c r="H376" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="I376" t="s" s="1">
+        <v>5409</v>
+      </c>
+      <c r="J376" t="s" s="1">
+        <v>865</v>
+      </c>
+      <c r="K376" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="L376" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M376" t="s" s="1">
+        <v>868</v>
+      </c>
+      <c r="N376" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="O376" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="P376" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Q376" t="s" s="1">
+        <v>5410</v>
+      </c>
+      <c r="R376" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="S376" t="s" s="1">
+        <v>571</v>
+      </c>
+      <c r="T376" t="s" s="1">
+        <v>5411</v>
+      </c>
+      <c r="U376" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="V376" t="s" s="1">
+        <v>5412</v>
+      </c>
+      <c r="W376" t="s" s="1">
+        <v>4401</v>
+      </c>
+      <c r="X376" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Y376" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Z376" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AA376" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AB376" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AC376" t="s" s="1">
+        <v>5413</v>
+      </c>
+      <c r="AD376" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AE376" t="s" s="1">
+        <v>5414</v>
+      </c>
+      <c r="AF376" t="s" s="1">
         <v>5415</v>
-      </c>
-      <c r="D376" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="E376" t="s" s="1">
-        <v>5416</v>
-      </c>
-      <c r="F376" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="G376" t="s" s="1">
-        <v>5417</v>
-      </c>
-      <c r="H376" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="I376" t="s" s="1">
-        <v>5418</v>
-      </c>
-      <c r="J376" t="s" s="1">
-        <v>5419</v>
-      </c>
-      <c r="K376" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="L376" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="M376" t="s" s="1">
-        <v>5420</v>
-      </c>
-      <c r="N376" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O376" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="P376" t="s" s="1">
-        <v>5421</v>
-      </c>
-      <c r="Q376" t="s" s="1">
-        <v>5422</v>
-      </c>
-      <c r="R376" t="s" s="1">
-        <v>5423</v>
-      </c>
-      <c r="S376" t="s" s="1">
-        <v>5424</v>
-      </c>
-      <c r="T376" t="s" s="1">
-        <v>5425</v>
-      </c>
-      <c r="U376" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="V376" t="s" s="1">
-        <v>5426</v>
-      </c>
-      <c r="W376" t="s" s="1">
-        <v>5427</v>
-      </c>
-      <c r="X376" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Y376" t="s" s="1">
-        <v>5428</v>
-      </c>
-      <c r="Z376" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AA376" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AB376" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AC376" t="s" s="1">
-        <v>5429</v>
-      </c>
-      <c r="AD376" t="s" s="1">
-        <v>5430</v>
-      </c>
-      <c r="AE376" t="s" s="1">
-        <v>5431</v>
-      </c>
-      <c r="AF376" t="s" s="1">
-        <v>5432</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="s" s="1">
-        <v>5433</v>
+        <v>5416</v>
       </c>
       <c r="B377" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C377" t="s" s="1">
+        <v>5417</v>
+      </c>
+      <c r="D377" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E377" t="s" s="1">
+        <v>5418</v>
+      </c>
+      <c r="F377" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="G377" t="s" s="1">
+        <v>5419</v>
+      </c>
+      <c r="H377" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="I377" t="s" s="1">
+        <v>5420</v>
+      </c>
+      <c r="J377" t="s" s="1">
+        <v>5421</v>
+      </c>
+      <c r="K377" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="L377" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M377" t="s" s="1">
+        <v>5422</v>
+      </c>
+      <c r="N377" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="O377" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="P377" t="s" s="1">
+        <v>5423</v>
+      </c>
+      <c r="Q377" t="s" s="1">
+        <v>5424</v>
+      </c>
+      <c r="R377" t="s" s="1">
+        <v>5425</v>
+      </c>
+      <c r="S377" t="s" s="1">
+        <v>5426</v>
+      </c>
+      <c r="T377" t="s" s="1">
+        <v>5427</v>
+      </c>
+      <c r="U377" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="V377" t="s" s="1">
+        <v>5428</v>
+      </c>
+      <c r="W377" t="s" s="1">
+        <v>5429</v>
+      </c>
+      <c r="X377" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Y377" t="s" s="1">
+        <v>5430</v>
+      </c>
+      <c r="Z377" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AA377" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AB377" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AC377" t="s" s="1">
+        <v>5431</v>
+      </c>
+      <c r="AD377" t="s" s="1">
+        <v>5432</v>
+      </c>
+      <c r="AE377" t="s" s="1">
+        <v>5433</v>
+      </c>
+      <c r="AF377" t="s" s="1">
         <v>5434</v>
-      </c>
-      <c r="D377" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="E377" t="s" s="1">
-        <v>5435</v>
-      </c>
-      <c r="F377" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="G377" t="s" s="1">
-        <v>5436</v>
-      </c>
-      <c r="H377" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="I377" t="s" s="1">
-        <v>5437</v>
-      </c>
-      <c r="J377" t="s" s="1">
-        <v>5438</v>
-      </c>
-      <c r="K377" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="L377" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="M377" t="s" s="1">
-        <v>5439</v>
-      </c>
-      <c r="N377" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O377" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="P377" t="s" s="1">
-        <v>5440</v>
-      </c>
-      <c r="Q377" t="s" s="1">
-        <v>5441</v>
-      </c>
-      <c r="R377" t="s" s="1">
-        <v>5442</v>
-      </c>
-      <c r="S377" t="s" s="1">
-        <v>5443</v>
-      </c>
-      <c r="T377" t="s" s="1">
-        <v>5444</v>
-      </c>
-      <c r="U377" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="V377" t="s" s="1">
-        <v>5445</v>
-      </c>
-      <c r="W377" t="s" s="1">
-        <v>5446</v>
-      </c>
-      <c r="X377" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Y377" t="s" s="1">
-        <v>5447</v>
-      </c>
-      <c r="Z377" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AA377" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AB377" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AC377" t="s" s="1">
-        <v>5448</v>
-      </c>
-      <c r="AD377" t="s" s="1">
-        <v>5449</v>
-      </c>
-      <c r="AE377" t="s" s="1">
-        <v>5450</v>
-      </c>
-      <c r="AF377" t="s" s="1">
-        <v>5451</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="s" s="1">
-        <v>5452</v>
+        <v>5435</v>
       </c>
       <c r="B378" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C378" t="s" s="1">
+        <v>5436</v>
+      </c>
+      <c r="D378" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E378" t="s" s="1">
+        <v>5437</v>
+      </c>
+      <c r="F378" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="G378" t="s" s="1">
+        <v>5438</v>
+      </c>
+      <c r="H378" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="I378" t="s" s="1">
+        <v>5439</v>
+      </c>
+      <c r="J378" t="s" s="1">
+        <v>5440</v>
+      </c>
+      <c r="K378" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="L378" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M378" t="s" s="1">
+        <v>5441</v>
+      </c>
+      <c r="N378" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="O378" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="P378" t="s" s="1">
+        <v>5442</v>
+      </c>
+      <c r="Q378" t="s" s="1">
+        <v>5443</v>
+      </c>
+      <c r="R378" t="s" s="1">
+        <v>5444</v>
+      </c>
+      <c r="S378" t="s" s="1">
+        <v>5445</v>
+      </c>
+      <c r="T378" t="s" s="1">
+        <v>5446</v>
+      </c>
+      <c r="U378" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="V378" t="s" s="1">
+        <v>5447</v>
+      </c>
+      <c r="W378" t="s" s="1">
+        <v>5448</v>
+      </c>
+      <c r="X378" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Y378" t="s" s="1">
+        <v>5449</v>
+      </c>
+      <c r="Z378" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AA378" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AB378" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AC378" t="s" s="1">
+        <v>5450</v>
+      </c>
+      <c r="AD378" t="s" s="1">
+        <v>5451</v>
+      </c>
+      <c r="AE378" t="s" s="1">
+        <v>5452</v>
+      </c>
+      <c r="AF378" t="s" s="1">
         <v>5453</v>
-      </c>
-      <c r="D378" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="E378" t="s" s="1">
-        <v>5454</v>
-      </c>
-      <c r="F378" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="G378" t="s" s="1">
-        <v>5455</v>
-      </c>
-      <c r="H378" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="I378" t="s" s="1">
-        <v>5456</v>
-      </c>
-      <c r="J378" t="s" s="1">
-        <v>5457</v>
-      </c>
-      <c r="K378" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="L378" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="M378" t="s" s="1">
-        <v>5458</v>
-      </c>
-      <c r="N378" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O378" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="P378" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Q378" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="R378" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="S378" t="s" s="1">
-        <v>5459</v>
-      </c>
-      <c r="T378" t="s" s="1">
-        <v>5460</v>
-      </c>
-      <c r="U378" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="V378" t="s" s="1">
-        <v>5461</v>
-      </c>
-      <c r="W378" t="s" s="1">
-        <v>5462</v>
-      </c>
-      <c r="X378" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Y378" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Z378" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AA378" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AB378" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AC378" t="s" s="1">
-        <v>5463</v>
-      </c>
-      <c r="AD378" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AE378" t="s" s="1">
-        <v>5464</v>
-      </c>
-      <c r="AF378" t="s" s="1">
-        <v>5465</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="s" s="1">
-        <v>5466</v>
+        <v>5454</v>
       </c>
       <c r="B379" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C379" t="s" s="1">
+        <v>5455</v>
+      </c>
+      <c r="D379" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E379" t="s" s="1">
+        <v>5456</v>
+      </c>
+      <c r="F379" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="G379" t="s" s="1">
+        <v>5457</v>
+      </c>
+      <c r="H379" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="I379" t="s" s="1">
+        <v>5458</v>
+      </c>
+      <c r="J379" t="s" s="1">
+        <v>5459</v>
+      </c>
+      <c r="K379" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="L379" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M379" t="s" s="1">
+        <v>5460</v>
+      </c>
+      <c r="N379" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="O379" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="P379" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Q379" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="R379" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="S379" t="s" s="1">
+        <v>5461</v>
+      </c>
+      <c r="T379" t="s" s="1">
+        <v>5462</v>
+      </c>
+      <c r="U379" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="V379" t="s" s="1">
+        <v>5463</v>
+      </c>
+      <c r="W379" t="s" s="1">
+        <v>5464</v>
+      </c>
+      <c r="X379" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Y379" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Z379" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AA379" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AB379" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AC379" t="s" s="1">
+        <v>5465</v>
+      </c>
+      <c r="AD379" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AE379" t="s" s="1">
+        <v>5466</v>
+      </c>
+      <c r="AF379" t="s" s="1">
         <v>5467</v>
-      </c>
-      <c r="D379" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="E379" t="s" s="1">
-        <v>5468</v>
-      </c>
-      <c r="F379" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="G379" t="s" s="1">
-        <v>5469</v>
-      </c>
-      <c r="H379" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="I379" t="s" s="1">
-        <v>5470</v>
-      </c>
-      <c r="J379" t="s" s="1">
-        <v>5471</v>
-      </c>
-      <c r="K379" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="L379" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="M379" t="s" s="1">
-        <v>5472</v>
-      </c>
-      <c r="N379" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O379" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="P379" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Q379" t="s" s="1">
-        <v>5473</v>
-      </c>
-      <c r="R379" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="S379" t="s" s="1">
-        <v>5474</v>
-      </c>
-      <c r="T379" t="s" s="1">
-        <v>5475</v>
-      </c>
-      <c r="U379" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="V379" t="s" s="1">
-        <v>5476</v>
-      </c>
-      <c r="W379" t="s" s="1">
-        <v>5477</v>
-      </c>
-      <c r="X379" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Y379" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Z379" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AA379" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AB379" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AC379" t="s" s="1">
-        <v>5478</v>
-      </c>
-      <c r="AD379" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AE379" t="s" s="1">
-        <v>5479</v>
-      </c>
-      <c r="AF379" t="s" s="1">
-        <v>5480</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="s" s="1">
-        <v>5481</v>
+        <v>5468</v>
       </c>
       <c r="B380" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C380" t="s" s="1">
+        <v>5469</v>
+      </c>
+      <c r="D380" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E380" t="s" s="1">
+        <v>5470</v>
+      </c>
+      <c r="F380" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="G380" t="s" s="1">
+        <v>5471</v>
+      </c>
+      <c r="H380" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="I380" t="s" s="1">
+        <v>5472</v>
+      </c>
+      <c r="J380" t="s" s="1">
+        <v>5473</v>
+      </c>
+      <c r="K380" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="L380" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M380" t="s" s="1">
+        <v>5474</v>
+      </c>
+      <c r="N380" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="O380" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="P380" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Q380" t="s" s="1">
+        <v>5475</v>
+      </c>
+      <c r="R380" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="S380" t="s" s="1">
+        <v>5476</v>
+      </c>
+      <c r="T380" t="s" s="1">
+        <v>5477</v>
+      </c>
+      <c r="U380" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="V380" t="s" s="1">
+        <v>5478</v>
+      </c>
+      <c r="W380" t="s" s="1">
+        <v>5479</v>
+      </c>
+      <c r="X380" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Y380" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Z380" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AA380" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AB380" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AC380" t="s" s="1">
+        <v>5480</v>
+      </c>
+      <c r="AD380" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AE380" t="s" s="1">
+        <v>5481</v>
+      </c>
+      <c r="AF380" t="s" s="1">
         <v>5482</v>
-      </c>
-      <c r="D380" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="E380" t="s" s="1">
-        <v>5483</v>
-      </c>
-      <c r="F380" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="G380" t="s" s="1">
-        <v>5484</v>
-      </c>
-      <c r="H380" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="I380" t="s" s="1">
-        <v>5485</v>
-      </c>
-      <c r="J380" t="s" s="1">
-        <v>5486</v>
-      </c>
-      <c r="K380" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="L380" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="M380" t="s" s="1">
-        <v>5487</v>
-      </c>
-      <c r="N380" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O380" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="P380" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Q380" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="R380" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="S380" t="s" s="1">
-        <v>5488</v>
-      </c>
-      <c r="T380" t="s" s="1">
-        <v>5489</v>
-      </c>
-      <c r="U380" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="V380" t="s" s="1">
-        <v>5490</v>
-      </c>
-      <c r="W380" t="s" s="1">
-        <v>5491</v>
-      </c>
-      <c r="X380" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Y380" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Z380" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AA380" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AB380" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AC380" t="s" s="1">
-        <v>5492</v>
-      </c>
-      <c r="AD380" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AE380" t="s" s="1">
-        <v>5493</v>
-      </c>
-      <c r="AF380" t="s" s="1">
-        <v>5494</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="s" s="1">
-        <v>5495</v>
+        <v>5483</v>
       </c>
       <c r="B381" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C381" t="s" s="1">
+        <v>5484</v>
+      </c>
+      <c r="D381" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E381" t="s" s="1">
+        <v>5485</v>
+      </c>
+      <c r="F381" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="G381" t="s" s="1">
+        <v>5486</v>
+      </c>
+      <c r="H381" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="I381" t="s" s="1">
+        <v>5487</v>
+      </c>
+      <c r="J381" t="s" s="1">
+        <v>5488</v>
+      </c>
+      <c r="K381" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="L381" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M381" t="s" s="1">
+        <v>5489</v>
+      </c>
+      <c r="N381" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="O381" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="P381" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Q381" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="R381" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="S381" t="s" s="1">
+        <v>5490</v>
+      </c>
+      <c r="T381" t="s" s="1">
+        <v>5491</v>
+      </c>
+      <c r="U381" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="V381" t="s" s="1">
+        <v>5492</v>
+      </c>
+      <c r="W381" t="s" s="1">
+        <v>5493</v>
+      </c>
+      <c r="X381" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Y381" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Z381" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AA381" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AB381" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AC381" t="s" s="1">
+        <v>5494</v>
+      </c>
+      <c r="AD381" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AE381" t="s" s="1">
+        <v>5495</v>
+      </c>
+      <c r="AF381" t="s" s="1">
         <v>5496</v>
-      </c>
-      <c r="D381" t="s" s="1">
-        <v>5497</v>
-      </c>
-      <c r="E381" t="s" s="1">
-        <v>5498</v>
-      </c>
-      <c r="F381" t="s" s="1">
-        <v>5499</v>
-      </c>
-      <c r="G381" t="s" s="1">
-        <v>5500</v>
-      </c>
-      <c r="H381" t="s" s="1">
-        <v>5501</v>
-      </c>
-      <c r="I381" t="s" s="1">
-        <v>5502</v>
-      </c>
-      <c r="J381" t="s" s="1">
-        <v>5503</v>
-      </c>
-      <c r="K381" t="s" s="1">
-        <v>5504</v>
-      </c>
-      <c r="L381" t="s" s="1">
-        <v>5505</v>
-      </c>
-      <c r="M381" t="s" s="1">
-        <v>5506</v>
-      </c>
-      <c r="N381" t="s" s="1">
-        <v>5507</v>
-      </c>
-      <c r="O381" t="s" s="1">
-        <v>5508</v>
-      </c>
-      <c r="P381" t="s" s="1">
-        <v>5509</v>
-      </c>
-      <c r="Q381" t="s" s="1">
-        <v>5510</v>
-      </c>
-      <c r="R381" t="s" s="1">
-        <v>5511</v>
-      </c>
-      <c r="S381" t="s" s="1">
-        <v>5512</v>
-      </c>
-      <c r="T381" t="s" s="1">
-        <v>5513</v>
-      </c>
-      <c r="U381" t="s" s="1">
-        <v>5513</v>
-      </c>
-      <c r="V381" t="s" s="1">
-        <v>5514</v>
-      </c>
-      <c r="W381" t="s" s="1">
-        <v>5515</v>
-      </c>
-      <c r="X381" t="s" s="1">
-        <v>5516</v>
-      </c>
-      <c r="Y381" t="s" s="1">
-        <v>5517</v>
-      </c>
-      <c r="Z381" t="s" s="1">
-        <v>5518</v>
-      </c>
-      <c r="AA381" t="s" s="1">
-        <v>5519</v>
-      </c>
-      <c r="AB381" t="s" s="1">
-        <v>5520</v>
-      </c>
-      <c r="AC381" t="s" s="1">
-        <v>5521</v>
-      </c>
-      <c r="AD381" t="s" s="1">
-        <v>5522</v>
-      </c>
-      <c r="AE381" t="s" s="1">
-        <v>5523</v>
-      </c>
-      <c r="AF381" t="s" s="1">
-        <v>5524</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="s" s="1">
-        <v>5525</v>
+        <v>5497</v>
       </c>
       <c r="B382" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C382" t="s" s="1">
+        <v>5498</v>
+      </c>
+      <c r="D382" t="s" s="1">
+        <v>5499</v>
+      </c>
+      <c r="E382" t="s" s="1">
+        <v>5500</v>
+      </c>
+      <c r="F382" t="s" s="1">
+        <v>5501</v>
+      </c>
+      <c r="G382" t="s" s="1">
+        <v>5502</v>
+      </c>
+      <c r="H382" t="s" s="1">
+        <v>5503</v>
+      </c>
+      <c r="I382" t="s" s="1">
+        <v>5504</v>
+      </c>
+      <c r="J382" t="s" s="1">
+        <v>5505</v>
+      </c>
+      <c r="K382" t="s" s="1">
+        <v>5506</v>
+      </c>
+      <c r="L382" t="s" s="1">
+        <v>5507</v>
+      </c>
+      <c r="M382" t="s" s="1">
+        <v>5508</v>
+      </c>
+      <c r="N382" t="s" s="1">
+        <v>5509</v>
+      </c>
+      <c r="O382" t="s" s="1">
+        <v>5510</v>
+      </c>
+      <c r="P382" t="s" s="1">
+        <v>5511</v>
+      </c>
+      <c r="Q382" t="s" s="1">
+        <v>5512</v>
+      </c>
+      <c r="R382" t="s" s="1">
+        <v>5513</v>
+      </c>
+      <c r="S382" t="s" s="1">
+        <v>5514</v>
+      </c>
+      <c r="T382" t="s" s="1">
+        <v>5515</v>
+      </c>
+      <c r="U382" t="s" s="1">
+        <v>5515</v>
+      </c>
+      <c r="V382" t="s" s="1">
+        <v>5516</v>
+      </c>
+      <c r="W382" t="s" s="1">
+        <v>5517</v>
+      </c>
+      <c r="X382" t="s" s="1">
+        <v>5518</v>
+      </c>
+      <c r="Y382" t="s" s="1">
+        <v>5519</v>
+      </c>
+      <c r="Z382" t="s" s="1">
+        <v>5520</v>
+      </c>
+      <c r="AA382" t="s" s="1">
+        <v>5521</v>
+      </c>
+      <c r="AB382" t="s" s="1">
+        <v>5522</v>
+      </c>
+      <c r="AC382" t="s" s="1">
+        <v>5523</v>
+      </c>
+      <c r="AD382" t="s" s="1">
+        <v>5524</v>
+      </c>
+      <c r="AE382" t="s" s="1">
+        <v>5525</v>
+      </c>
+      <c r="AF382" t="s" s="1">
         <v>5526</v>
-      </c>
-      <c r="D382" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="E382" t="s" s="1">
-        <v>5527</v>
-      </c>
-      <c r="F382" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="G382" t="s" s="1">
-        <v>5528</v>
-      </c>
-      <c r="H382" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="I382" t="s" s="1">
-        <v>3909</v>
-      </c>
-      <c r="J382" t="s" s="1">
-        <v>5529</v>
-      </c>
-      <c r="K382" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="L382" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="M382" t="s" s="1">
-        <v>3907</v>
-      </c>
-      <c r="N382" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O382" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="P382" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Q382" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="R382" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="S382" t="s" s="1">
-        <v>5530</v>
-      </c>
-      <c r="T382" t="s" s="1">
-        <v>5531</v>
-      </c>
-      <c r="U382" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="V382" t="s" s="1">
-        <v>5532</v>
-      </c>
-      <c r="W382" t="s" s="1">
-        <v>5533</v>
-      </c>
-      <c r="X382" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Y382" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Z382" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AA382" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AB382" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AC382" t="s" s="1">
-        <v>5534</v>
-      </c>
-      <c r="AD382" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AE382" t="s" s="1">
-        <v>5535</v>
-      </c>
-      <c r="AF382" t="s" s="1">
-        <v>5536</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="s" s="1">
-        <v>5537</v>
+        <v>5527</v>
       </c>
       <c r="B383" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C383" t="s" s="1">
+        <v>5528</v>
+      </c>
+      <c r="D383" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E383" t="s" s="1">
+        <v>5529</v>
+      </c>
+      <c r="F383" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="G383" t="s" s="1">
+        <v>5530</v>
+      </c>
+      <c r="H383" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="I383" t="s" s="1">
+        <v>3909</v>
+      </c>
+      <c r="J383" t="s" s="1">
+        <v>5531</v>
+      </c>
+      <c r="K383" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="L383" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M383" t="s" s="1">
+        <v>3907</v>
+      </c>
+      <c r="N383" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="O383" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="P383" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Q383" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="R383" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="S383" t="s" s="1">
+        <v>5532</v>
+      </c>
+      <c r="T383" t="s" s="1">
+        <v>5533</v>
+      </c>
+      <c r="U383" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="V383" t="s" s="1">
+        <v>5534</v>
+      </c>
+      <c r="W383" t="s" s="1">
+        <v>5535</v>
+      </c>
+      <c r="X383" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Y383" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Z383" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AA383" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AB383" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AC383" t="s" s="1">
+        <v>5536</v>
+      </c>
+      <c r="AD383" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AE383" t="s" s="1">
+        <v>5537</v>
+      </c>
+      <c r="AF383" t="s" s="1">
         <v>5538</v>
-      </c>
-      <c r="D383" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="E383" t="s" s="1">
-        <v>2286</v>
-      </c>
-      <c r="F383" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="G383" t="s" s="1">
-        <v>5539</v>
-      </c>
-      <c r="H383" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="I383" t="s" s="1">
-        <v>5540</v>
-      </c>
-      <c r="J383" t="s" s="1">
-        <v>5541</v>
-      </c>
-      <c r="K383" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="L383" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="M383" t="s" s="1">
-        <v>5542</v>
-      </c>
-      <c r="N383" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O383" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="P383" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Q383" t="s" s="1">
-        <v>5543</v>
-      </c>
-      <c r="R383" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="S383" t="s" s="1">
-        <v>5544</v>
-      </c>
-      <c r="T383" t="s" s="1">
-        <v>5545</v>
-      </c>
-      <c r="U383" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="V383" t="s" s="1">
-        <v>5546</v>
-      </c>
-      <c r="W383" t="s" s="1">
-        <v>5547</v>
-      </c>
-      <c r="X383" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Y383" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Z383" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AA383" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AB383" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AC383" t="s" s="1">
-        <v>5548</v>
-      </c>
-      <c r="AD383" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AE383" t="s" s="1">
-        <v>5549</v>
-      </c>
-      <c r="AF383" t="s" s="1">
-        <v>5550</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="s" s="1">
-        <v>5551</v>
+        <v>5539</v>
       </c>
       <c r="B384" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C384" t="s" s="1">
+        <v>5540</v>
+      </c>
+      <c r="D384" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E384" t="s" s="1">
+        <v>2286</v>
+      </c>
+      <c r="F384" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="G384" t="s" s="1">
+        <v>5541</v>
+      </c>
+      <c r="H384" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="I384" t="s" s="1">
+        <v>5542</v>
+      </c>
+      <c r="J384" t="s" s="1">
+        <v>5543</v>
+      </c>
+      <c r="K384" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="L384" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M384" t="s" s="1">
+        <v>5544</v>
+      </c>
+      <c r="N384" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="O384" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="P384" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Q384" t="s" s="1">
+        <v>5545</v>
+      </c>
+      <c r="R384" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="S384" t="s" s="1">
+        <v>5546</v>
+      </c>
+      <c r="T384" t="s" s="1">
+        <v>5547</v>
+      </c>
+      <c r="U384" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="V384" t="s" s="1">
+        <v>5548</v>
+      </c>
+      <c r="W384" t="s" s="1">
+        <v>5549</v>
+      </c>
+      <c r="X384" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Y384" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Z384" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AA384" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AB384" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AC384" t="s" s="1">
+        <v>5550</v>
+      </c>
+      <c r="AD384" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AE384" t="s" s="1">
+        <v>5551</v>
+      </c>
+      <c r="AF384" t="s" s="1">
         <v>5552</v>
-      </c>
-      <c r="D384" t="s" s="1">
-        <v>5553</v>
-      </c>
-      <c r="E384" t="s" s="1">
-        <v>5554</v>
-      </c>
-      <c r="F384" t="s" s="1">
-        <v>5555</v>
-      </c>
-      <c r="G384" t="s" s="1">
-        <v>5556</v>
-      </c>
-      <c r="H384" t="s" s="1">
-        <v>5557</v>
-      </c>
-      <c r="I384" t="s" s="1">
-        <v>5558</v>
-      </c>
-      <c r="J384" t="s" s="1">
-        <v>5559</v>
-      </c>
-      <c r="K384" t="s" s="1">
-        <v>5560</v>
-      </c>
-      <c r="L384" t="s" s="1">
-        <v>5561</v>
-      </c>
-      <c r="M384" t="s" s="1">
-        <v>5558</v>
-      </c>
-      <c r="N384" t="s" s="1">
-        <v>5562</v>
-      </c>
-      <c r="O384" t="s" s="1">
-        <v>5563</v>
-      </c>
-      <c r="P384" t="s" s="1">
-        <v>5555</v>
-      </c>
-      <c r="Q384" t="s" s="1">
-        <v>5564</v>
-      </c>
-      <c r="R384" t="s" s="1">
-        <v>5555</v>
-      </c>
-      <c r="S384" t="s" s="1">
-        <v>5565</v>
-      </c>
-      <c r="T384" t="s" s="1">
-        <v>5566</v>
-      </c>
-      <c r="U384" t="s" s="1">
-        <v>5566</v>
-      </c>
-      <c r="V384" t="s" s="1">
-        <v>5567</v>
-      </c>
-      <c r="W384" t="s" s="1">
-        <v>5568</v>
-      </c>
-      <c r="X384" t="s" s="1">
-        <v>5569</v>
-      </c>
-      <c r="Y384" t="s" s="1">
-        <v>5570</v>
-      </c>
-      <c r="Z384" t="s" s="1">
-        <v>5571</v>
-      </c>
-      <c r="AA384" t="s" s="1">
-        <v>5572</v>
-      </c>
-      <c r="AB384" t="s" s="1">
-        <v>5573</v>
-      </c>
-      <c r="AC384" t="s" s="1">
-        <v>5574</v>
-      </c>
-      <c r="AD384" t="s" s="1">
-        <v>5575</v>
-      </c>
-      <c r="AE384" t="s" s="1">
-        <v>5576</v>
-      </c>
-      <c r="AF384" t="s" s="1">
-        <v>5577</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="s" s="1">
-        <v>5578</v>
+        <v>5553</v>
       </c>
       <c r="B385" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C385" t="s" s="1">
+        <v>5554</v>
+      </c>
+      <c r="D385" t="s" s="1">
+        <v>5555</v>
+      </c>
+      <c r="E385" t="s" s="1">
+        <v>5556</v>
+      </c>
+      <c r="F385" t="s" s="1">
+        <v>5557</v>
+      </c>
+      <c r="G385" t="s" s="1">
+        <v>5558</v>
+      </c>
+      <c r="H385" t="s" s="1">
+        <v>5559</v>
+      </c>
+      <c r="I385" t="s" s="1">
+        <v>5560</v>
+      </c>
+      <c r="J385" t="s" s="1">
+        <v>5561</v>
+      </c>
+      <c r="K385" t="s" s="1">
+        <v>5562</v>
+      </c>
+      <c r="L385" t="s" s="1">
+        <v>5563</v>
+      </c>
+      <c r="M385" t="s" s="1">
+        <v>5560</v>
+      </c>
+      <c r="N385" t="s" s="1">
+        <v>5564</v>
+      </c>
+      <c r="O385" t="s" s="1">
+        <v>5565</v>
+      </c>
+      <c r="P385" t="s" s="1">
+        <v>5557</v>
+      </c>
+      <c r="Q385" t="s" s="1">
+        <v>5566</v>
+      </c>
+      <c r="R385" t="s" s="1">
+        <v>5557</v>
+      </c>
+      <c r="S385" t="s" s="1">
+        <v>5567</v>
+      </c>
+      <c r="T385" t="s" s="1">
+        <v>5568</v>
+      </c>
+      <c r="U385" t="s" s="1">
+        <v>5568</v>
+      </c>
+      <c r="V385" t="s" s="1">
+        <v>5569</v>
+      </c>
+      <c r="W385" t="s" s="1">
+        <v>5570</v>
+      </c>
+      <c r="X385" t="s" s="1">
+        <v>5571</v>
+      </c>
+      <c r="Y385" t="s" s="1">
+        <v>5572</v>
+      </c>
+      <c r="Z385" t="s" s="1">
+        <v>5573</v>
+      </c>
+      <c r="AA385" t="s" s="1">
+        <v>5574</v>
+      </c>
+      <c r="AB385" t="s" s="1">
+        <v>5575</v>
+      </c>
+      <c r="AC385" t="s" s="1">
+        <v>5576</v>
+      </c>
+      <c r="AD385" t="s" s="1">
+        <v>5577</v>
+      </c>
+      <c r="AE385" t="s" s="1">
+        <v>5578</v>
+      </c>
+      <c r="AF385" t="s" s="1">
         <v>5579</v>
-      </c>
-      <c r="D385" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="E385" t="s" s="1">
-        <v>5580</v>
-      </c>
-      <c r="F385" t="s" s="1">
-        <v>5581</v>
-      </c>
-      <c r="G385" t="s" s="1">
-        <v>5582</v>
-      </c>
-      <c r="H385" t="s" s="1">
-        <v>5583</v>
-      </c>
-      <c r="I385" t="s" s="1">
-        <v>5584</v>
-      </c>
-      <c r="J385" t="s" s="1">
-        <v>5585</v>
-      </c>
-      <c r="K385" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="L385" t="s" s="1">
-        <v>5586</v>
-      </c>
-      <c r="M385" t="s" s="1">
-        <v>5587</v>
-      </c>
-      <c r="N385" t="s" s="1">
-        <v>5588</v>
-      </c>
-      <c r="O385" t="s" s="1">
-        <v>5589</v>
-      </c>
-      <c r="P385" t="s" s="1">
-        <v>5581</v>
-      </c>
-      <c r="Q385" t="s" s="1">
-        <v>5590</v>
-      </c>
-      <c r="R385" t="s" s="1">
-        <v>5591</v>
-      </c>
-      <c r="S385" t="s" s="1">
-        <v>5592</v>
-      </c>
-      <c r="T385" t="s" s="1">
-        <v>5593</v>
-      </c>
-      <c r="U385" t="s" s="1">
-        <v>5594</v>
-      </c>
-      <c r="V385" t="s" s="1">
-        <v>5595</v>
-      </c>
-      <c r="W385" t="s" s="1">
-        <v>5596</v>
-      </c>
-      <c r="X385" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Y385" t="s" s="1">
-        <v>5597</v>
-      </c>
-      <c r="Z385" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AA385" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AB385" t="s" s="1">
-        <v>5598</v>
-      </c>
-      <c r="AC385" t="s" s="1">
-        <v>5599</v>
-      </c>
-      <c r="AD385" t="s" s="1">
-        <v>5600</v>
-      </c>
-      <c r="AE385" t="s" s="1">
-        <v>5601</v>
-      </c>
-      <c r="AF385" t="s" s="1">
-        <v>5602</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="s" s="1">
-        <v>5603</v>
+        <v>5580</v>
       </c>
       <c r="B386" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C386" t="s" s="1">
+        <v>5581</v>
+      </c>
+      <c r="D386" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E386" t="s" s="1">
+        <v>5582</v>
+      </c>
+      <c r="F386" t="s" s="1">
+        <v>5583</v>
+      </c>
+      <c r="G386" t="s" s="1">
+        <v>5584</v>
+      </c>
+      <c r="H386" t="s" s="1">
+        <v>5585</v>
+      </c>
+      <c r="I386" t="s" s="1">
+        <v>5586</v>
+      </c>
+      <c r="J386" t="s" s="1">
+        <v>5587</v>
+      </c>
+      <c r="K386" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="L386" t="s" s="1">
+        <v>5588</v>
+      </c>
+      <c r="M386" t="s" s="1">
+        <v>5589</v>
+      </c>
+      <c r="N386" t="s" s="1">
+        <v>5590</v>
+      </c>
+      <c r="O386" t="s" s="1">
+        <v>5591</v>
+      </c>
+      <c r="P386" t="s" s="1">
+        <v>5583</v>
+      </c>
+      <c r="Q386" t="s" s="1">
+        <v>5592</v>
+      </c>
+      <c r="R386" t="s" s="1">
+        <v>5593</v>
+      </c>
+      <c r="S386" t="s" s="1">
+        <v>5594</v>
+      </c>
+      <c r="T386" t="s" s="1">
+        <v>5595</v>
+      </c>
+      <c r="U386" t="s" s="1">
+        <v>5596</v>
+      </c>
+      <c r="V386" t="s" s="1">
+        <v>5597</v>
+      </c>
+      <c r="W386" t="s" s="1">
+        <v>5598</v>
+      </c>
+      <c r="X386" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Y386" t="s" s="1">
+        <v>5599</v>
+      </c>
+      <c r="Z386" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AA386" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AB386" t="s" s="1">
+        <v>5600</v>
+      </c>
+      <c r="AC386" t="s" s="1">
+        <v>5601</v>
+      </c>
+      <c r="AD386" t="s" s="1">
+        <v>5602</v>
+      </c>
+      <c r="AE386" t="s" s="1">
+        <v>5603</v>
+      </c>
+      <c r="AF386" t="s" s="1">
         <v>5604</v>
-      </c>
-      <c r="D386" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="E386" t="s" s="1">
-        <v>5605</v>
-      </c>
-      <c r="F386" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="G386" t="s" s="1">
-        <v>5606</v>
-      </c>
-      <c r="H386" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="I386" t="s" s="1">
-        <v>5607</v>
-      </c>
-      <c r="J386" t="s" s="1">
-        <v>5608</v>
-      </c>
-      <c r="K386" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="L386" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="M386" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="N386" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O386" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="P386" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Q386" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="R386" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="S386" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="T386" t="s" s="1">
-        <v>5609</v>
-      </c>
-      <c r="U386" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="V386" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="W386" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="X386" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Y386" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Z386" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AA386" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AB386" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AC386" t="s" s="1">
-        <v>5610</v>
-      </c>
-      <c r="AD386" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AE386" t="s" s="1">
-        <v>5611</v>
-      </c>
-      <c r="AF386" t="s" s="2">
-        <v>63</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="s" s="1">
-        <v>5612</v>
+        <v>5605</v>
       </c>
       <c r="B387" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C387" t="s" s="1">
+        <v>5606</v>
+      </c>
+      <c r="D387" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E387" t="s" s="1">
+        <v>5607</v>
+      </c>
+      <c r="F387" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="G387" t="s" s="1">
+        <v>5608</v>
+      </c>
+      <c r="H387" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="I387" t="s" s="1">
+        <v>5609</v>
+      </c>
+      <c r="J387" t="s" s="1">
+        <v>5610</v>
+      </c>
+      <c r="K387" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="L387" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M387" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="N387" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="O387" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="P387" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Q387" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="R387" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="S387" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="T387" t="s" s="1">
+        <v>5611</v>
+      </c>
+      <c r="U387" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="V387" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="W387" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="X387" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Y387" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Z387" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AA387" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AB387" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AC387" t="s" s="1">
+        <v>5612</v>
+      </c>
+      <c r="AD387" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AE387" t="s" s="1">
         <v>5613</v>
       </c>
-      <c r="D387" t="s" s="1">
-        <v>5614</v>
-      </c>
-      <c r="E387" t="s" s="1">
-        <v>5615</v>
-      </c>
-      <c r="F387" t="s" s="1">
-        <v>5616</v>
-      </c>
-      <c r="G387" t="s" s="1">
-        <v>5617</v>
-      </c>
-      <c r="H387" t="s" s="1">
-        <v>5618</v>
-      </c>
-      <c r="I387" t="s" s="1">
-        <v>5619</v>
-      </c>
-      <c r="J387" t="s" s="1">
-        <v>5620</v>
-      </c>
-      <c r="K387" t="s" s="1">
-        <v>5621</v>
-      </c>
-      <c r="L387" t="s" s="1">
-        <v>5622</v>
-      </c>
-      <c r="M387" t="s" s="1">
-        <v>5623</v>
-      </c>
-      <c r="N387" t="s" s="1">
-        <v>5624</v>
-      </c>
-      <c r="O387" t="s" s="1">
-        <v>5625</v>
-      </c>
-      <c r="P387" t="s" s="1">
-        <v>5626</v>
-      </c>
-      <c r="Q387" t="s" s="1">
-        <v>5627</v>
-      </c>
-      <c r="R387" t="s" s="1">
-        <v>5628</v>
-      </c>
-      <c r="S387" t="s" s="1">
-        <v>5629</v>
-      </c>
-      <c r="T387" t="s" s="1">
-        <v>5630</v>
-      </c>
-      <c r="U387" t="s" s="1">
-        <v>5630</v>
-      </c>
-      <c r="V387" t="s" s="1">
-        <v>5631</v>
-      </c>
-      <c r="W387" t="s" s="1">
-        <v>5632</v>
-      </c>
-      <c r="X387" t="s" s="1">
-        <v>5633</v>
-      </c>
-      <c r="Y387" t="s" s="1">
-        <v>5634</v>
-      </c>
-      <c r="Z387" t="s" s="1">
-        <v>5635</v>
-      </c>
-      <c r="AA387" t="s" s="1">
-        <v>5636</v>
-      </c>
-      <c r="AB387" t="s" s="1">
-        <v>5637</v>
-      </c>
-      <c r="AC387" t="s" s="1">
-        <v>5638</v>
-      </c>
-      <c r="AD387" t="s" s="1">
-        <v>5639</v>
-      </c>
-      <c r="AE387" t="s" s="1">
-        <v>5640</v>
-      </c>
-      <c r="AF387" t="s" s="1">
-        <v>5641</v>
+      <c r="AF387" t="s" s="2">
+        <v>63</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="s" s="1">
-        <v>5642</v>
+        <v>5614</v>
       </c>
       <c r="B388" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C388" t="s" s="1">
+        <v>5615</v>
+      </c>
+      <c r="D388" t="s" s="1">
+        <v>5616</v>
+      </c>
+      <c r="E388" t="s" s="1">
+        <v>5617</v>
+      </c>
+      <c r="F388" t="s" s="1">
+        <v>5618</v>
+      </c>
+      <c r="G388" t="s" s="1">
+        <v>5619</v>
+      </c>
+      <c r="H388" t="s" s="1">
+        <v>5620</v>
+      </c>
+      <c r="I388" t="s" s="1">
+        <v>5621</v>
+      </c>
+      <c r="J388" t="s" s="1">
+        <v>5622</v>
+      </c>
+      <c r="K388" t="s" s="1">
+        <v>5623</v>
+      </c>
+      <c r="L388" t="s" s="1">
+        <v>5624</v>
+      </c>
+      <c r="M388" t="s" s="1">
+        <v>5625</v>
+      </c>
+      <c r="N388" t="s" s="1">
+        <v>5626</v>
+      </c>
+      <c r="O388" t="s" s="1">
+        <v>5627</v>
+      </c>
+      <c r="P388" t="s" s="1">
+        <v>5628</v>
+      </c>
+      <c r="Q388" t="s" s="1">
+        <v>5629</v>
+      </c>
+      <c r="R388" t="s" s="1">
+        <v>5630</v>
+      </c>
+      <c r="S388" t="s" s="1">
+        <v>5631</v>
+      </c>
+      <c r="T388" t="s" s="1">
+        <v>5632</v>
+      </c>
+      <c r="U388" t="s" s="1">
+        <v>5632</v>
+      </c>
+      <c r="V388" t="s" s="1">
+        <v>5633</v>
+      </c>
+      <c r="W388" t="s" s="1">
+        <v>5634</v>
+      </c>
+      <c r="X388" t="s" s="1">
+        <v>5635</v>
+      </c>
+      <c r="Y388" t="s" s="1">
+        <v>5636</v>
+      </c>
+      <c r="Z388" t="s" s="1">
+        <v>5637</v>
+      </c>
+      <c r="AA388" t="s" s="1">
+        <v>5638</v>
+      </c>
+      <c r="AB388" t="s" s="1">
+        <v>5639</v>
+      </c>
+      <c r="AC388" t="s" s="1">
+        <v>5640</v>
+      </c>
+      <c r="AD388" t="s" s="1">
+        <v>5641</v>
+      </c>
+      <c r="AE388" t="s" s="1">
+        <v>5642</v>
+      </c>
+      <c r="AF388" t="s" s="1">
         <v>5643</v>
-      </c>
-      <c r="D388" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="E388" t="s" s="1">
-        <v>5644</v>
-      </c>
-      <c r="F388" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="G388" t="s" s="1">
-        <v>5645</v>
-      </c>
-      <c r="H388" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="I388" t="s" s="1">
-        <v>5646</v>
-      </c>
-      <c r="J388" t="s" s="1">
-        <v>5647</v>
-      </c>
-      <c r="K388" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="L388" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="M388" t="s" s="1">
-        <v>5648</v>
-      </c>
-      <c r="N388" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O388" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="P388" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Q388" t="s" s="1">
-        <v>5649</v>
-      </c>
-      <c r="R388" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="S388" t="s" s="1">
-        <v>5650</v>
-      </c>
-      <c r="T388" t="s" s="1">
-        <v>5651</v>
-      </c>
-      <c r="U388" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="V388" t="s" s="1">
-        <v>5652</v>
-      </c>
-      <c r="W388" t="s" s="1">
-        <v>5653</v>
-      </c>
-      <c r="X388" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Y388" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Z388" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AA388" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AB388" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AC388" t="s" s="1">
-        <v>5654</v>
-      </c>
-      <c r="AD388" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AE388" t="s" s="1">
-        <v>5655</v>
-      </c>
-      <c r="AF388" t="s" s="1">
-        <v>5656</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="s" s="1">
-        <v>5657</v>
+        <v>5644</v>
       </c>
       <c r="B389" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C389" t="s" s="1">
+        <v>5645</v>
+      </c>
+      <c r="D389" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E389" t="s" s="1">
+        <v>5646</v>
+      </c>
+      <c r="F389" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="G389" t="s" s="1">
+        <v>5647</v>
+      </c>
+      <c r="H389" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="I389" t="s" s="1">
+        <v>5648</v>
+      </c>
+      <c r="J389" t="s" s="1">
+        <v>5649</v>
+      </c>
+      <c r="K389" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="L389" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M389" t="s" s="1">
+        <v>5650</v>
+      </c>
+      <c r="N389" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="O389" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="P389" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Q389" t="s" s="1">
+        <v>5651</v>
+      </c>
+      <c r="R389" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="S389" t="s" s="1">
+        <v>5652</v>
+      </c>
+      <c r="T389" t="s" s="1">
+        <v>5653</v>
+      </c>
+      <c r="U389" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="V389" t="s" s="1">
+        <v>5654</v>
+      </c>
+      <c r="W389" t="s" s="1">
+        <v>5655</v>
+      </c>
+      <c r="X389" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Y389" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Z389" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AA389" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AB389" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AC389" t="s" s="1">
+        <v>5656</v>
+      </c>
+      <c r="AD389" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AE389" t="s" s="1">
+        <v>5657</v>
+      </c>
+      <c r="AF389" t="s" s="1">
         <v>5658</v>
-      </c>
-      <c r="D389" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="E389" t="s" s="1">
-        <v>5659</v>
-      </c>
-      <c r="F389" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="G389" t="s" s="1">
-        <v>5660</v>
-      </c>
-      <c r="H389" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="I389" t="s" s="1">
-        <v>5661</v>
-      </c>
-      <c r="J389" t="s" s="1">
-        <v>5662</v>
-      </c>
-      <c r="K389" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="L389" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="M389" t="s" s="1">
-        <v>5663</v>
-      </c>
-      <c r="N389" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O389" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="P389" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Q389" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="R389" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="S389" t="s" s="1">
-        <v>5664</v>
-      </c>
-      <c r="T389" t="s" s="1">
-        <v>5661</v>
-      </c>
-      <c r="U389" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="V389" t="s" s="1">
-        <v>5665</v>
-      </c>
-      <c r="W389" t="s" s="1">
-        <v>5666</v>
-      </c>
-      <c r="X389" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Y389" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Z389" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AA389" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AB389" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AC389" t="s" s="1">
-        <v>5667</v>
-      </c>
-      <c r="AD389" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AE389" t="s" s="1">
-        <v>5668</v>
-      </c>
-      <c r="AF389" t="s" s="1">
-        <v>5669</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="s" s="1">
-        <v>5670</v>
+        <v>5659</v>
       </c>
       <c r="B390" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C390" t="s" s="1">
+        <v>5660</v>
+      </c>
+      <c r="D390" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E390" t="s" s="1">
+        <v>5661</v>
+      </c>
+      <c r="F390" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="G390" t="s" s="1">
+        <v>5662</v>
+      </c>
+      <c r="H390" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="I390" t="s" s="1">
+        <v>5663</v>
+      </c>
+      <c r="J390" t="s" s="1">
+        <v>5664</v>
+      </c>
+      <c r="K390" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="L390" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M390" t="s" s="1">
+        <v>5665</v>
+      </c>
+      <c r="N390" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="O390" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="P390" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Q390" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="R390" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="S390" t="s" s="1">
+        <v>5666</v>
+      </c>
+      <c r="T390" t="s" s="1">
+        <v>5663</v>
+      </c>
+      <c r="U390" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="V390" t="s" s="1">
+        <v>5667</v>
+      </c>
+      <c r="W390" t="s" s="1">
+        <v>5668</v>
+      </c>
+      <c r="X390" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Y390" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Z390" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AA390" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AB390" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AC390" t="s" s="1">
+        <v>5669</v>
+      </c>
+      <c r="AD390" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AE390" t="s" s="1">
+        <v>5670</v>
+      </c>
+      <c r="AF390" t="s" s="1">
         <v>5671</v>
-      </c>
-      <c r="D390" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="E390" t="s" s="1">
-        <v>5672</v>
-      </c>
-      <c r="F390" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="G390" t="s" s="1">
-        <v>5673</v>
-      </c>
-      <c r="H390" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="I390" t="s" s="1">
-        <v>5674</v>
-      </c>
-      <c r="J390" t="s" s="1">
-        <v>5675</v>
-      </c>
-      <c r="K390" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="L390" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="M390" t="s" s="1">
-        <v>5676</v>
-      </c>
-      <c r="N390" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O390" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="P390" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Q390" t="s" s="1">
-        <v>5677</v>
-      </c>
-      <c r="R390" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="S390" t="s" s="1">
-        <v>5678</v>
-      </c>
-      <c r="T390" t="s" s="1">
-        <v>5679</v>
-      </c>
-      <c r="U390" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="V390" t="s" s="1">
-        <v>5680</v>
-      </c>
-      <c r="W390" t="s" s="1">
-        <v>5681</v>
-      </c>
-      <c r="X390" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Y390" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Z390" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AA390" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AB390" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AC390" t="s" s="1">
-        <v>5682</v>
-      </c>
-      <c r="AD390" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AE390" t="s" s="1">
-        <v>5683</v>
-      </c>
-      <c r="AF390" t="s" s="1">
-        <v>5684</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="s" s="1">
-        <v>5685</v>
+        <v>5672</v>
       </c>
       <c r="B391" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C391" t="s" s="1">
+        <v>5673</v>
+      </c>
+      <c r="D391" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E391" t="s" s="1">
+        <v>5674</v>
+      </c>
+      <c r="F391" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="G391" t="s" s="1">
+        <v>5675</v>
+      </c>
+      <c r="H391" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="I391" t="s" s="1">
+        <v>5676</v>
+      </c>
+      <c r="J391" t="s" s="1">
+        <v>5677</v>
+      </c>
+      <c r="K391" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="L391" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M391" t="s" s="1">
+        <v>5678</v>
+      </c>
+      <c r="N391" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="O391" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="P391" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Q391" t="s" s="1">
+        <v>5679</v>
+      </c>
+      <c r="R391" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="S391" t="s" s="1">
+        <v>5680</v>
+      </c>
+      <c r="T391" t="s" s="1">
+        <v>5681</v>
+      </c>
+      <c r="U391" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="V391" t="s" s="1">
+        <v>5682</v>
+      </c>
+      <c r="W391" t="s" s="1">
+        <v>5683</v>
+      </c>
+      <c r="X391" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Y391" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Z391" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AA391" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AB391" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AC391" t="s" s="1">
+        <v>5684</v>
+      </c>
+      <c r="AD391" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AE391" t="s" s="1">
+        <v>5685</v>
+      </c>
+      <c r="AF391" t="s" s="1">
         <v>5686</v>
-      </c>
-      <c r="D391" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="E391" t="s" s="1">
-        <v>5687</v>
-      </c>
-      <c r="F391" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="G391" t="s" s="1">
-        <v>5688</v>
-      </c>
-      <c r="H391" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="I391" t="s" s="1">
-        <v>5689</v>
-      </c>
-      <c r="J391" t="s" s="1">
-        <v>5690</v>
-      </c>
-      <c r="K391" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="L391" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="M391" t="s" s="1">
-        <v>5691</v>
-      </c>
-      <c r="N391" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O391" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="P391" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Q391" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="R391" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="S391" t="s" s="1">
-        <v>5692</v>
-      </c>
-      <c r="T391" t="s" s="1">
-        <v>5693</v>
-      </c>
-      <c r="U391" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="V391" t="s" s="1">
-        <v>5689</v>
-      </c>
-      <c r="W391" t="s" s="1">
-        <v>5694</v>
-      </c>
-      <c r="X391" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Y391" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Z391" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AA391" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AB391" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AC391" t="s" s="1">
-        <v>5695</v>
-      </c>
-      <c r="AD391" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AE391" t="s" s="1">
-        <v>5696</v>
-      </c>
-      <c r="AF391" t="s" s="1">
-        <v>5697</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="s" s="1">
-        <v>5698</v>
+        <v>5687</v>
       </c>
       <c r="B392" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C392" t="s" s="1">
+        <v>5688</v>
+      </c>
+      <c r="D392" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E392" t="s" s="1">
+        <v>5689</v>
+      </c>
+      <c r="F392" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="G392" t="s" s="1">
+        <v>5690</v>
+      </c>
+      <c r="H392" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="I392" t="s" s="1">
+        <v>5691</v>
+      </c>
+      <c r="J392" t="s" s="1">
+        <v>5692</v>
+      </c>
+      <c r="K392" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="L392" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M392" t="s" s="1">
+        <v>5693</v>
+      </c>
+      <c r="N392" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="O392" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="P392" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Q392" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="R392" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="S392" t="s" s="1">
+        <v>5694</v>
+      </c>
+      <c r="T392" t="s" s="1">
+        <v>5695</v>
+      </c>
+      <c r="U392" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="V392" t="s" s="1">
+        <v>5691</v>
+      </c>
+      <c r="W392" t="s" s="1">
+        <v>5696</v>
+      </c>
+      <c r="X392" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Y392" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Z392" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AA392" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AB392" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AC392" t="s" s="1">
+        <v>5697</v>
+      </c>
+      <c r="AD392" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AE392" t="s" s="1">
+        <v>5698</v>
+      </c>
+      <c r="AF392" t="s" s="1">
         <v>5699</v>
-      </c>
-      <c r="D392" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="E392" t="s" s="1">
-        <v>5700</v>
-      </c>
-      <c r="F392" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="G392" t="s" s="1">
-        <v>5701</v>
-      </c>
-      <c r="H392" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="I392" t="s" s="1">
-        <v>5702</v>
-      </c>
-      <c r="J392" t="s" s="1">
-        <v>5703</v>
-      </c>
-      <c r="K392" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="L392" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="M392" t="s" s="1">
-        <v>5704</v>
-      </c>
-      <c r="N392" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O392" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="P392" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Q392" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="R392" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="S392" t="s" s="1">
-        <v>5705</v>
-      </c>
-      <c r="T392" t="s" s="1">
-        <v>5706</v>
-      </c>
-      <c r="U392" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="V392" t="s" s="1">
-        <v>5707</v>
-      </c>
-      <c r="W392" t="s" s="1">
-        <v>5708</v>
-      </c>
-      <c r="X392" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Y392" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Z392" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AA392" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AB392" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AC392" t="s" s="1">
-        <v>5709</v>
-      </c>
-      <c r="AD392" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AE392" t="s" s="1">
-        <v>5710</v>
-      </c>
-      <c r="AF392" t="s" s="1">
-        <v>5711</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="s" s="1">
-        <v>5712</v>
+        <v>5700</v>
       </c>
       <c r="B393" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C393" t="s" s="1">
+        <v>5701</v>
+      </c>
+      <c r="D393" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E393" t="s" s="1">
+        <v>5702</v>
+      </c>
+      <c r="F393" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="G393" t="s" s="1">
+        <v>5703</v>
+      </c>
+      <c r="H393" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="I393" t="s" s="1">
+        <v>5704</v>
+      </c>
+      <c r="J393" t="s" s="1">
+        <v>5705</v>
+      </c>
+      <c r="K393" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="L393" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M393" t="s" s="1">
+        <v>5706</v>
+      </c>
+      <c r="N393" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="O393" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="P393" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Q393" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="R393" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="S393" t="s" s="1">
+        <v>5707</v>
+      </c>
+      <c r="T393" t="s" s="1">
+        <v>5708</v>
+      </c>
+      <c r="U393" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="V393" t="s" s="1">
+        <v>5709</v>
+      </c>
+      <c r="W393" t="s" s="1">
+        <v>5710</v>
+      </c>
+      <c r="X393" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Y393" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Z393" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AA393" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AB393" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AC393" t="s" s="1">
+        <v>5711</v>
+      </c>
+      <c r="AD393" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AE393" t="s" s="1">
+        <v>5712</v>
+      </c>
+      <c r="AF393" t="s" s="1">
         <v>5713</v>
       </c>
-      <c r="D393" t="s" s="1">
+    </row>
+    <row r="394">
+      <c r="A394" t="s" s="1">
         <v>5714</v>
       </c>
-      <c r="E393" t="s" s="1">
+      <c r="B394" t="s" s="1">
+        <v>33</v>
+      </c>
+      <c r="C394" t="s" s="1">
         <v>5715</v>
       </c>
-      <c r="F393" t="s" s="1">
+      <c r="D394" t="s" s="1">
         <v>5716</v>
       </c>
-      <c r="G393" t="s" s="1">
+      <c r="E394" t="s" s="1">
         <v>5717</v>
       </c>
-      <c r="H393" t="s" s="1">
+      <c r="F394" t="s" s="1">
         <v>5718</v>
       </c>
-      <c r="I393" t="s" s="1">
+      <c r="G394" t="s" s="1">
         <v>5719</v>
       </c>
-      <c r="J393" t="s" s="1">
+      <c r="H394" t="s" s="1">
         <v>5720</v>
       </c>
-      <c r="K393" t="s" s="1">
+      <c r="I394" t="s" s="1">
         <v>5721</v>
       </c>
-      <c r="L393" t="s" s="1">
+      <c r="J394" t="s" s="1">
         <v>5722</v>
       </c>
-      <c r="M393" t="s" s="1">
+      <c r="K394" t="s" s="1">
         <v>5723</v>
       </c>
-      <c r="N393" t="s" s="1">
+      <c r="L394" t="s" s="1">
         <v>5724</v>
       </c>
-      <c r="O393" t="s" s="1">
+      <c r="M394" t="s" s="1">
         <v>5725</v>
       </c>
-      <c r="P393" t="s" s="1">
+      <c r="N394" t="s" s="1">
         <v>5726</v>
       </c>
-      <c r="Q393" t="s" s="1">
+      <c r="O394" t="s" s="1">
         <v>5727</v>
       </c>
-      <c r="R393" t="s" s="1">
+      <c r="P394" t="s" s="1">
         <v>5728</v>
       </c>
-      <c r="S393" t="s" s="1">
+      <c r="Q394" t="s" s="1">
         <v>5729</v>
       </c>
-      <c r="T393" t="s" s="1">
+      <c r="R394" t="s" s="1">
         <v>5730</v>
       </c>
-      <c r="U393" t="s" s="1">
+      <c r="S394" t="s" s="1">
         <v>5731</v>
       </c>
-      <c r="V393" t="s" s="1">
+      <c r="T394" t="s" s="1">
         <v>5732</v>
       </c>
-      <c r="W393" t="s" s="1">
+      <c r="U394" t="s" s="1">
         <v>5733</v>
       </c>
-      <c r="X393" t="s" s="1">
+      <c r="V394" t="s" s="1">
         <v>5734</v>
       </c>
-      <c r="Y393" t="s" s="1">
+      <c r="W394" t="s" s="1">
         <v>5735</v>
       </c>
-      <c r="Z393" t="s" s="1">
+      <c r="X394" t="s" s="1">
         <v>5736</v>
       </c>
-      <c r="AA393" t="s" s="1">
+      <c r="Y394" t="s" s="1">
         <v>5737</v>
       </c>
-      <c r="AB393" t="s" s="1">
+      <c r="Z394" t="s" s="1">
         <v>5738</v>
       </c>
-      <c r="AC393" t="s" s="1">
+      <c r="AA394" t="s" s="1">
         <v>5739</v>
       </c>
-      <c r="AD393" t="s" s="1">
+      <c r="AB394" t="s" s="1">
         <v>5740</v>
       </c>
-      <c r="AE393" t="s" s="1">
+      <c r="AC394" t="s" s="1">
         <v>5741</v>
       </c>
-      <c r="AF393" t="s" s="1">
+      <c r="AD394" t="s" s="1">
         <v>5742</v>
+      </c>
+      <c r="AE394" t="s" s="1">
+        <v>5743</v>
+      </c>
+      <c r="AF394" t="s" s="1">
+        <v>5744</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AG393"/>
+  <autoFilter ref="A1:AG394"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId3"/>

--- a/app/translations.xlsx
+++ b/app/translations.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Translations" r:id="rId3" sheetId="1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">Translations!$A$1:$AG$394</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="true">Translations!$A$1:$AG$396</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -15380,7 +15380,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A369" authorId="0">
+    <comment ref="A371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15392,7 +15392,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B369" authorId="0">
+    <comment ref="B371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15404,7 +15404,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C369" authorId="0">
+    <comment ref="C371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15416,7 +15416,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D369" authorId="0">
+    <comment ref="D371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15428,7 +15428,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E369" authorId="0">
+    <comment ref="E371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15440,7 +15440,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F369" authorId="0">
+    <comment ref="F371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15452,7 +15452,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G369" authorId="0">
+    <comment ref="G371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15464,7 +15464,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H369" authorId="0">
+    <comment ref="H371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15476,7 +15476,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I369" authorId="0">
+    <comment ref="I371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15488,7 +15488,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J369" authorId="0">
+    <comment ref="J371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15500,7 +15500,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K369" authorId="0">
+    <comment ref="K371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15512,7 +15512,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L369" authorId="0">
+    <comment ref="L371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15524,7 +15524,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M369" authorId="0">
+    <comment ref="M371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15536,7 +15536,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N369" authorId="0">
+    <comment ref="N371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15548,7 +15548,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O369" authorId="0">
+    <comment ref="O371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15560,7 +15560,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P369" authorId="0">
+    <comment ref="P371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15572,7 +15572,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q369" authorId="0">
+    <comment ref="Q371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15584,7 +15584,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R369" authorId="0">
+    <comment ref="R371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15596,7 +15596,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S369" authorId="0">
+    <comment ref="S371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15608,7 +15608,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T369" authorId="0">
+    <comment ref="T371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15620,7 +15620,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U369" authorId="0">
+    <comment ref="U371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15632,7 +15632,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V369" authorId="0">
+    <comment ref="V371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15644,7 +15644,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W369" authorId="0">
+    <comment ref="W371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15656,7 +15656,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X369" authorId="0">
+    <comment ref="X371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15668,7 +15668,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y369" authorId="0">
+    <comment ref="Y371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15680,7 +15680,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z369" authorId="0">
+    <comment ref="Z371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15692,7 +15692,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA369" authorId="0">
+    <comment ref="AA371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15704,7 +15704,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB369" authorId="0">
+    <comment ref="AB371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15716,7 +15716,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC369" authorId="0">
+    <comment ref="AC371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15728,7 +15728,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD369" authorId="0">
+    <comment ref="AD371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15740,7 +15740,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE369" authorId="0">
+    <comment ref="AE371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15752,7 +15752,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF369" authorId="0">
+    <comment ref="AF371" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15764,7 +15764,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A370" authorId="0">
+    <comment ref="A372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15776,7 +15776,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B370" authorId="0">
+    <comment ref="B372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15788,7 +15788,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C370" authorId="0">
+    <comment ref="C372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15800,7 +15800,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D370" authorId="0">
+    <comment ref="D372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15812,7 +15812,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E370" authorId="0">
+    <comment ref="E372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15824,7 +15824,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F370" authorId="0">
+    <comment ref="F372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15836,7 +15836,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G370" authorId="0">
+    <comment ref="G372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15848,7 +15848,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H370" authorId="0">
+    <comment ref="H372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15860,7 +15860,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I370" authorId="0">
+    <comment ref="I372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15872,7 +15872,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J370" authorId="0">
+    <comment ref="J372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15884,7 +15884,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K370" authorId="0">
+    <comment ref="K372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15896,7 +15896,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L370" authorId="0">
+    <comment ref="L372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15908,7 +15908,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M370" authorId="0">
+    <comment ref="M372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15920,7 +15920,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N370" authorId="0">
+    <comment ref="N372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15932,7 +15932,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O370" authorId="0">
+    <comment ref="O372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15944,7 +15944,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P370" authorId="0">
+    <comment ref="P372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15956,7 +15956,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q370" authorId="0">
+    <comment ref="Q372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15968,7 +15968,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R370" authorId="0">
+    <comment ref="R372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15980,7 +15980,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S370" authorId="0">
+    <comment ref="S372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -15992,7 +15992,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T370" authorId="0">
+    <comment ref="T372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16004,7 +16004,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U370" authorId="0">
+    <comment ref="U372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16016,7 +16016,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V370" authorId="0">
+    <comment ref="V372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16028,7 +16028,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W370" authorId="0">
+    <comment ref="W372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16040,7 +16040,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X370" authorId="0">
+    <comment ref="X372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16052,7 +16052,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y370" authorId="0">
+    <comment ref="Y372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16064,7 +16064,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z370" authorId="0">
+    <comment ref="Z372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16076,7 +16076,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA370" authorId="0">
+    <comment ref="AA372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16088,7 +16088,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB370" authorId="0">
+    <comment ref="AB372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16100,7 +16100,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC370" authorId="0">
+    <comment ref="AC372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16112,7 +16112,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD370" authorId="0">
+    <comment ref="AD372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16124,7 +16124,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE370" authorId="0">
+    <comment ref="AE372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16136,7 +16136,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF370" authorId="0">
+    <comment ref="AF372" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16148,7 +16148,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A373" authorId="0">
+    <comment ref="A375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16160,7 +16160,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B373" authorId="0">
+    <comment ref="B375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16172,7 +16172,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C373" authorId="0">
+    <comment ref="C375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16184,7 +16184,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D373" authorId="0">
+    <comment ref="D375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16196,7 +16196,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E373" authorId="0">
+    <comment ref="E375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16208,7 +16208,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F373" authorId="0">
+    <comment ref="F375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16220,7 +16220,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G373" authorId="0">
+    <comment ref="G375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16232,7 +16232,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H373" authorId="0">
+    <comment ref="H375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16244,7 +16244,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I373" authorId="0">
+    <comment ref="I375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16256,7 +16256,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J373" authorId="0">
+    <comment ref="J375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16268,7 +16268,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K373" authorId="0">
+    <comment ref="K375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16280,7 +16280,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L373" authorId="0">
+    <comment ref="L375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16292,7 +16292,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M373" authorId="0">
+    <comment ref="M375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16304,7 +16304,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N373" authorId="0">
+    <comment ref="N375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16316,7 +16316,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O373" authorId="0">
+    <comment ref="O375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16328,7 +16328,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P373" authorId="0">
+    <comment ref="P375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16340,7 +16340,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q373" authorId="0">
+    <comment ref="Q375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16352,7 +16352,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R373" authorId="0">
+    <comment ref="R375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16364,7 +16364,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S373" authorId="0">
+    <comment ref="S375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16376,7 +16376,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T373" authorId="0">
+    <comment ref="T375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16388,7 +16388,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U373" authorId="0">
+    <comment ref="U375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16400,7 +16400,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V373" authorId="0">
+    <comment ref="V375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16412,7 +16412,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W373" authorId="0">
+    <comment ref="W375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16424,7 +16424,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X373" authorId="0">
+    <comment ref="X375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16436,7 +16436,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y373" authorId="0">
+    <comment ref="Y375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16448,7 +16448,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z373" authorId="0">
+    <comment ref="Z375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16460,7 +16460,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA373" authorId="0">
+    <comment ref="AA375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16472,7 +16472,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB373" authorId="0">
+    <comment ref="AB375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16484,7 +16484,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC373" authorId="0">
+    <comment ref="AC375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16496,7 +16496,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD373" authorId="0">
+    <comment ref="AD375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16508,7 +16508,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE373" authorId="0">
+    <comment ref="AE375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16520,7 +16520,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF373" authorId="0">
+    <comment ref="AF375" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16532,7 +16532,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A374" authorId="0">
+    <comment ref="A376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16544,7 +16544,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B374" authorId="0">
+    <comment ref="B376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16556,7 +16556,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C374" authorId="0">
+    <comment ref="C376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16568,7 +16568,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D374" authorId="0">
+    <comment ref="D376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16580,7 +16580,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E374" authorId="0">
+    <comment ref="E376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16592,7 +16592,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F374" authorId="0">
+    <comment ref="F376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16604,7 +16604,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G374" authorId="0">
+    <comment ref="G376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16616,7 +16616,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H374" authorId="0">
+    <comment ref="H376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16628,7 +16628,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I374" authorId="0">
+    <comment ref="I376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16640,7 +16640,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J374" authorId="0">
+    <comment ref="J376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16652,7 +16652,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K374" authorId="0">
+    <comment ref="K376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16664,7 +16664,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L374" authorId="0">
+    <comment ref="L376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16676,7 +16676,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M374" authorId="0">
+    <comment ref="M376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16688,7 +16688,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N374" authorId="0">
+    <comment ref="N376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16700,7 +16700,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O374" authorId="0">
+    <comment ref="O376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16712,7 +16712,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P374" authorId="0">
+    <comment ref="P376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16724,7 +16724,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q374" authorId="0">
+    <comment ref="Q376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16736,7 +16736,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="R374" authorId="0">
+    <comment ref="R376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16748,7 +16748,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S374" authorId="0">
+    <comment ref="S376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16760,7 +16760,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="T374" authorId="0">
+    <comment ref="T376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16772,7 +16772,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U374" authorId="0">
+    <comment ref="U376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16784,7 +16784,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V374" authorId="0">
+    <comment ref="V376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16796,7 +16796,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W374" authorId="0">
+    <comment ref="W376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16808,7 +16808,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X374" authorId="0">
+    <comment ref="X376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16820,7 +16820,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y374" authorId="0">
+    <comment ref="Y376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16832,7 +16832,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Z374" authorId="0">
+    <comment ref="Z376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16844,7 +16844,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AA374" authorId="0">
+    <comment ref="AA376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16856,7 +16856,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB374" authorId="0">
+    <comment ref="AB376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16868,7 +16868,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC374" authorId="0">
+    <comment ref="AC376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16880,7 +16880,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD374" authorId="0">
+    <comment ref="AD376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16892,7 +16892,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE374" authorId="0">
+    <comment ref="AE376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16904,7 +16904,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF374" authorId="0">
+    <comment ref="AF376" authorId="0">
       <text>
         <r>
           <rPr>
@@ -16943,7 +16943,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12608" uniqueCount="5764">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12672" uniqueCount="5768">
   <si>
     <t>Key</t>
   </si>
@@ -32904,7 +32904,7 @@
     <t>text_size</t>
   </si>
   <si>
-    <t>Text size</t>
+    <t>Text size (Note Editor)</t>
   </si>
   <si>
     <t>Velikost písma</t>
@@ -32959,6 +32959,18 @@
   </si>
   <si>
     <t>文字大小</t>
+  </si>
+  <si>
+    <t>text_size_overview</t>
+  </si>
+  <si>
+    <t>Text size (Overview)</t>
+  </si>
+  <si>
+    <t>text_size_preview</t>
+  </si>
+  <si>
+    <t>Lorem ipsum dolor sit</t>
   </si>
   <si>
     <t>theme</t>
@@ -40192,7 +40204,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AF394"/>
+  <dimension ref="A1:AF396"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="50"/>
   <cols>
     <col min="1" max="1" width="40.0" customWidth="true"/>
@@ -75783,124 +75795,124 @@
       <c r="C364" t="s" s="1">
         <v>5283</v>
       </c>
-      <c r="D364" t="s" s="1">
-        <v>5284</v>
-      </c>
-      <c r="E364" t="s" s="1">
-        <v>5285</v>
-      </c>
-      <c r="F364" t="s" s="1">
-        <v>5284</v>
-      </c>
-      <c r="G364" t="s" s="1">
-        <v>5286</v>
-      </c>
-      <c r="H364" t="s" s="1">
-        <v>5287</v>
-      </c>
-      <c r="I364" t="s" s="1">
-        <v>5284</v>
-      </c>
-      <c r="J364" t="s" s="1">
-        <v>5288</v>
-      </c>
-      <c r="K364" t="s" s="1">
-        <v>5285</v>
-      </c>
-      <c r="L364" t="s" s="1">
-        <v>5284</v>
-      </c>
-      <c r="M364" t="s" s="1">
-        <v>5284</v>
-      </c>
-      <c r="N364" t="s" s="1">
-        <v>5289</v>
-      </c>
-      <c r="O364" t="s" s="1">
-        <v>5290</v>
-      </c>
-      <c r="P364" t="s" s="1">
-        <v>5284</v>
-      </c>
-      <c r="Q364" t="s" s="1">
-        <v>5291</v>
-      </c>
-      <c r="R364" t="s" s="1">
-        <v>5284</v>
-      </c>
-      <c r="S364" t="s" s="1">
-        <v>5292</v>
-      </c>
-      <c r="T364" t="s" s="1">
-        <v>5284</v>
-      </c>
-      <c r="U364" t="s" s="1">
-        <v>5284</v>
-      </c>
-      <c r="V364" t="s" s="1">
-        <v>5284</v>
-      </c>
-      <c r="W364" t="s" s="1">
-        <v>5293</v>
-      </c>
-      <c r="X364" t="s" s="1">
-        <v>5285</v>
-      </c>
-      <c r="Y364" t="s" s="1">
-        <v>5284</v>
-      </c>
-      <c r="Z364" t="s" s="1">
-        <v>5284</v>
-      </c>
-      <c r="AA364" t="s" s="1">
-        <v>5284</v>
-      </c>
-      <c r="AB364" t="s" s="1">
-        <v>5284</v>
-      </c>
-      <c r="AC364" t="s" s="1">
-        <v>5293</v>
-      </c>
-      <c r="AD364" t="s" s="1">
-        <v>5294</v>
-      </c>
-      <c r="AE364" t="s" s="1">
-        <v>5295</v>
-      </c>
-      <c r="AF364" t="s" s="1">
-        <v>5296</v>
+      <c r="D364" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E364" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="F364" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="G364" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="H364" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="I364" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="J364" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="K364" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="L364" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M364" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="N364" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="O364" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="P364" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Q364" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="R364" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="S364" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="T364" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="U364" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="V364" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="W364" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="X364" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Y364" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Z364" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AA364" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AB364" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AC364" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AD364" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AE364" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AF364" t="s" s="2">
+        <v>63</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="s" s="1">
-        <v>5297</v>
+        <v>5284</v>
       </c>
       <c r="B365" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C365" t="s" s="1">
-        <v>5298</v>
+        <v>5285</v>
       </c>
       <c r="D365" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="E365" t="s" s="1">
-        <v>5299</v>
+      <c r="E365" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="F365" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="G365" t="s" s="1">
-        <v>5300</v>
+      <c r="G365" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="H365" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="I365" t="s" s="1">
-        <v>5301</v>
-      </c>
-      <c r="J365" t="s" s="1">
-        <v>5302</v>
+      <c r="I365" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="J365" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="K365" t="s" s="2">
         <v>63</v>
@@ -75926,20 +75938,20 @@
       <c r="R365" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="S365" t="s" s="1">
-        <v>5303</v>
-      </c>
-      <c r="T365" t="s" s="1">
-        <v>5304</v>
+      <c r="S365" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="T365" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="U365" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="V365" t="s" s="1">
-        <v>5305</v>
-      </c>
-      <c r="W365" t="s" s="1">
-        <v>5306</v>
+      <c r="V365" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="W365" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="X365" t="s" s="2">
         <v>63</v>
@@ -75956,147 +75968,147 @@
       <c r="AB365" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="AC365" t="s" s="1">
-        <v>5307</v>
+      <c r="AC365" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="AD365" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="AE365" t="s" s="1">
-        <v>5308</v>
-      </c>
-      <c r="AF365" t="s" s="1">
-        <v>5309</v>
+      <c r="AE365" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AF365" t="s" s="2">
+        <v>63</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="s" s="1">
-        <v>5310</v>
+        <v>5286</v>
       </c>
       <c r="B366" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C366" t="s" s="1">
-        <v>5311</v>
+        <v>5287</v>
       </c>
       <c r="D366" t="s" s="1">
-        <v>5312</v>
+        <v>5288</v>
       </c>
       <c r="E366" t="s" s="1">
-        <v>5313</v>
+        <v>5289</v>
       </c>
       <c r="F366" t="s" s="1">
-        <v>5314</v>
+        <v>5288</v>
       </c>
       <c r="G366" t="s" s="1">
-        <v>5314</v>
+        <v>5290</v>
       </c>
       <c r="H366" t="s" s="1">
-        <v>5315</v>
+        <v>5291</v>
       </c>
       <c r="I366" t="s" s="1">
-        <v>5316</v>
+        <v>5288</v>
       </c>
       <c r="J366" t="s" s="1">
-        <v>5317</v>
+        <v>5292</v>
       </c>
       <c r="K366" t="s" s="1">
-        <v>5318</v>
+        <v>5289</v>
       </c>
       <c r="L366" t="s" s="1">
-        <v>5319</v>
+        <v>5288</v>
       </c>
       <c r="M366" t="s" s="1">
-        <v>5320</v>
+        <v>5288</v>
       </c>
       <c r="N366" t="s" s="1">
-        <v>5321</v>
+        <v>5293</v>
       </c>
       <c r="O366" t="s" s="1">
-        <v>5322</v>
+        <v>5294</v>
       </c>
       <c r="P366" t="s" s="1">
-        <v>5323</v>
+        <v>5288</v>
       </c>
       <c r="Q366" t="s" s="1">
-        <v>5314</v>
+        <v>5295</v>
       </c>
       <c r="R366" t="s" s="1">
-        <v>5323</v>
+        <v>5288</v>
       </c>
       <c r="S366" t="s" s="1">
-        <v>5324</v>
+        <v>5296</v>
       </c>
       <c r="T366" t="s" s="1">
-        <v>5316</v>
+        <v>5288</v>
       </c>
       <c r="U366" t="s" s="1">
-        <v>5316</v>
+        <v>5288</v>
       </c>
       <c r="V366" t="s" s="1">
-        <v>5325</v>
+        <v>5288</v>
       </c>
       <c r="W366" t="s" s="1">
-        <v>5326</v>
+        <v>5297</v>
       </c>
       <c r="X366" t="s" s="1">
-        <v>5327</v>
+        <v>5289</v>
       </c>
       <c r="Y366" t="s" s="1">
-        <v>5328</v>
+        <v>5288</v>
       </c>
       <c r="Z366" t="s" s="1">
-        <v>5314</v>
+        <v>5288</v>
       </c>
       <c r="AA366" t="s" s="1">
-        <v>5329</v>
+        <v>5288</v>
       </c>
       <c r="AB366" t="s" s="1">
-        <v>5330</v>
+        <v>5288</v>
       </c>
       <c r="AC366" t="s" s="1">
-        <v>5331</v>
+        <v>5297</v>
       </c>
       <c r="AD366" t="s" s="1">
-        <v>5332</v>
+        <v>5298</v>
       </c>
       <c r="AE366" t="s" s="1">
-        <v>5333</v>
+        <v>5299</v>
       </c>
       <c r="AF366" t="s" s="1">
-        <v>5334</v>
+        <v>5300</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="s" s="1">
-        <v>5335</v>
+        <v>5301</v>
       </c>
       <c r="B367" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C367" t="s" s="1">
-        <v>5336</v>
+        <v>5302</v>
       </c>
       <c r="D367" t="s" s="2">
         <v>63</v>
       </c>
       <c r="E367" t="s" s="1">
-        <v>5337</v>
+        <v>5303</v>
       </c>
       <c r="F367" t="s" s="2">
         <v>63</v>
       </c>
       <c r="G367" t="s" s="1">
-        <v>5338</v>
+        <v>5304</v>
       </c>
       <c r="H367" t="s" s="2">
         <v>63</v>
       </c>
       <c r="I367" t="s" s="1">
-        <v>5339</v>
+        <v>5305</v>
       </c>
       <c r="J367" t="s" s="1">
-        <v>5340</v>
+        <v>5306</v>
       </c>
       <c r="K367" t="s" s="2">
         <v>63</v>
@@ -76104,8 +76116,8 @@
       <c r="L367" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="M367" t="s" s="1">
-        <v>5341</v>
+      <c r="M367" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="N367" t="s" s="2">
         <v>63</v>
@@ -76116,26 +76128,26 @@
       <c r="P367" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="Q367" t="s" s="1">
-        <v>5342</v>
+      <c r="Q367" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="R367" t="s" s="2">
         <v>63</v>
       </c>
       <c r="S367" t="s" s="1">
-        <v>5343</v>
+        <v>5307</v>
       </c>
       <c r="T367" t="s" s="1">
-        <v>5344</v>
+        <v>5308</v>
       </c>
       <c r="U367" t="s" s="2">
         <v>63</v>
       </c>
       <c r="V367" t="s" s="1">
-        <v>5345</v>
+        <v>5309</v>
       </c>
       <c r="W367" t="s" s="1">
-        <v>5346</v>
+        <v>5310</v>
       </c>
       <c r="X367" t="s" s="2">
         <v>63</v>
@@ -76153,930 +76165,930 @@
         <v>63</v>
       </c>
       <c r="AC367" t="s" s="1">
-        <v>5347</v>
+        <v>5311</v>
       </c>
       <c r="AD367" t="s" s="2">
         <v>63</v>
       </c>
       <c r="AE367" t="s" s="1">
-        <v>5348</v>
+        <v>5312</v>
       </c>
       <c r="AF367" t="s" s="1">
-        <v>5349</v>
+        <v>5313</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="s" s="1">
-        <v>5350</v>
+        <v>5314</v>
       </c>
       <c r="B368" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C368" t="s" s="1">
-        <v>5351</v>
+        <v>5315</v>
       </c>
       <c r="D368" t="s" s="1">
-        <v>5352</v>
+        <v>5316</v>
       </c>
       <c r="E368" t="s" s="1">
-        <v>5353</v>
+        <v>5317</v>
       </c>
       <c r="F368" t="s" s="1">
-        <v>5354</v>
+        <v>5318</v>
       </c>
       <c r="G368" t="s" s="1">
-        <v>5355</v>
+        <v>5318</v>
       </c>
       <c r="H368" t="s" s="1">
-        <v>5356</v>
+        <v>5319</v>
       </c>
       <c r="I368" t="s" s="1">
-        <v>5357</v>
+        <v>5320</v>
       </c>
       <c r="J368" t="s" s="1">
-        <v>4600</v>
+        <v>5321</v>
       </c>
       <c r="K368" t="s" s="1">
-        <v>5358</v>
+        <v>5322</v>
       </c>
       <c r="L368" t="s" s="1">
-        <v>5359</v>
+        <v>5323</v>
       </c>
       <c r="M368" t="s" s="1">
-        <v>5360</v>
+        <v>5324</v>
       </c>
       <c r="N368" t="s" s="1">
-        <v>5361</v>
+        <v>5325</v>
       </c>
       <c r="O368" t="s" s="1">
-        <v>5362</v>
+        <v>5326</v>
       </c>
       <c r="P368" t="s" s="1">
-        <v>5363</v>
+        <v>5327</v>
       </c>
       <c r="Q368" t="s" s="1">
-        <v>5364</v>
+        <v>5318</v>
       </c>
       <c r="R368" t="s" s="1">
-        <v>5365</v>
+        <v>5327</v>
       </c>
       <c r="S368" t="s" s="1">
-        <v>5366</v>
+        <v>5328</v>
       </c>
       <c r="T368" t="s" s="1">
-        <v>5367</v>
+        <v>5320</v>
       </c>
       <c r="U368" t="s" s="1">
-        <v>5367</v>
+        <v>5320</v>
       </c>
       <c r="V368" t="s" s="1">
-        <v>5368</v>
+        <v>5329</v>
       </c>
       <c r="W368" t="s" s="1">
-        <v>5369</v>
+        <v>5330</v>
       </c>
       <c r="X368" t="s" s="1">
-        <v>5370</v>
+        <v>5331</v>
       </c>
       <c r="Y368" t="s" s="1">
-        <v>5371</v>
+        <v>5332</v>
       </c>
       <c r="Z368" t="s" s="1">
-        <v>5372</v>
+        <v>5318</v>
       </c>
       <c r="AA368" t="s" s="1">
-        <v>5373</v>
+        <v>5333</v>
       </c>
       <c r="AB368" t="s" s="1">
-        <v>5374</v>
+        <v>5334</v>
       </c>
       <c r="AC368" t="s" s="1">
-        <v>5375</v>
+        <v>5335</v>
       </c>
       <c r="AD368" t="s" s="1">
-        <v>5376</v>
+        <v>5336</v>
       </c>
       <c r="AE368" t="s" s="1">
-        <v>5377</v>
+        <v>5337</v>
       </c>
       <c r="AF368" t="s" s="1">
-        <v>5378</v>
+        <v>5338</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="s" s="1">
-        <v>5379</v>
+        <v>5339</v>
       </c>
       <c r="B369" t="s" s="1">
         <v>33</v>
       </c>
-      <c r="C369" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="D369" t="s" s="3">
+      <c r="C369" t="s" s="1">
+        <v>5340</v>
+      </c>
+      <c r="D369" t="s" s="2">
         <v>63</v>
       </c>
       <c r="E369" t="s" s="1">
-        <v>4621</v>
-      </c>
-      <c r="F369" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="G369" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="H369" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="I369" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="J369" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="K369" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="L369" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="M369" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="N369" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="O369" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="P369" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="Q369" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="R369" t="s" s="3">
+        <v>5341</v>
+      </c>
+      <c r="F369" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="G369" t="s" s="1">
+        <v>5342</v>
+      </c>
+      <c r="H369" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="I369" t="s" s="1">
+        <v>5343</v>
+      </c>
+      <c r="J369" t="s" s="1">
+        <v>5344</v>
+      </c>
+      <c r="K369" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="L369" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M369" t="s" s="1">
+        <v>5345</v>
+      </c>
+      <c r="N369" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="O369" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="P369" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Q369" t="s" s="1">
+        <v>5346</v>
+      </c>
+      <c r="R369" t="s" s="2">
         <v>63</v>
       </c>
       <c r="S369" t="s" s="1">
-        <v>5380</v>
-      </c>
-      <c r="T369" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="U369" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="V369" t="s" s="3">
-        <v>63</v>
+        <v>5347</v>
+      </c>
+      <c r="T369" t="s" s="1">
+        <v>5348</v>
+      </c>
+      <c r="U369" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="V369" t="s" s="1">
+        <v>5349</v>
       </c>
       <c r="W369" t="s" s="1">
-        <v>5381</v>
-      </c>
-      <c r="X369" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="Y369" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="Z369" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AA369" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AB369" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AC369" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AD369" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AE369" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AF369" t="s" s="3">
-        <v>63</v>
+        <v>5350</v>
+      </c>
+      <c r="X369" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Y369" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Z369" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AA369" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AB369" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AC369" t="s" s="1">
+        <v>5351</v>
+      </c>
+      <c r="AD369" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AE369" t="s" s="1">
+        <v>5352</v>
+      </c>
+      <c r="AF369" t="s" s="1">
+        <v>5353</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="s" s="1">
-        <v>5382</v>
+        <v>5354</v>
       </c>
       <c r="B370" t="s" s="1">
         <v>33</v>
       </c>
-      <c r="C370" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="D370" t="s" s="3">
-        <v>63</v>
+      <c r="C370" t="s" s="1">
+        <v>5355</v>
+      </c>
+      <c r="D370" t="s" s="1">
+        <v>5356</v>
       </c>
       <c r="E370" t="s" s="1">
-        <v>4625</v>
-      </c>
-      <c r="F370" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="G370" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="H370" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="I370" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="J370" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="K370" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="L370" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="M370" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="N370" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="O370" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="P370" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="Q370" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="R370" t="s" s="3">
-        <v>63</v>
+        <v>5357</v>
+      </c>
+      <c r="F370" t="s" s="1">
+        <v>5358</v>
+      </c>
+      <c r="G370" t="s" s="1">
+        <v>5359</v>
+      </c>
+      <c r="H370" t="s" s="1">
+        <v>5360</v>
+      </c>
+      <c r="I370" t="s" s="1">
+        <v>5361</v>
+      </c>
+      <c r="J370" t="s" s="1">
+        <v>4600</v>
+      </c>
+      <c r="K370" t="s" s="1">
+        <v>5362</v>
+      </c>
+      <c r="L370" t="s" s="1">
+        <v>5363</v>
+      </c>
+      <c r="M370" t="s" s="1">
+        <v>5364</v>
+      </c>
+      <c r="N370" t="s" s="1">
+        <v>5365</v>
+      </c>
+      <c r="O370" t="s" s="1">
+        <v>5366</v>
+      </c>
+      <c r="P370" t="s" s="1">
+        <v>5367</v>
+      </c>
+      <c r="Q370" t="s" s="1">
+        <v>5368</v>
+      </c>
+      <c r="R370" t="s" s="1">
+        <v>5369</v>
       </c>
       <c r="S370" t="s" s="1">
-        <v>5383</v>
-      </c>
-      <c r="T370" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="U370" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="V370" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="W370" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="X370" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="Y370" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="Z370" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AA370" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AB370" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AC370" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AD370" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AE370" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AF370" t="s" s="3">
-        <v>63</v>
+        <v>5370</v>
+      </c>
+      <c r="T370" t="s" s="1">
+        <v>5371</v>
+      </c>
+      <c r="U370" t="s" s="1">
+        <v>5371</v>
+      </c>
+      <c r="V370" t="s" s="1">
+        <v>5372</v>
+      </c>
+      <c r="W370" t="s" s="1">
+        <v>5373</v>
+      </c>
+      <c r="X370" t="s" s="1">
+        <v>5374</v>
+      </c>
+      <c r="Y370" t="s" s="1">
+        <v>5375</v>
+      </c>
+      <c r="Z370" t="s" s="1">
+        <v>5376</v>
+      </c>
+      <c r="AA370" t="s" s="1">
+        <v>5377</v>
+      </c>
+      <c r="AB370" t="s" s="1">
+        <v>5378</v>
+      </c>
+      <c r="AC370" t="s" s="1">
+        <v>5379</v>
+      </c>
+      <c r="AD370" t="s" s="1">
+        <v>5380</v>
+      </c>
+      <c r="AE370" t="s" s="1">
+        <v>5381</v>
+      </c>
+      <c r="AF370" t="s" s="1">
+        <v>5382</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="s" s="1">
-        <v>5384</v>
+        <v>5383</v>
       </c>
       <c r="B371" t="s" s="1">
         <v>33</v>
       </c>
-      <c r="C371" t="s" s="1">
-        <v>5385</v>
-      </c>
-      <c r="D371" t="s" s="2">
+      <c r="C371" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="D371" t="s" s="3">
         <v>63</v>
       </c>
       <c r="E371" t="s" s="1">
         <v>4621</v>
       </c>
-      <c r="F371" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="G371" t="s" s="1">
-        <v>5386</v>
-      </c>
-      <c r="H371" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="I371" t="s" s="1">
-        <v>5387</v>
-      </c>
-      <c r="J371" t="s" s="1">
-        <v>5388</v>
-      </c>
-      <c r="K371" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="L371" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="M371" t="s" s="1">
-        <v>5389</v>
-      </c>
-      <c r="N371" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O371" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="P371" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Q371" t="s" s="1">
-        <v>5390</v>
-      </c>
-      <c r="R371" t="s" s="2">
+      <c r="F371" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="G371" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="H371" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="I371" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="J371" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="K371" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="L371" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="M371" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="N371" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="O371" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="P371" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="Q371" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="R371" t="s" s="3">
         <v>63</v>
       </c>
       <c r="S371" t="s" s="1">
-        <v>5391</v>
-      </c>
-      <c r="T371" t="s" s="1">
-        <v>5392</v>
-      </c>
-      <c r="U371" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="V371" t="s" s="1">
-        <v>5393</v>
+        <v>5384</v>
+      </c>
+      <c r="T371" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="U371" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="V371" t="s" s="3">
+        <v>63</v>
       </c>
       <c r="W371" t="s" s="1">
-        <v>5394</v>
-      </c>
-      <c r="X371" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Y371" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Z371" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AA371" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AB371" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AC371" t="s" s="1">
-        <v>5395</v>
-      </c>
-      <c r="AD371" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AE371" t="s" s="1">
-        <v>5396</v>
-      </c>
-      <c r="AF371" t="s" s="1">
-        <v>5397</v>
+        <v>5385</v>
+      </c>
+      <c r="X371" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="Y371" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="Z371" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AA371" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AB371" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AC371" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AD371" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AE371" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AF371" t="s" s="3">
+        <v>63</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="s" s="1">
-        <v>5398</v>
+        <v>5386</v>
       </c>
       <c r="B372" t="s" s="1">
         <v>33</v>
       </c>
-      <c r="C372" t="s" s="1">
-        <v>5399</v>
-      </c>
-      <c r="D372" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="E372" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="F372" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="G372" t="s" s="1">
-        <v>5400</v>
-      </c>
-      <c r="H372" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="I372" t="s" s="1">
-        <v>5401</v>
-      </c>
-      <c r="J372" t="s" s="1">
-        <v>5402</v>
-      </c>
-      <c r="K372" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="L372" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="M372" t="s" s="1">
-        <v>5403</v>
-      </c>
-      <c r="N372" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O372" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="P372" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Q372" t="s" s="1">
-        <v>5404</v>
-      </c>
-      <c r="R372" t="s" s="2">
+      <c r="C372" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="D372" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="E372" t="s" s="1">
+        <v>4625</v>
+      </c>
+      <c r="F372" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="G372" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="H372" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="I372" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="J372" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="K372" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="L372" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="M372" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="N372" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="O372" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="P372" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="Q372" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="R372" t="s" s="3">
         <v>63</v>
       </c>
       <c r="S372" t="s" s="1">
-        <v>5383</v>
-      </c>
-      <c r="T372" t="s" s="1">
-        <v>5405</v>
-      </c>
-      <c r="U372" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="V372" t="s" s="1">
-        <v>5406</v>
-      </c>
-      <c r="W372" t="s" s="1">
-        <v>5407</v>
-      </c>
-      <c r="X372" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Y372" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Z372" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AA372" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AB372" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AC372" t="s" s="1">
-        <v>5395</v>
-      </c>
-      <c r="AD372" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AE372" t="s" s="1">
-        <v>5396</v>
-      </c>
-      <c r="AF372" t="s" s="1">
-        <v>5397</v>
+        <v>5387</v>
+      </c>
+      <c r="T372" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="U372" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="V372" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="W372" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="X372" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="Y372" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="Z372" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AA372" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AB372" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AC372" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AD372" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AE372" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AF372" t="s" s="3">
+        <v>63</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="s" s="1">
-        <v>5408</v>
+        <v>5388</v>
       </c>
       <c r="B373" t="s" s="1">
         <v>33</v>
       </c>
-      <c r="C373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="D373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="E373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="F373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="G373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="H373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="I373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="J373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="K373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="L373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="M373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="N373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="O373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="P373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="Q373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="R373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="S373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="T373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="U373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="V373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="W373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="X373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="Y373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="Z373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AA373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AB373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AC373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AD373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AE373" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AF373" t="s" s="3">
-        <v>63</v>
+      <c r="C373" t="s" s="1">
+        <v>5389</v>
+      </c>
+      <c r="D373" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E373" t="s" s="1">
+        <v>4621</v>
+      </c>
+      <c r="F373" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="G373" t="s" s="1">
+        <v>5390</v>
+      </c>
+      <c r="H373" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="I373" t="s" s="1">
+        <v>5391</v>
+      </c>
+      <c r="J373" t="s" s="1">
+        <v>5392</v>
+      </c>
+      <c r="K373" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="L373" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M373" t="s" s="1">
+        <v>5393</v>
+      </c>
+      <c r="N373" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="O373" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="P373" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Q373" t="s" s="1">
+        <v>5394</v>
+      </c>
+      <c r="R373" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="S373" t="s" s="1">
+        <v>5395</v>
+      </c>
+      <c r="T373" t="s" s="1">
+        <v>5396</v>
+      </c>
+      <c r="U373" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="V373" t="s" s="1">
+        <v>5397</v>
+      </c>
+      <c r="W373" t="s" s="1">
+        <v>5398</v>
+      </c>
+      <c r="X373" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Y373" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Z373" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AA373" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AB373" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AC373" t="s" s="1">
+        <v>5399</v>
+      </c>
+      <c r="AD373" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AE373" t="s" s="1">
+        <v>5400</v>
+      </c>
+      <c r="AF373" t="s" s="1">
+        <v>5401</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="s" s="1">
-        <v>5409</v>
+        <v>5402</v>
       </c>
       <c r="B374" t="s" s="1">
         <v>33</v>
       </c>
-      <c r="C374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="D374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="E374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="F374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="G374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="H374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="I374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="J374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="K374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="L374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="M374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="N374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="O374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="P374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="Q374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="R374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="S374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="T374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="U374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="V374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="W374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="X374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="Y374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="Z374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AA374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AB374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AC374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AD374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AE374" t="s" s="3">
-        <v>63</v>
-      </c>
-      <c r="AF374" t="s" s="3">
-        <v>63</v>
+      <c r="C374" t="s" s="1">
+        <v>5403</v>
+      </c>
+      <c r="D374" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E374" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="F374" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="G374" t="s" s="1">
+        <v>5404</v>
+      </c>
+      <c r="H374" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="I374" t="s" s="1">
+        <v>5405</v>
+      </c>
+      <c r="J374" t="s" s="1">
+        <v>5406</v>
+      </c>
+      <c r="K374" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="L374" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M374" t="s" s="1">
+        <v>5407</v>
+      </c>
+      <c r="N374" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="O374" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="P374" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Q374" t="s" s="1">
+        <v>5408</v>
+      </c>
+      <c r="R374" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="S374" t="s" s="1">
+        <v>5387</v>
+      </c>
+      <c r="T374" t="s" s="1">
+        <v>5409</v>
+      </c>
+      <c r="U374" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="V374" t="s" s="1">
+        <v>5410</v>
+      </c>
+      <c r="W374" t="s" s="1">
+        <v>5411</v>
+      </c>
+      <c r="X374" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Y374" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Z374" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AA374" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AB374" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AC374" t="s" s="1">
+        <v>5399</v>
+      </c>
+      <c r="AD374" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AE374" t="s" s="1">
+        <v>5400</v>
+      </c>
+      <c r="AF374" t="s" s="1">
+        <v>5401</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="s" s="1">
-        <v>5410</v>
+        <v>5412</v>
       </c>
       <c r="B375" t="s" s="1">
         <v>33</v>
       </c>
-      <c r="C375" t="s" s="1">
-        <v>5411</v>
-      </c>
-      <c r="D375" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="E375" t="s" s="1">
-        <v>5412</v>
-      </c>
-      <c r="F375" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="G375" t="s" s="1">
-        <v>5413</v>
-      </c>
-      <c r="H375" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="I375" t="s" s="1">
-        <v>5414</v>
-      </c>
-      <c r="J375" t="s" s="1">
-        <v>5415</v>
-      </c>
-      <c r="K375" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="L375" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="M375" t="s" s="1">
-        <v>5416</v>
-      </c>
-      <c r="N375" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O375" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="P375" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Q375" t="s" s="1">
-        <v>5417</v>
-      </c>
-      <c r="R375" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="S375" t="s" s="1">
-        <v>5418</v>
-      </c>
-      <c r="T375" t="s" s="1">
-        <v>5419</v>
-      </c>
-      <c r="U375" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="V375" t="s" s="1">
-        <v>5420</v>
-      </c>
-      <c r="W375" t="s" s="1">
-        <v>5421</v>
-      </c>
-      <c r="X375" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Y375" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Z375" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AA375" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AB375" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AC375" t="s" s="1">
-        <v>5422</v>
-      </c>
-      <c r="AD375" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AE375" t="s" s="1">
-        <v>5423</v>
-      </c>
-      <c r="AF375" t="s" s="1">
-        <v>5424</v>
+      <c r="C375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="D375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="E375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="F375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="G375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="H375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="I375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="J375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="K375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="L375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="M375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="N375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="O375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="P375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="Q375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="R375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="S375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="T375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="U375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="V375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="W375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="X375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="Y375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="Z375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AA375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AB375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AC375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AD375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AE375" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AF375" t="s" s="3">
+        <v>63</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="s" s="1">
-        <v>5425</v>
+        <v>5413</v>
       </c>
       <c r="B376" t="s" s="1">
         <v>33</v>
       </c>
-      <c r="C376" t="s" s="1">
-        <v>5426</v>
-      </c>
-      <c r="D376" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="E376" t="s" s="1">
-        <v>572</v>
-      </c>
-      <c r="F376" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="G376" t="s" s="1">
-        <v>5427</v>
-      </c>
-      <c r="H376" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="I376" t="s" s="1">
-        <v>5428</v>
-      </c>
-      <c r="J376" t="s" s="1">
-        <v>871</v>
-      </c>
-      <c r="K376" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="L376" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="M376" t="s" s="1">
-        <v>874</v>
-      </c>
-      <c r="N376" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O376" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="P376" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Q376" t="s" s="1">
-        <v>5429</v>
-      </c>
-      <c r="R376" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="S376" t="s" s="1">
-        <v>577</v>
-      </c>
-      <c r="T376" t="s" s="1">
-        <v>5430</v>
-      </c>
-      <c r="U376" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="V376" t="s" s="1">
-        <v>5431</v>
-      </c>
-      <c r="W376" t="s" s="1">
-        <v>4417</v>
-      </c>
-      <c r="X376" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Y376" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Z376" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AA376" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AB376" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AC376" t="s" s="1">
-        <v>5432</v>
-      </c>
-      <c r="AD376" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AE376" t="s" s="1">
-        <v>5433</v>
-      </c>
-      <c r="AF376" t="s" s="1">
-        <v>5434</v>
+      <c r="C376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="D376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="E376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="F376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="G376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="H376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="I376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="J376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="K376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="L376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="M376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="N376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="O376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="P376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="Q376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="R376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="S376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="T376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="U376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="V376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="W376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="X376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="Y376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="Z376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AA376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AB376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AC376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AD376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AE376" t="s" s="3">
+        <v>63</v>
+      </c>
+      <c r="AF376" t="s" s="3">
+        <v>63</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="s" s="1">
-        <v>5435</v>
+        <v>5414</v>
       </c>
       <c r="B377" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C377" t="s" s="1">
-        <v>5436</v>
+        <v>5415</v>
       </c>
       <c r="D377" t="s" s="2">
         <v>63</v>
       </c>
       <c r="E377" t="s" s="1">
-        <v>5437</v>
+        <v>5416</v>
       </c>
       <c r="F377" t="s" s="2">
         <v>63</v>
       </c>
       <c r="G377" t="s" s="1">
-        <v>5438</v>
+        <v>5417</v>
       </c>
       <c r="H377" t="s" s="2">
         <v>63</v>
       </c>
       <c r="I377" t="s" s="1">
-        <v>5439</v>
+        <v>5418</v>
       </c>
       <c r="J377" t="s" s="1">
-        <v>5440</v>
+        <v>5419</v>
       </c>
       <c r="K377" t="s" s="2">
         <v>63</v>
@@ -77085,7 +77097,7 @@
         <v>63</v>
       </c>
       <c r="M377" t="s" s="1">
-        <v>5441</v>
+        <v>5420</v>
       </c>
       <c r="N377" t="s" s="2">
         <v>63</v>
@@ -77093,35 +77105,35 @@
       <c r="O377" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="P377" t="s" s="1">
-        <v>5442</v>
+      <c r="P377" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="Q377" t="s" s="1">
-        <v>5443</v>
-      </c>
-      <c r="R377" t="s" s="1">
-        <v>5444</v>
+        <v>5421</v>
+      </c>
+      <c r="R377" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="S377" t="s" s="1">
-        <v>5445</v>
+        <v>5422</v>
       </c>
       <c r="T377" t="s" s="1">
-        <v>5446</v>
+        <v>5423</v>
       </c>
       <c r="U377" t="s" s="2">
         <v>63</v>
       </c>
       <c r="V377" t="s" s="1">
-        <v>5447</v>
+        <v>5424</v>
       </c>
       <c r="W377" t="s" s="1">
-        <v>5448</v>
+        <v>5425</v>
       </c>
       <c r="X377" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="Y377" t="s" s="1">
-        <v>5449</v>
+      <c r="Y377" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="Z377" t="s" s="2">
         <v>63</v>
@@ -77133,48 +77145,48 @@
         <v>63</v>
       </c>
       <c r="AC377" t="s" s="1">
-        <v>5450</v>
-      </c>
-      <c r="AD377" t="s" s="1">
-        <v>5451</v>
+        <v>5426</v>
+      </c>
+      <c r="AD377" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="AE377" t="s" s="1">
-        <v>5452</v>
+        <v>5427</v>
       </c>
       <c r="AF377" t="s" s="1">
-        <v>5453</v>
+        <v>5428</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="s" s="1">
-        <v>5454</v>
+        <v>5429</v>
       </c>
       <c r="B378" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C378" t="s" s="1">
-        <v>5455</v>
+        <v>5430</v>
       </c>
       <c r="D378" t="s" s="2">
         <v>63</v>
       </c>
       <c r="E378" t="s" s="1">
-        <v>5456</v>
+        <v>572</v>
       </c>
       <c r="F378" t="s" s="2">
         <v>63</v>
       </c>
       <c r="G378" t="s" s="1">
-        <v>5457</v>
+        <v>5431</v>
       </c>
       <c r="H378" t="s" s="2">
         <v>63</v>
       </c>
       <c r="I378" t="s" s="1">
-        <v>5458</v>
+        <v>5432</v>
       </c>
       <c r="J378" t="s" s="1">
-        <v>5459</v>
+        <v>871</v>
       </c>
       <c r="K378" t="s" s="2">
         <v>63</v>
@@ -77183,7 +77195,7 @@
         <v>63</v>
       </c>
       <c r="M378" t="s" s="1">
-        <v>5460</v>
+        <v>874</v>
       </c>
       <c r="N378" t="s" s="2">
         <v>63</v>
@@ -77191,35 +77203,35 @@
       <c r="O378" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="P378" t="s" s="1">
-        <v>5461</v>
+      <c r="P378" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="Q378" t="s" s="1">
-        <v>5462</v>
-      </c>
-      <c r="R378" t="s" s="1">
-        <v>5463</v>
+        <v>5433</v>
+      </c>
+      <c r="R378" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="S378" t="s" s="1">
-        <v>5464</v>
+        <v>577</v>
       </c>
       <c r="T378" t="s" s="1">
-        <v>5465</v>
+        <v>5434</v>
       </c>
       <c r="U378" t="s" s="2">
         <v>63</v>
       </c>
       <c r="V378" t="s" s="1">
-        <v>5466</v>
+        <v>5435</v>
       </c>
       <c r="W378" t="s" s="1">
-        <v>5467</v>
+        <v>4417</v>
       </c>
       <c r="X378" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="Y378" t="s" s="1">
-        <v>5468</v>
+      <c r="Y378" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="Z378" t="s" s="2">
         <v>63</v>
@@ -77231,48 +77243,48 @@
         <v>63</v>
       </c>
       <c r="AC378" t="s" s="1">
-        <v>5469</v>
-      </c>
-      <c r="AD378" t="s" s="1">
-        <v>5470</v>
+        <v>5436</v>
+      </c>
+      <c r="AD378" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="AE378" t="s" s="1">
-        <v>5471</v>
+        <v>5437</v>
       </c>
       <c r="AF378" t="s" s="1">
-        <v>5472</v>
+        <v>5438</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="s" s="1">
-        <v>5473</v>
+        <v>5439</v>
       </c>
       <c r="B379" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C379" t="s" s="1">
-        <v>5474</v>
+        <v>5440</v>
       </c>
       <c r="D379" t="s" s="2">
         <v>63</v>
       </c>
       <c r="E379" t="s" s="1">
-        <v>5475</v>
+        <v>5441</v>
       </c>
       <c r="F379" t="s" s="2">
         <v>63</v>
       </c>
       <c r="G379" t="s" s="1">
-        <v>5476</v>
+        <v>5442</v>
       </c>
       <c r="H379" t="s" s="2">
         <v>63</v>
       </c>
       <c r="I379" t="s" s="1">
-        <v>5477</v>
+        <v>5443</v>
       </c>
       <c r="J379" t="s" s="1">
-        <v>5478</v>
+        <v>5444</v>
       </c>
       <c r="K379" t="s" s="2">
         <v>63</v>
@@ -77281,7 +77293,7 @@
         <v>63</v>
       </c>
       <c r="M379" t="s" s="1">
-        <v>5479</v>
+        <v>5445</v>
       </c>
       <c r="N379" t="s" s="2">
         <v>63</v>
@@ -77289,35 +77301,35 @@
       <c r="O379" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="P379" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Q379" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="R379" t="s" s="2">
-        <v>63</v>
+      <c r="P379" t="s" s="1">
+        <v>5446</v>
+      </c>
+      <c r="Q379" t="s" s="1">
+        <v>5447</v>
+      </c>
+      <c r="R379" t="s" s="1">
+        <v>5448</v>
       </c>
       <c r="S379" t="s" s="1">
-        <v>5480</v>
+        <v>5449</v>
       </c>
       <c r="T379" t="s" s="1">
-        <v>5481</v>
+        <v>5450</v>
       </c>
       <c r="U379" t="s" s="2">
         <v>63</v>
       </c>
       <c r="V379" t="s" s="1">
-        <v>5482</v>
+        <v>5451</v>
       </c>
       <c r="W379" t="s" s="1">
-        <v>5483</v>
+        <v>5452</v>
       </c>
       <c r="X379" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="Y379" t="s" s="2">
-        <v>63</v>
+      <c r="Y379" t="s" s="1">
+        <v>5453</v>
       </c>
       <c r="Z379" t="s" s="2">
         <v>63</v>
@@ -77329,48 +77341,48 @@
         <v>63</v>
       </c>
       <c r="AC379" t="s" s="1">
-        <v>5484</v>
-      </c>
-      <c r="AD379" t="s" s="2">
-        <v>63</v>
+        <v>5454</v>
+      </c>
+      <c r="AD379" t="s" s="1">
+        <v>5455</v>
       </c>
       <c r="AE379" t="s" s="1">
-        <v>5485</v>
+        <v>5456</v>
       </c>
       <c r="AF379" t="s" s="1">
-        <v>5486</v>
+        <v>5457</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="s" s="1">
-        <v>5487</v>
+        <v>5458</v>
       </c>
       <c r="B380" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C380" t="s" s="1">
-        <v>5488</v>
+        <v>5459</v>
       </c>
       <c r="D380" t="s" s="2">
         <v>63</v>
       </c>
       <c r="E380" t="s" s="1">
-        <v>5489</v>
+        <v>5460</v>
       </c>
       <c r="F380" t="s" s="2">
         <v>63</v>
       </c>
       <c r="G380" t="s" s="1">
-        <v>5490</v>
+        <v>5461</v>
       </c>
       <c r="H380" t="s" s="2">
         <v>63</v>
       </c>
       <c r="I380" t="s" s="1">
-        <v>5491</v>
+        <v>5462</v>
       </c>
       <c r="J380" t="s" s="1">
-        <v>5492</v>
+        <v>5463</v>
       </c>
       <c r="K380" t="s" s="2">
         <v>63</v>
@@ -77379,7 +77391,7 @@
         <v>63</v>
       </c>
       <c r="M380" t="s" s="1">
-        <v>5493</v>
+        <v>5464</v>
       </c>
       <c r="N380" t="s" s="2">
         <v>63</v>
@@ -77387,35 +77399,35 @@
       <c r="O380" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="P380" t="s" s="2">
-        <v>63</v>
+      <c r="P380" t="s" s="1">
+        <v>5465</v>
       </c>
       <c r="Q380" t="s" s="1">
-        <v>5494</v>
-      </c>
-      <c r="R380" t="s" s="2">
-        <v>63</v>
+        <v>5466</v>
+      </c>
+      <c r="R380" t="s" s="1">
+        <v>5467</v>
       </c>
       <c r="S380" t="s" s="1">
-        <v>5495</v>
+        <v>5468</v>
       </c>
       <c r="T380" t="s" s="1">
-        <v>5496</v>
+        <v>5469</v>
       </c>
       <c r="U380" t="s" s="2">
         <v>63</v>
       </c>
       <c r="V380" t="s" s="1">
-        <v>5497</v>
+        <v>5470</v>
       </c>
       <c r="W380" t="s" s="1">
-        <v>5498</v>
+        <v>5471</v>
       </c>
       <c r="X380" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="Y380" t="s" s="2">
-        <v>63</v>
+      <c r="Y380" t="s" s="1">
+        <v>5472</v>
       </c>
       <c r="Z380" t="s" s="2">
         <v>63</v>
@@ -77427,48 +77439,48 @@
         <v>63</v>
       </c>
       <c r="AC380" t="s" s="1">
-        <v>5499</v>
-      </c>
-      <c r="AD380" t="s" s="2">
-        <v>63</v>
+        <v>5473</v>
+      </c>
+      <c r="AD380" t="s" s="1">
+        <v>5474</v>
       </c>
       <c r="AE380" t="s" s="1">
-        <v>5500</v>
+        <v>5475</v>
       </c>
       <c r="AF380" t="s" s="1">
-        <v>5501</v>
+        <v>5476</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="s" s="1">
-        <v>5502</v>
+        <v>5477</v>
       </c>
       <c r="B381" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C381" t="s" s="1">
-        <v>5503</v>
+        <v>5478</v>
       </c>
       <c r="D381" t="s" s="2">
         <v>63</v>
       </c>
       <c r="E381" t="s" s="1">
-        <v>5504</v>
+        <v>5479</v>
       </c>
       <c r="F381" t="s" s="2">
         <v>63</v>
       </c>
       <c r="G381" t="s" s="1">
-        <v>5505</v>
+        <v>5480</v>
       </c>
       <c r="H381" t="s" s="2">
         <v>63</v>
       </c>
       <c r="I381" t="s" s="1">
-        <v>5506</v>
+        <v>5481</v>
       </c>
       <c r="J381" t="s" s="1">
-        <v>5507</v>
+        <v>5482</v>
       </c>
       <c r="K381" t="s" s="2">
         <v>63</v>
@@ -77477,7 +77489,7 @@
         <v>63</v>
       </c>
       <c r="M381" t="s" s="1">
-        <v>5508</v>
+        <v>5483</v>
       </c>
       <c r="N381" t="s" s="2">
         <v>63</v>
@@ -77495,19 +77507,19 @@
         <v>63</v>
       </c>
       <c r="S381" t="s" s="1">
-        <v>5509</v>
+        <v>5484</v>
       </c>
       <c r="T381" t="s" s="1">
-        <v>5510</v>
+        <v>5485</v>
       </c>
       <c r="U381" t="s" s="2">
         <v>63</v>
       </c>
       <c r="V381" t="s" s="1">
-        <v>5511</v>
+        <v>5486</v>
       </c>
       <c r="W381" t="s" s="1">
-        <v>5512</v>
+        <v>5487</v>
       </c>
       <c r="X381" t="s" s="2">
         <v>63</v>
@@ -77525,146 +77537,146 @@
         <v>63</v>
       </c>
       <c r="AC381" t="s" s="1">
-        <v>5513</v>
+        <v>5488</v>
       </c>
       <c r="AD381" t="s" s="2">
         <v>63</v>
       </c>
       <c r="AE381" t="s" s="1">
-        <v>5514</v>
+        <v>5489</v>
       </c>
       <c r="AF381" t="s" s="1">
-        <v>5515</v>
+        <v>5490</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="s" s="1">
-        <v>5516</v>
+        <v>5491</v>
       </c>
       <c r="B382" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C382" t="s" s="1">
-        <v>5517</v>
-      </c>
-      <c r="D382" t="s" s="1">
-        <v>5518</v>
+        <v>5492</v>
+      </c>
+      <c r="D382" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="E382" t="s" s="1">
-        <v>5519</v>
-      </c>
-      <c r="F382" t="s" s="1">
-        <v>5520</v>
+        <v>5493</v>
+      </c>
+      <c r="F382" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="G382" t="s" s="1">
-        <v>5521</v>
-      </c>
-      <c r="H382" t="s" s="1">
-        <v>5522</v>
+        <v>5494</v>
+      </c>
+      <c r="H382" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="I382" t="s" s="1">
-        <v>5523</v>
+        <v>5495</v>
       </c>
       <c r="J382" t="s" s="1">
-        <v>5524</v>
-      </c>
-      <c r="K382" t="s" s="1">
-        <v>5525</v>
-      </c>
-      <c r="L382" t="s" s="1">
-        <v>5526</v>
+        <v>5496</v>
+      </c>
+      <c r="K382" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="L382" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="M382" t="s" s="1">
-        <v>5527</v>
-      </c>
-      <c r="N382" t="s" s="1">
-        <v>5528</v>
-      </c>
-      <c r="O382" t="s" s="1">
-        <v>5529</v>
-      </c>
-      <c r="P382" t="s" s="1">
-        <v>5530</v>
+        <v>5497</v>
+      </c>
+      <c r="N382" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="O382" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="P382" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="Q382" t="s" s="1">
-        <v>5531</v>
-      </c>
-      <c r="R382" t="s" s="1">
-        <v>5532</v>
+        <v>5498</v>
+      </c>
+      <c r="R382" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="S382" t="s" s="1">
-        <v>5533</v>
+        <v>5499</v>
       </c>
       <c r="T382" t="s" s="1">
-        <v>5534</v>
-      </c>
-      <c r="U382" t="s" s="1">
-        <v>5534</v>
+        <v>5500</v>
+      </c>
+      <c r="U382" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="V382" t="s" s="1">
-        <v>5535</v>
+        <v>5501</v>
       </c>
       <c r="W382" t="s" s="1">
-        <v>5536</v>
-      </c>
-      <c r="X382" t="s" s="1">
-        <v>5537</v>
-      </c>
-      <c r="Y382" t="s" s="1">
-        <v>5538</v>
-      </c>
-      <c r="Z382" t="s" s="1">
-        <v>5539</v>
-      </c>
-      <c r="AA382" t="s" s="1">
-        <v>5540</v>
-      </c>
-      <c r="AB382" t="s" s="1">
-        <v>5541</v>
+        <v>5502</v>
+      </c>
+      <c r="X382" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Y382" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Z382" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AA382" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AB382" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="AC382" t="s" s="1">
-        <v>5542</v>
-      </c>
-      <c r="AD382" t="s" s="1">
-        <v>5543</v>
+        <v>5503</v>
+      </c>
+      <c r="AD382" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="AE382" t="s" s="1">
-        <v>5544</v>
+        <v>5504</v>
       </c>
       <c r="AF382" t="s" s="1">
-        <v>5545</v>
+        <v>5505</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="s" s="1">
-        <v>5546</v>
+        <v>5506</v>
       </c>
       <c r="B383" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C383" t="s" s="1">
-        <v>5547</v>
+        <v>5507</v>
       </c>
       <c r="D383" t="s" s="2">
         <v>63</v>
       </c>
       <c r="E383" t="s" s="1">
-        <v>5548</v>
+        <v>5508</v>
       </c>
       <c r="F383" t="s" s="2">
         <v>63</v>
       </c>
       <c r="G383" t="s" s="1">
-        <v>5549</v>
+        <v>5509</v>
       </c>
       <c r="H383" t="s" s="2">
         <v>63</v>
       </c>
       <c r="I383" t="s" s="1">
-        <v>3923</v>
+        <v>5510</v>
       </c>
       <c r="J383" t="s" s="1">
-        <v>5550</v>
+        <v>5511</v>
       </c>
       <c r="K383" t="s" s="2">
         <v>63</v>
@@ -77673,7 +77685,7 @@
         <v>63</v>
       </c>
       <c r="M383" t="s" s="1">
-        <v>3921</v>
+        <v>5512</v>
       </c>
       <c r="N383" t="s" s="2">
         <v>63</v>
@@ -77691,19 +77703,19 @@
         <v>63</v>
       </c>
       <c r="S383" t="s" s="1">
-        <v>5551</v>
+        <v>5513</v>
       </c>
       <c r="T383" t="s" s="1">
-        <v>5552</v>
+        <v>5514</v>
       </c>
       <c r="U383" t="s" s="2">
         <v>63</v>
       </c>
       <c r="V383" t="s" s="1">
-        <v>5553</v>
+        <v>5515</v>
       </c>
       <c r="W383" t="s" s="1">
-        <v>5554</v>
+        <v>5516</v>
       </c>
       <c r="X383" t="s" s="2">
         <v>63</v>
@@ -77721,289 +77733,289 @@
         <v>63</v>
       </c>
       <c r="AC383" t="s" s="1">
-        <v>5555</v>
+        <v>5517</v>
       </c>
       <c r="AD383" t="s" s="2">
         <v>63</v>
       </c>
       <c r="AE383" t="s" s="1">
-        <v>5556</v>
+        <v>5518</v>
       </c>
       <c r="AF383" t="s" s="1">
-        <v>5557</v>
+        <v>5519</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="s" s="1">
-        <v>5558</v>
+        <v>5520</v>
       </c>
       <c r="B384" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C384" t="s" s="1">
-        <v>5559</v>
-      </c>
-      <c r="D384" t="s" s="2">
-        <v>63</v>
+        <v>5521</v>
+      </c>
+      <c r="D384" t="s" s="1">
+        <v>5522</v>
       </c>
       <c r="E384" t="s" s="1">
-        <v>2295</v>
-      </c>
-      <c r="F384" t="s" s="2">
-        <v>63</v>
+        <v>5523</v>
+      </c>
+      <c r="F384" t="s" s="1">
+        <v>5524</v>
       </c>
       <c r="G384" t="s" s="1">
-        <v>5560</v>
-      </c>
-      <c r="H384" t="s" s="2">
-        <v>63</v>
+        <v>5525</v>
+      </c>
+      <c r="H384" t="s" s="1">
+        <v>5526</v>
       </c>
       <c r="I384" t="s" s="1">
-        <v>5561</v>
+        <v>5527</v>
       </c>
       <c r="J384" t="s" s="1">
-        <v>5562</v>
-      </c>
-      <c r="K384" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="L384" t="s" s="2">
-        <v>63</v>
+        <v>5528</v>
+      </c>
+      <c r="K384" t="s" s="1">
+        <v>5529</v>
+      </c>
+      <c r="L384" t="s" s="1">
+        <v>5530</v>
       </c>
       <c r="M384" t="s" s="1">
-        <v>5563</v>
-      </c>
-      <c r="N384" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O384" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="P384" t="s" s="2">
-        <v>63</v>
+        <v>5531</v>
+      </c>
+      <c r="N384" t="s" s="1">
+        <v>5532</v>
+      </c>
+      <c r="O384" t="s" s="1">
+        <v>5533</v>
+      </c>
+      <c r="P384" t="s" s="1">
+        <v>5534</v>
       </c>
       <c r="Q384" t="s" s="1">
-        <v>5564</v>
-      </c>
-      <c r="R384" t="s" s="2">
-        <v>63</v>
+        <v>5535</v>
+      </c>
+      <c r="R384" t="s" s="1">
+        <v>5536</v>
       </c>
       <c r="S384" t="s" s="1">
-        <v>5565</v>
+        <v>5537</v>
       </c>
       <c r="T384" t="s" s="1">
-        <v>5566</v>
-      </c>
-      <c r="U384" t="s" s="2">
-        <v>63</v>
+        <v>5538</v>
+      </c>
+      <c r="U384" t="s" s="1">
+        <v>5538</v>
       </c>
       <c r="V384" t="s" s="1">
-        <v>5567</v>
+        <v>5539</v>
       </c>
       <c r="W384" t="s" s="1">
-        <v>5568</v>
-      </c>
-      <c r="X384" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Y384" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Z384" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AA384" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AB384" t="s" s="2">
-        <v>63</v>
+        <v>5540</v>
+      </c>
+      <c r="X384" t="s" s="1">
+        <v>5541</v>
+      </c>
+      <c r="Y384" t="s" s="1">
+        <v>5542</v>
+      </c>
+      <c r="Z384" t="s" s="1">
+        <v>5543</v>
+      </c>
+      <c r="AA384" t="s" s="1">
+        <v>5544</v>
+      </c>
+      <c r="AB384" t="s" s="1">
+        <v>5545</v>
       </c>
       <c r="AC384" t="s" s="1">
-        <v>5569</v>
-      </c>
-      <c r="AD384" t="s" s="2">
-        <v>63</v>
+        <v>5546</v>
+      </c>
+      <c r="AD384" t="s" s="1">
+        <v>5547</v>
       </c>
       <c r="AE384" t="s" s="1">
-        <v>5570</v>
+        <v>5548</v>
       </c>
       <c r="AF384" t="s" s="1">
-        <v>5571</v>
+        <v>5549</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="s" s="1">
-        <v>5572</v>
+        <v>5550</v>
       </c>
       <c r="B385" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C385" t="s" s="1">
-        <v>5573</v>
-      </c>
-      <c r="D385" t="s" s="1">
-        <v>5574</v>
+        <v>5551</v>
+      </c>
+      <c r="D385" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="E385" t="s" s="1">
-        <v>5575</v>
-      </c>
-      <c r="F385" t="s" s="1">
-        <v>5576</v>
+        <v>5552</v>
+      </c>
+      <c r="F385" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="G385" t="s" s="1">
-        <v>5577</v>
-      </c>
-      <c r="H385" t="s" s="1">
-        <v>5578</v>
+        <v>5553</v>
+      </c>
+      <c r="H385" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="I385" t="s" s="1">
-        <v>5579</v>
+        <v>3923</v>
       </c>
       <c r="J385" t="s" s="1">
-        <v>5580</v>
-      </c>
-      <c r="K385" t="s" s="1">
-        <v>5581</v>
-      </c>
-      <c r="L385" t="s" s="1">
-        <v>5582</v>
+        <v>5554</v>
+      </c>
+      <c r="K385" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="L385" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="M385" t="s" s="1">
-        <v>5579</v>
-      </c>
-      <c r="N385" t="s" s="1">
-        <v>5583</v>
-      </c>
-      <c r="O385" t="s" s="1">
-        <v>5584</v>
-      </c>
-      <c r="P385" t="s" s="1">
-        <v>5576</v>
-      </c>
-      <c r="Q385" t="s" s="1">
-        <v>5585</v>
-      </c>
-      <c r="R385" t="s" s="1">
-        <v>5576</v>
+        <v>3921</v>
+      </c>
+      <c r="N385" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="O385" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="P385" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Q385" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="R385" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="S385" t="s" s="1">
-        <v>5586</v>
+        <v>5555</v>
       </c>
       <c r="T385" t="s" s="1">
-        <v>5587</v>
-      </c>
-      <c r="U385" t="s" s="1">
-        <v>5587</v>
+        <v>5556</v>
+      </c>
+      <c r="U385" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="V385" t="s" s="1">
-        <v>5588</v>
+        <v>5557</v>
       </c>
       <c r="W385" t="s" s="1">
-        <v>5589</v>
-      </c>
-      <c r="X385" t="s" s="1">
-        <v>5590</v>
-      </c>
-      <c r="Y385" t="s" s="1">
-        <v>5591</v>
-      </c>
-      <c r="Z385" t="s" s="1">
-        <v>5592</v>
-      </c>
-      <c r="AA385" t="s" s="1">
-        <v>5593</v>
-      </c>
-      <c r="AB385" t="s" s="1">
-        <v>5594</v>
+        <v>5558</v>
+      </c>
+      <c r="X385" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Y385" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Z385" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AA385" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AB385" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="AC385" t="s" s="1">
-        <v>5595</v>
-      </c>
-      <c r="AD385" t="s" s="1">
-        <v>5596</v>
+        <v>5559</v>
+      </c>
+      <c r="AD385" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="AE385" t="s" s="1">
-        <v>5597</v>
+        <v>5560</v>
       </c>
       <c r="AF385" t="s" s="1">
-        <v>5598</v>
+        <v>5561</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="s" s="1">
-        <v>5599</v>
+        <v>5562</v>
       </c>
       <c r="B386" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C386" t="s" s="1">
-        <v>5600</v>
+        <v>5563</v>
       </c>
       <c r="D386" t="s" s="2">
         <v>63</v>
       </c>
       <c r="E386" t="s" s="1">
-        <v>5601</v>
-      </c>
-      <c r="F386" t="s" s="1">
-        <v>5602</v>
+        <v>2295</v>
+      </c>
+      <c r="F386" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="G386" t="s" s="1">
-        <v>5603</v>
-      </c>
-      <c r="H386" t="s" s="1">
-        <v>5604</v>
+        <v>5564</v>
+      </c>
+      <c r="H386" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="I386" t="s" s="1">
-        <v>5605</v>
+        <v>5565</v>
       </c>
       <c r="J386" t="s" s="1">
-        <v>5606</v>
+        <v>5566</v>
       </c>
       <c r="K386" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="L386" t="s" s="1">
-        <v>5607</v>
+      <c r="L386" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="M386" t="s" s="1">
-        <v>5608</v>
-      </c>
-      <c r="N386" t="s" s="1">
-        <v>5609</v>
-      </c>
-      <c r="O386" t="s" s="1">
-        <v>5610</v>
-      </c>
-      <c r="P386" t="s" s="1">
-        <v>5602</v>
+        <v>5567</v>
+      </c>
+      <c r="N386" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="O386" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="P386" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="Q386" t="s" s="1">
-        <v>5611</v>
-      </c>
-      <c r="R386" t="s" s="1">
-        <v>5612</v>
+        <v>5568</v>
+      </c>
+      <c r="R386" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="S386" t="s" s="1">
-        <v>5613</v>
+        <v>5569</v>
       </c>
       <c r="T386" t="s" s="1">
-        <v>5614</v>
-      </c>
-      <c r="U386" t="s" s="1">
-        <v>5615</v>
+        <v>5570</v>
+      </c>
+      <c r="U386" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="V386" t="s" s="1">
-        <v>5616</v>
+        <v>5571</v>
       </c>
       <c r="W386" t="s" s="1">
-        <v>5617</v>
+        <v>5572</v>
       </c>
       <c r="X386" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="Y386" t="s" s="1">
-        <v>5618</v>
+      <c r="Y386" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="Z386" t="s" s="2">
         <v>63</v>
@@ -78011,248 +78023,248 @@
       <c r="AA386" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="AB386" t="s" s="1">
-        <v>5619</v>
+      <c r="AB386" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="AC386" t="s" s="1">
-        <v>5620</v>
-      </c>
-      <c r="AD386" t="s" s="1">
-        <v>5621</v>
+        <v>5573</v>
+      </c>
+      <c r="AD386" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="AE386" t="s" s="1">
-        <v>5622</v>
+        <v>5574</v>
       </c>
       <c r="AF386" t="s" s="1">
-        <v>5623</v>
+        <v>5575</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="s" s="1">
-        <v>5624</v>
+        <v>5576</v>
       </c>
       <c r="B387" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C387" t="s" s="1">
-        <v>5625</v>
-      </c>
-      <c r="D387" t="s" s="2">
-        <v>63</v>
+        <v>5577</v>
+      </c>
+      <c r="D387" t="s" s="1">
+        <v>5578</v>
       </c>
       <c r="E387" t="s" s="1">
-        <v>5626</v>
-      </c>
-      <c r="F387" t="s" s="2">
-        <v>63</v>
+        <v>5579</v>
+      </c>
+      <c r="F387" t="s" s="1">
+        <v>5580</v>
       </c>
       <c r="G387" t="s" s="1">
-        <v>5627</v>
-      </c>
-      <c r="H387" t="s" s="2">
-        <v>63</v>
+        <v>5581</v>
+      </c>
+      <c r="H387" t="s" s="1">
+        <v>5582</v>
       </c>
       <c r="I387" t="s" s="1">
-        <v>5628</v>
+        <v>5583</v>
       </c>
       <c r="J387" t="s" s="1">
-        <v>5629</v>
-      </c>
-      <c r="K387" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="L387" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="M387" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="N387" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O387" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="P387" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Q387" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="R387" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="S387" t="s" s="2">
-        <v>63</v>
+        <v>5584</v>
+      </c>
+      <c r="K387" t="s" s="1">
+        <v>5585</v>
+      </c>
+      <c r="L387" t="s" s="1">
+        <v>5586</v>
+      </c>
+      <c r="M387" t="s" s="1">
+        <v>5583</v>
+      </c>
+      <c r="N387" t="s" s="1">
+        <v>5587</v>
+      </c>
+      <c r="O387" t="s" s="1">
+        <v>5588</v>
+      </c>
+      <c r="P387" t="s" s="1">
+        <v>5580</v>
+      </c>
+      <c r="Q387" t="s" s="1">
+        <v>5589</v>
+      </c>
+      <c r="R387" t="s" s="1">
+        <v>5580</v>
+      </c>
+      <c r="S387" t="s" s="1">
+        <v>5590</v>
       </c>
       <c r="T387" t="s" s="1">
-        <v>5630</v>
-      </c>
-      <c r="U387" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="V387" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="W387" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="X387" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Y387" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Z387" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AA387" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AB387" t="s" s="2">
-        <v>63</v>
+        <v>5591</v>
+      </c>
+      <c r="U387" t="s" s="1">
+        <v>5591</v>
+      </c>
+      <c r="V387" t="s" s="1">
+        <v>5592</v>
+      </c>
+      <c r="W387" t="s" s="1">
+        <v>5593</v>
+      </c>
+      <c r="X387" t="s" s="1">
+        <v>5594</v>
+      </c>
+      <c r="Y387" t="s" s="1">
+        <v>5595</v>
+      </c>
+      <c r="Z387" t="s" s="1">
+        <v>5596</v>
+      </c>
+      <c r="AA387" t="s" s="1">
+        <v>5597</v>
+      </c>
+      <c r="AB387" t="s" s="1">
+        <v>5598</v>
       </c>
       <c r="AC387" t="s" s="1">
-        <v>5631</v>
-      </c>
-      <c r="AD387" t="s" s="2">
-        <v>63</v>
+        <v>5599</v>
+      </c>
+      <c r="AD387" t="s" s="1">
+        <v>5600</v>
       </c>
       <c r="AE387" t="s" s="1">
-        <v>5632</v>
-      </c>
-      <c r="AF387" t="s" s="2">
-        <v>63</v>
+        <v>5601</v>
+      </c>
+      <c r="AF387" t="s" s="1">
+        <v>5602</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="s" s="1">
-        <v>5633</v>
+        <v>5603</v>
       </c>
       <c r="B388" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C388" t="s" s="1">
-        <v>5634</v>
-      </c>
-      <c r="D388" t="s" s="1">
-        <v>5635</v>
+        <v>5604</v>
+      </c>
+      <c r="D388" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="E388" t="s" s="1">
-        <v>5636</v>
+        <v>5605</v>
       </c>
       <c r="F388" t="s" s="1">
-        <v>5637</v>
+        <v>5606</v>
       </c>
       <c r="G388" t="s" s="1">
-        <v>5638</v>
+        <v>5607</v>
       </c>
       <c r="H388" t="s" s="1">
-        <v>5639</v>
+        <v>5608</v>
       </c>
       <c r="I388" t="s" s="1">
-        <v>5640</v>
+        <v>5609</v>
       </c>
       <c r="J388" t="s" s="1">
-        <v>5641</v>
-      </c>
-      <c r="K388" t="s" s="1">
-        <v>5642</v>
+        <v>5610</v>
+      </c>
+      <c r="K388" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="L388" t="s" s="1">
-        <v>5643</v>
+        <v>5611</v>
       </c>
       <c r="M388" t="s" s="1">
-        <v>5644</v>
+        <v>5612</v>
       </c>
       <c r="N388" t="s" s="1">
-        <v>5645</v>
+        <v>5613</v>
       </c>
       <c r="O388" t="s" s="1">
-        <v>5646</v>
+        <v>5614</v>
       </c>
       <c r="P388" t="s" s="1">
-        <v>5647</v>
+        <v>5606</v>
       </c>
       <c r="Q388" t="s" s="1">
-        <v>5648</v>
+        <v>5615</v>
       </c>
       <c r="R388" t="s" s="1">
-        <v>5649</v>
+        <v>5616</v>
       </c>
       <c r="S388" t="s" s="1">
-        <v>5650</v>
+        <v>5617</v>
       </c>
       <c r="T388" t="s" s="1">
-        <v>5651</v>
+        <v>5618</v>
       </c>
       <c r="U388" t="s" s="1">
-        <v>5651</v>
+        <v>5619</v>
       </c>
       <c r="V388" t="s" s="1">
-        <v>5652</v>
+        <v>5620</v>
       </c>
       <c r="W388" t="s" s="1">
-        <v>5653</v>
-      </c>
-      <c r="X388" t="s" s="1">
-        <v>5654</v>
+        <v>5621</v>
+      </c>
+      <c r="X388" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="Y388" t="s" s="1">
-        <v>5655</v>
-      </c>
-      <c r="Z388" t="s" s="1">
-        <v>5656</v>
-      </c>
-      <c r="AA388" t="s" s="1">
-        <v>5657</v>
+        <v>5622</v>
+      </c>
+      <c r="Z388" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AA388" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="AB388" t="s" s="1">
-        <v>5658</v>
+        <v>5623</v>
       </c>
       <c r="AC388" t="s" s="1">
-        <v>5659</v>
+        <v>5624</v>
       </c>
       <c r="AD388" t="s" s="1">
-        <v>5660</v>
+        <v>5625</v>
       </c>
       <c r="AE388" t="s" s="1">
-        <v>5661</v>
+        <v>5626</v>
       </c>
       <c r="AF388" t="s" s="1">
-        <v>5662</v>
+        <v>5627</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="s" s="1">
-        <v>5663</v>
+        <v>5628</v>
       </c>
       <c r="B389" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C389" t="s" s="1">
-        <v>5664</v>
+        <v>5629</v>
       </c>
       <c r="D389" t="s" s="2">
         <v>63</v>
       </c>
       <c r="E389" t="s" s="1">
-        <v>5665</v>
+        <v>5630</v>
       </c>
       <c r="F389" t="s" s="2">
         <v>63</v>
       </c>
       <c r="G389" t="s" s="1">
-        <v>5666</v>
+        <v>5631</v>
       </c>
       <c r="H389" t="s" s="2">
         <v>63</v>
       </c>
       <c r="I389" t="s" s="1">
-        <v>5667</v>
+        <v>5632</v>
       </c>
       <c r="J389" t="s" s="1">
-        <v>5668</v>
+        <v>5633</v>
       </c>
       <c r="K389" t="s" s="2">
         <v>63</v>
@@ -78260,8 +78272,8 @@
       <c r="L389" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="M389" t="s" s="1">
-        <v>5669</v>
+      <c r="M389" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="N389" t="s" s="2">
         <v>63</v>
@@ -78272,26 +78284,26 @@
       <c r="P389" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="Q389" t="s" s="1">
-        <v>5670</v>
+      <c r="Q389" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="R389" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="S389" t="s" s="1">
-        <v>5671</v>
+      <c r="S389" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="T389" t="s" s="1">
-        <v>5672</v>
+        <v>5634</v>
       </c>
       <c r="U389" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="V389" t="s" s="1">
-        <v>5673</v>
-      </c>
-      <c r="W389" t="s" s="1">
-        <v>5674</v>
+      <c r="V389" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="W389" t="s" s="2">
+        <v>63</v>
       </c>
       <c r="X389" t="s" s="2">
         <v>63</v>
@@ -78309,146 +78321,146 @@
         <v>63</v>
       </c>
       <c r="AC389" t="s" s="1">
-        <v>5675</v>
+        <v>5635</v>
       </c>
       <c r="AD389" t="s" s="2">
         <v>63</v>
       </c>
       <c r="AE389" t="s" s="1">
-        <v>5676</v>
-      </c>
-      <c r="AF389" t="s" s="1">
-        <v>5677</v>
+        <v>5636</v>
+      </c>
+      <c r="AF389" t="s" s="2">
+        <v>63</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="s" s="1">
-        <v>5678</v>
+        <v>5637</v>
       </c>
       <c r="B390" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C390" t="s" s="1">
-        <v>5679</v>
-      </c>
-      <c r="D390" t="s" s="2">
-        <v>63</v>
+        <v>5638</v>
+      </c>
+      <c r="D390" t="s" s="1">
+        <v>5639</v>
       </c>
       <c r="E390" t="s" s="1">
-        <v>5680</v>
-      </c>
-      <c r="F390" t="s" s="2">
-        <v>63</v>
+        <v>5640</v>
+      </c>
+      <c r="F390" t="s" s="1">
+        <v>5641</v>
       </c>
       <c r="G390" t="s" s="1">
-        <v>5681</v>
-      </c>
-      <c r="H390" t="s" s="2">
-        <v>63</v>
+        <v>5642</v>
+      </c>
+      <c r="H390" t="s" s="1">
+        <v>5643</v>
       </c>
       <c r="I390" t="s" s="1">
-        <v>5682</v>
+        <v>5644</v>
       </c>
       <c r="J390" t="s" s="1">
-        <v>5683</v>
-      </c>
-      <c r="K390" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="L390" t="s" s="2">
-        <v>63</v>
+        <v>5645</v>
+      </c>
+      <c r="K390" t="s" s="1">
+        <v>5646</v>
+      </c>
+      <c r="L390" t="s" s="1">
+        <v>5647</v>
       </c>
       <c r="M390" t="s" s="1">
-        <v>5684</v>
-      </c>
-      <c r="N390" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O390" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="P390" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Q390" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="R390" t="s" s="2">
-        <v>63</v>
+        <v>5648</v>
+      </c>
+      <c r="N390" t="s" s="1">
+        <v>5649</v>
+      </c>
+      <c r="O390" t="s" s="1">
+        <v>5650</v>
+      </c>
+      <c r="P390" t="s" s="1">
+        <v>5651</v>
+      </c>
+      <c r="Q390" t="s" s="1">
+        <v>5652</v>
+      </c>
+      <c r="R390" t="s" s="1">
+        <v>5653</v>
       </c>
       <c r="S390" t="s" s="1">
-        <v>5685</v>
+        <v>5654</v>
       </c>
       <c r="T390" t="s" s="1">
-        <v>5682</v>
-      </c>
-      <c r="U390" t="s" s="2">
-        <v>63</v>
+        <v>5655</v>
+      </c>
+      <c r="U390" t="s" s="1">
+        <v>5655</v>
       </c>
       <c r="V390" t="s" s="1">
-        <v>5686</v>
+        <v>5656</v>
       </c>
       <c r="W390" t="s" s="1">
-        <v>5687</v>
-      </c>
-      <c r="X390" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Y390" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Z390" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AA390" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AB390" t="s" s="2">
-        <v>63</v>
+        <v>5657</v>
+      </c>
+      <c r="X390" t="s" s="1">
+        <v>5658</v>
+      </c>
+      <c r="Y390" t="s" s="1">
+        <v>5659</v>
+      </c>
+      <c r="Z390" t="s" s="1">
+        <v>5660</v>
+      </c>
+      <c r="AA390" t="s" s="1">
+        <v>5661</v>
+      </c>
+      <c r="AB390" t="s" s="1">
+        <v>5662</v>
       </c>
       <c r="AC390" t="s" s="1">
-        <v>5688</v>
-      </c>
-      <c r="AD390" t="s" s="2">
-        <v>63</v>
+        <v>5663</v>
+      </c>
+      <c r="AD390" t="s" s="1">
+        <v>5664</v>
       </c>
       <c r="AE390" t="s" s="1">
-        <v>5689</v>
+        <v>5665</v>
       </c>
       <c r="AF390" t="s" s="1">
-        <v>5690</v>
+        <v>5666</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="s" s="1">
-        <v>5691</v>
+        <v>5667</v>
       </c>
       <c r="B391" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C391" t="s" s="1">
-        <v>5692</v>
+        <v>5668</v>
       </c>
       <c r="D391" t="s" s="2">
         <v>63</v>
       </c>
       <c r="E391" t="s" s="1">
-        <v>5693</v>
+        <v>5669</v>
       </c>
       <c r="F391" t="s" s="2">
         <v>63</v>
       </c>
       <c r="G391" t="s" s="1">
-        <v>5694</v>
+        <v>5670</v>
       </c>
       <c r="H391" t="s" s="2">
         <v>63</v>
       </c>
       <c r="I391" t="s" s="1">
-        <v>5695</v>
+        <v>5671</v>
       </c>
       <c r="J391" t="s" s="1">
-        <v>5696</v>
+        <v>5672</v>
       </c>
       <c r="K391" t="s" s="2">
         <v>63</v>
@@ -78457,7 +78469,7 @@
         <v>63</v>
       </c>
       <c r="M391" t="s" s="1">
-        <v>5697</v>
+        <v>5673</v>
       </c>
       <c r="N391" t="s" s="2">
         <v>63</v>
@@ -78469,25 +78481,25 @@
         <v>63</v>
       </c>
       <c r="Q391" t="s" s="1">
-        <v>5698</v>
+        <v>5674</v>
       </c>
       <c r="R391" t="s" s="2">
         <v>63</v>
       </c>
       <c r="S391" t="s" s="1">
-        <v>5699</v>
+        <v>5675</v>
       </c>
       <c r="T391" t="s" s="1">
-        <v>5700</v>
+        <v>5676</v>
       </c>
       <c r="U391" t="s" s="2">
         <v>63</v>
       </c>
       <c r="V391" t="s" s="1">
-        <v>5701</v>
+        <v>5677</v>
       </c>
       <c r="W391" t="s" s="1">
-        <v>5702</v>
+        <v>5678</v>
       </c>
       <c r="X391" t="s" s="2">
         <v>63</v>
@@ -78505,48 +78517,48 @@
         <v>63</v>
       </c>
       <c r="AC391" t="s" s="1">
-        <v>5703</v>
+        <v>5679</v>
       </c>
       <c r="AD391" t="s" s="2">
         <v>63</v>
       </c>
       <c r="AE391" t="s" s="1">
-        <v>5704</v>
+        <v>5680</v>
       </c>
       <c r="AF391" t="s" s="1">
-        <v>5705</v>
+        <v>5681</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="s" s="1">
-        <v>5706</v>
+        <v>5682</v>
       </c>
       <c r="B392" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C392" t="s" s="1">
-        <v>5707</v>
+        <v>5683</v>
       </c>
       <c r="D392" t="s" s="2">
         <v>63</v>
       </c>
       <c r="E392" t="s" s="1">
-        <v>5708</v>
+        <v>5684</v>
       </c>
       <c r="F392" t="s" s="2">
         <v>63</v>
       </c>
       <c r="G392" t="s" s="1">
-        <v>5709</v>
+        <v>5685</v>
       </c>
       <c r="H392" t="s" s="2">
         <v>63</v>
       </c>
       <c r="I392" t="s" s="1">
-        <v>5710</v>
+        <v>5686</v>
       </c>
       <c r="J392" t="s" s="1">
-        <v>5711</v>
+        <v>5687</v>
       </c>
       <c r="K392" t="s" s="2">
         <v>63</v>
@@ -78555,7 +78567,7 @@
         <v>63</v>
       </c>
       <c r="M392" t="s" s="1">
-        <v>5712</v>
+        <v>5688</v>
       </c>
       <c r="N392" t="s" s="2">
         <v>63</v>
@@ -78573,19 +78585,19 @@
         <v>63</v>
       </c>
       <c r="S392" t="s" s="1">
-        <v>5713</v>
+        <v>5689</v>
       </c>
       <c r="T392" t="s" s="1">
-        <v>5714</v>
+        <v>5686</v>
       </c>
       <c r="U392" t="s" s="2">
         <v>63</v>
       </c>
       <c r="V392" t="s" s="1">
-        <v>5710</v>
+        <v>5690</v>
       </c>
       <c r="W392" t="s" s="1">
-        <v>5715</v>
+        <v>5691</v>
       </c>
       <c r="X392" t="s" s="2">
         <v>63</v>
@@ -78603,48 +78615,48 @@
         <v>63</v>
       </c>
       <c r="AC392" t="s" s="1">
-        <v>5716</v>
+        <v>5692</v>
       </c>
       <c r="AD392" t="s" s="2">
         <v>63</v>
       </c>
       <c r="AE392" t="s" s="1">
-        <v>5717</v>
+        <v>5693</v>
       </c>
       <c r="AF392" t="s" s="1">
-        <v>5718</v>
+        <v>5694</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="s" s="1">
-        <v>5719</v>
+        <v>5695</v>
       </c>
       <c r="B393" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C393" t="s" s="1">
-        <v>5720</v>
+        <v>5696</v>
       </c>
       <c r="D393" t="s" s="2">
         <v>63</v>
       </c>
       <c r="E393" t="s" s="1">
-        <v>5721</v>
+        <v>5697</v>
       </c>
       <c r="F393" t="s" s="2">
         <v>63</v>
       </c>
       <c r="G393" t="s" s="1">
-        <v>5722</v>
+        <v>5698</v>
       </c>
       <c r="H393" t="s" s="2">
         <v>63</v>
       </c>
       <c r="I393" t="s" s="1">
-        <v>5723</v>
+        <v>5699</v>
       </c>
       <c r="J393" t="s" s="1">
-        <v>5724</v>
+        <v>5700</v>
       </c>
       <c r="K393" t="s" s="2">
         <v>63</v>
@@ -78653,7 +78665,7 @@
         <v>63</v>
       </c>
       <c r="M393" t="s" s="1">
-        <v>5725</v>
+        <v>5701</v>
       </c>
       <c r="N393" t="s" s="2">
         <v>63</v>
@@ -78664,26 +78676,26 @@
       <c r="P393" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="Q393" t="s" s="2">
-        <v>63</v>
+      <c r="Q393" t="s" s="1">
+        <v>5702</v>
       </c>
       <c r="R393" t="s" s="2">
         <v>63</v>
       </c>
       <c r="S393" t="s" s="1">
-        <v>5726</v>
+        <v>5703</v>
       </c>
       <c r="T393" t="s" s="1">
-        <v>5727</v>
+        <v>5704</v>
       </c>
       <c r="U393" t="s" s="2">
         <v>63</v>
       </c>
       <c r="V393" t="s" s="1">
-        <v>5728</v>
+        <v>5705</v>
       </c>
       <c r="W393" t="s" s="1">
-        <v>5729</v>
+        <v>5706</v>
       </c>
       <c r="X393" t="s" s="2">
         <v>63</v>
@@ -78701,118 +78713,314 @@
         <v>63</v>
       </c>
       <c r="AC393" t="s" s="1">
-        <v>5730</v>
+        <v>5707</v>
       </c>
       <c r="AD393" t="s" s="2">
         <v>63</v>
       </c>
       <c r="AE393" t="s" s="1">
-        <v>5731</v>
+        <v>5708</v>
       </c>
       <c r="AF393" t="s" s="1">
-        <v>5732</v>
+        <v>5709</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="s" s="1">
-        <v>5733</v>
+        <v>5710</v>
       </c>
       <c r="B394" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C394" t="s" s="1">
+        <v>5711</v>
+      </c>
+      <c r="D394" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E394" t="s" s="1">
+        <v>5712</v>
+      </c>
+      <c r="F394" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="G394" t="s" s="1">
+        <v>5713</v>
+      </c>
+      <c r="H394" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="I394" t="s" s="1">
+        <v>5714</v>
+      </c>
+      <c r="J394" t="s" s="1">
+        <v>5715</v>
+      </c>
+      <c r="K394" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="L394" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M394" t="s" s="1">
+        <v>5716</v>
+      </c>
+      <c r="N394" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="O394" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="P394" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Q394" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="R394" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="S394" t="s" s="1">
+        <v>5717</v>
+      </c>
+      <c r="T394" t="s" s="1">
+        <v>5718</v>
+      </c>
+      <c r="U394" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="V394" t="s" s="1">
+        <v>5714</v>
+      </c>
+      <c r="W394" t="s" s="1">
+        <v>5719</v>
+      </c>
+      <c r="X394" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Y394" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Z394" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AA394" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AB394" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AC394" t="s" s="1">
+        <v>5720</v>
+      </c>
+      <c r="AD394" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AE394" t="s" s="1">
+        <v>5721</v>
+      </c>
+      <c r="AF394" t="s" s="1">
+        <v>5722</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="s" s="1">
+        <v>5723</v>
+      </c>
+      <c r="B395" t="s" s="1">
+        <v>33</v>
+      </c>
+      <c r="C395" t="s" s="1">
+        <v>5724</v>
+      </c>
+      <c r="D395" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E395" t="s" s="1">
+        <v>5725</v>
+      </c>
+      <c r="F395" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="G395" t="s" s="1">
+        <v>5726</v>
+      </c>
+      <c r="H395" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="I395" t="s" s="1">
+        <v>5727</v>
+      </c>
+      <c r="J395" t="s" s="1">
+        <v>5728</v>
+      </c>
+      <c r="K395" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="L395" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M395" t="s" s="1">
+        <v>5729</v>
+      </c>
+      <c r="N395" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="O395" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="P395" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Q395" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="R395" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="S395" t="s" s="1">
+        <v>5730</v>
+      </c>
+      <c r="T395" t="s" s="1">
+        <v>5731</v>
+      </c>
+      <c r="U395" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="V395" t="s" s="1">
+        <v>5732</v>
+      </c>
+      <c r="W395" t="s" s="1">
+        <v>5733</v>
+      </c>
+      <c r="X395" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Y395" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Z395" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AA395" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AB395" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AC395" t="s" s="1">
         <v>5734</v>
       </c>
-      <c r="D394" t="s" s="1">
+      <c r="AD395" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="AE395" t="s" s="1">
         <v>5735</v>
       </c>
-      <c r="E394" t="s" s="1">
+      <c r="AF395" t="s" s="1">
         <v>5736</v>
       </c>
-      <c r="F394" t="s" s="1">
+    </row>
+    <row r="396">
+      <c r="A396" t="s" s="1">
         <v>5737</v>
       </c>
-      <c r="G394" t="s" s="1">
+      <c r="B396" t="s" s="1">
+        <v>33</v>
+      </c>
+      <c r="C396" t="s" s="1">
         <v>5738</v>
       </c>
-      <c r="H394" t="s" s="1">
+      <c r="D396" t="s" s="1">
         <v>5739</v>
       </c>
-      <c r="I394" t="s" s="1">
+      <c r="E396" t="s" s="1">
         <v>5740</v>
       </c>
-      <c r="J394" t="s" s="1">
+      <c r="F396" t="s" s="1">
         <v>5741</v>
       </c>
-      <c r="K394" t="s" s="1">
+      <c r="G396" t="s" s="1">
         <v>5742</v>
       </c>
-      <c r="L394" t="s" s="1">
+      <c r="H396" t="s" s="1">
         <v>5743</v>
       </c>
-      <c r="M394" t="s" s="1">
+      <c r="I396" t="s" s="1">
         <v>5744</v>
       </c>
-      <c r="N394" t="s" s="1">
+      <c r="J396" t="s" s="1">
         <v>5745</v>
       </c>
-      <c r="O394" t="s" s="1">
+      <c r="K396" t="s" s="1">
         <v>5746</v>
       </c>
-      <c r="P394" t="s" s="1">
+      <c r="L396" t="s" s="1">
         <v>5747</v>
       </c>
-      <c r="Q394" t="s" s="1">
+      <c r="M396" t="s" s="1">
         <v>5748</v>
       </c>
-      <c r="R394" t="s" s="1">
+      <c r="N396" t="s" s="1">
         <v>5749</v>
       </c>
-      <c r="S394" t="s" s="1">
+      <c r="O396" t="s" s="1">
         <v>5750</v>
       </c>
-      <c r="T394" t="s" s="1">
+      <c r="P396" t="s" s="1">
         <v>5751</v>
       </c>
-      <c r="U394" t="s" s="1">
+      <c r="Q396" t="s" s="1">
         <v>5752</v>
       </c>
-      <c r="V394" t="s" s="1">
+      <c r="R396" t="s" s="1">
         <v>5753</v>
       </c>
-      <c r="W394" t="s" s="1">
+      <c r="S396" t="s" s="1">
         <v>5754</v>
       </c>
-      <c r="X394" t="s" s="1">
+      <c r="T396" t="s" s="1">
         <v>5755</v>
       </c>
-      <c r="Y394" t="s" s="1">
+      <c r="U396" t="s" s="1">
         <v>5756</v>
       </c>
-      <c r="Z394" t="s" s="1">
+      <c r="V396" t="s" s="1">
         <v>5757</v>
       </c>
-      <c r="AA394" t="s" s="1">
+      <c r="W396" t="s" s="1">
         <v>5758</v>
       </c>
-      <c r="AB394" t="s" s="1">
+      <c r="X396" t="s" s="1">
         <v>5759</v>
       </c>
-      <c r="AC394" t="s" s="1">
+      <c r="Y396" t="s" s="1">
         <v>5760</v>
       </c>
-      <c r="AD394" t="s" s="1">
+      <c r="Z396" t="s" s="1">
         <v>5761</v>
       </c>
-      <c r="AE394" t="s" s="1">
+      <c r="AA396" t="s" s="1">
         <v>5762</v>
       </c>
-      <c r="AF394" t="s" s="1">
+      <c r="AB396" t="s" s="1">
         <v>5763</v>
+      </c>
+      <c r="AC396" t="s" s="1">
+        <v>5764</v>
+      </c>
+      <c r="AD396" t="s" s="1">
+        <v>5765</v>
+      </c>
+      <c r="AE396" t="s" s="1">
+        <v>5766</v>
+      </c>
+      <c r="AF396" t="s" s="1">
+        <v>5767</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AG394"/>
+  <autoFilter ref="A1:AG396"/>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId3"/>

--- a/app/translations.xlsx
+++ b/app/translations.xlsx
@@ -32901,7 +32901,7 @@
     <t>預設</t>
   </si>
   <si>
-    <t>text_size</t>
+    <t>text_size_note_editor</t>
   </si>
   <si>
     <t>Text size (Note Editor)</t>

--- a/app/translations.xlsx
+++ b/app/translations.xlsx
@@ -16943,7 +16943,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12672" uniqueCount="5768">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12672" uniqueCount="5786">
   <si>
     <t>Key</t>
   </si>
@@ -32907,64 +32907,118 @@
     <t>Text size (Note Editor)</t>
   </si>
   <si>
-    <t>Velikost písma</t>
-  </si>
-  <si>
-    <t>Textgröße</t>
-  </si>
-  <si>
-    <t>Tamaño de texto</t>
-  </si>
-  <si>
-    <t>Taille du texte</t>
-  </si>
-  <si>
-    <t>Dimensione testo</t>
-  </si>
-  <si>
-    <t>စာလလုံးအရွယ်အစား</t>
-  </si>
-  <si>
-    <t>Skriftstørrelse</t>
-  </si>
-  <si>
-    <t>Tekstgrootte</t>
-  </si>
-  <si>
-    <t>Skriftstorleik</t>
-  </si>
-  <si>
-    <t>Rozmiar tekstu</t>
-  </si>
-  <si>
-    <t>Tamanho do texto</t>
-  </si>
-  <si>
-    <t>Mărimea textului</t>
-  </si>
-  <si>
-    <t>Размер текста</t>
-  </si>
-  <si>
-    <t>Velikost pisave</t>
-  </si>
-  <si>
-    <t>Розмір тексту</t>
-  </si>
-  <si>
-    <t>Cỡ chữ</t>
-  </si>
-  <si>
-    <t>文本大小</t>
-  </si>
-  <si>
-    <t>文字大小</t>
+    <t>Velikost písma (editor poznámek)</t>
+  </si>
+  <si>
+    <t>Textgröße (Notizeditor)</t>
+  </si>
+  <si>
+    <t>Tamaño de texto (editor de notas)</t>
+  </si>
+  <si>
+    <t>Taille du texte (éditeur de notes)</t>
+  </si>
+  <si>
+    <t>Dimensione testo (editor di note)</t>
+  </si>
+  <si>
+    <t>ဖောင့်အရွယ်အစား (မှတ်စုတည်းဖြတ်သူ)</t>
+  </si>
+  <si>
+    <t>Skriftstørrelse (notatredigering)</t>
+  </si>
+  <si>
+    <t>Tekstgrootte (notitie-editor)</t>
+  </si>
+  <si>
+    <t>Skriftstorleik (notereditor)</t>
+  </si>
+  <si>
+    <t>Rozmiar tekstu (edytor notatek)</t>
+  </si>
+  <si>
+    <t>Tamanho do texto (nota do editor)</t>
+  </si>
+  <si>
+    <t>Mărimea textului (editor de note)</t>
+  </si>
+  <si>
+    <t>Размер текста (в редакторе заметок)</t>
+  </si>
+  <si>
+    <t>Velikost pisave (urejevalnik zapiskov)</t>
+  </si>
+  <si>
+    <t>Розмір тексту (редактор нотаток)</t>
+  </si>
+  <si>
+    <t>Cỡ chữ (trình soạn thảo ghi chú)</t>
+  </si>
+  <si>
+    <t>文本大小（笔记编辑器）</t>
+  </si>
+  <si>
+    <t>字體大小（筆記編輯器）</t>
   </si>
   <si>
     <t>text_size_overview</t>
   </si>
   <si>
     <t>Text size (Overview)</t>
+  </si>
+  <si>
+    <t>Velikost písma (přehled)</t>
+  </si>
+  <si>
+    <t>Textgröße (Übersicht)</t>
+  </si>
+  <si>
+    <t>Tamaño de texto (descripción general)</t>
+  </si>
+  <si>
+    <t>Taille du texte (aperçu)</t>
+  </si>
+  <si>
+    <t>Dimensioni testo (panoramica)</t>
+  </si>
+  <si>
+    <t>စာသားအရွယ်အစား (ခြုံငုံသုံးသပ်ချက်)</t>
+  </si>
+  <si>
+    <t>Skriftstørrelse (oversikt)</t>
+  </si>
+  <si>
+    <t>Tekstgrootte (overzicht)</t>
+  </si>
+  <si>
+    <t>Skriftstorleik (oversikt)</t>
+  </si>
+  <si>
+    <t>Rozmiar tekstu (przegląd)</t>
+  </si>
+  <si>
+    <t>Tamanho do texto (visão geral)</t>
+  </si>
+  <si>
+    <t>Mărimea textului (prezentare generală)</t>
+  </si>
+  <si>
+    <t>Размер текста (обзор)</t>
+  </si>
+  <si>
+    <t>Velikost pisave (pregled)</t>
+  </si>
+  <si>
+    <t>Розмір тексту (огляд)</t>
+  </si>
+  <si>
+    <t>Cỡ chữ (tổng quan)</t>
+  </si>
+  <si>
+    <t>文本大小（概述）</t>
+  </si>
+  <si>
+    <t>文字大小（概述）</t>
   </si>
   <si>
     <t>text_size_preview</t>
@@ -75798,23 +75852,23 @@
       <c r="D364" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="E364" t="s" s="2">
-        <v>63</v>
+      <c r="E364" t="s" s="1">
+        <v>5284</v>
       </c>
       <c r="F364" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="G364" t="s" s="2">
-        <v>63</v>
+      <c r="G364" t="s" s="1">
+        <v>5285</v>
       </c>
       <c r="H364" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="I364" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="J364" t="s" s="2">
-        <v>63</v>
+      <c r="I364" t="s" s="1">
+        <v>5286</v>
+      </c>
+      <c r="J364" t="s" s="1">
+        <v>5287</v>
       </c>
       <c r="K364" t="s" s="2">
         <v>63</v>
@@ -75822,44 +75876,44 @@
       <c r="L364" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="M364" t="s" s="2">
-        <v>63</v>
+      <c r="M364" t="s" s="1">
+        <v>5288</v>
       </c>
       <c r="N364" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="O364" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="P364" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Q364" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="R364" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="S364" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="T364" t="s" s="2">
-        <v>63</v>
+      <c r="O364" t="s" s="1">
+        <v>5289</v>
+      </c>
+      <c r="P364" t="s" s="1">
+        <v>5290</v>
+      </c>
+      <c r="Q364" t="s" s="1">
+        <v>5291</v>
+      </c>
+      <c r="R364" t="s" s="1">
+        <v>5292</v>
+      </c>
+      <c r="S364" t="s" s="1">
+        <v>5293</v>
+      </c>
+      <c r="T364" t="s" s="1">
+        <v>5294</v>
       </c>
       <c r="U364" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="V364" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="W364" t="s" s="2">
-        <v>63</v>
+      <c r="V364" t="s" s="1">
+        <v>5295</v>
+      </c>
+      <c r="W364" t="s" s="1">
+        <v>5296</v>
       </c>
       <c r="X364" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="Y364" t="s" s="2">
-        <v>63</v>
+      <c r="Y364" t="s" s="1">
+        <v>5297</v>
       </c>
       <c r="Z364" t="s" s="2">
         <v>63</v>
@@ -75870,28 +75924,28 @@
       <c r="AB364" t="s" s="2">
         <v>63</v>
       </c>
-      <c r="AC364" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AD364" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AE364" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="AF364" t="s" s="2">
-        <v>63</v>
+      <c r="AC364" t="s" s="1">
+        <v>5298</v>
+      </c>
+      <c r="AD364" t="s" s="1">
+        <v>5299</v>
+      </c>
+      <c r="AE364" t="s" s="1">
+        <v>5300</v>
+      </c>
+      <c r="AF364" t="s" s="1">
+        <v>5301</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="s" s="1">
-        <v>5284</v>
+        <v>5302</v>
       </c>
       <c r="B365" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C365" t="s" s="1">
-        <v>5285</v>
+        <v>5303</v>
       </c>
       <c r="D365" t="s" s="2">
         <v>63</v>
@@ -75983,132 +76037,132 @@
     </row>
     <row r="366">
       <c r="A366" t="s" s="1">
-        <v>5286</v>
+        <v>5304</v>
       </c>
       <c r="B366" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C366" t="s" s="1">
-        <v>5287</v>
+        <v>5305</v>
       </c>
       <c r="D366" t="s" s="1">
-        <v>5288</v>
+        <v>5306</v>
       </c>
       <c r="E366" t="s" s="1">
-        <v>5289</v>
+        <v>5307</v>
       </c>
       <c r="F366" t="s" s="1">
-        <v>5288</v>
+        <v>5306</v>
       </c>
       <c r="G366" t="s" s="1">
-        <v>5290</v>
+        <v>5308</v>
       </c>
       <c r="H366" t="s" s="1">
-        <v>5291</v>
+        <v>5309</v>
       </c>
       <c r="I366" t="s" s="1">
-        <v>5288</v>
+        <v>5306</v>
       </c>
       <c r="J366" t="s" s="1">
-        <v>5292</v>
+        <v>5310</v>
       </c>
       <c r="K366" t="s" s="1">
-        <v>5289</v>
+        <v>5307</v>
       </c>
       <c r="L366" t="s" s="1">
-        <v>5288</v>
+        <v>5306</v>
       </c>
       <c r="M366" t="s" s="1">
-        <v>5288</v>
+        <v>5306</v>
       </c>
       <c r="N366" t="s" s="1">
-        <v>5293</v>
+        <v>5311</v>
       </c>
       <c r="O366" t="s" s="1">
-        <v>5294</v>
+        <v>5312</v>
       </c>
       <c r="P366" t="s" s="1">
-        <v>5288</v>
+        <v>5306</v>
       </c>
       <c r="Q366" t="s" s="1">
-        <v>5295</v>
+        <v>5313</v>
       </c>
       <c r="R366" t="s" s="1">
-        <v>5288</v>
+        <v>5306</v>
       </c>
       <c r="S366" t="s" s="1">
-        <v>5296</v>
+        <v>5314</v>
       </c>
       <c r="T366" t="s" s="1">
-        <v>5288</v>
+        <v>5306</v>
       </c>
       <c r="U366" t="s" s="1">
-        <v>5288</v>
+        <v>5306</v>
       </c>
       <c r="V366" t="s" s="1">
-        <v>5288</v>
+        <v>5306</v>
       </c>
       <c r="W366" t="s" s="1">
-        <v>5297</v>
+        <v>5315</v>
       </c>
       <c r="X366" t="s" s="1">
-        <v>5289</v>
+        <v>5307</v>
       </c>
       <c r="Y366" t="s" s="1">
-        <v>5288</v>
+        <v>5306</v>
       </c>
       <c r="Z366" t="s" s="1">
-        <v>5288</v>
+        <v>5306</v>
       </c>
       <c r="AA366" t="s" s="1">
-        <v>5288</v>
+        <v>5306</v>
       </c>
       <c r="AB366" t="s" s="1">
-        <v>5288</v>
+        <v>5306</v>
       </c>
       <c r="AC366" t="s" s="1">
-        <v>5297</v>
+        <v>5315</v>
       </c>
       <c r="AD366" t="s" s="1">
-        <v>5298</v>
+        <v>5316</v>
       </c>
       <c r="AE366" t="s" s="1">
-        <v>5299</v>
+        <v>5317</v>
       </c>
       <c r="AF366" t="s" s="1">
-        <v>5300</v>
+        <v>5318</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="s" s="1">
-        <v>5301</v>
+        <v>5319</v>
       </c>
       <c r="B367" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C367" t="s" s="1">
-        <v>5302</v>
+        <v>5320</v>
       </c>
       <c r="D367" t="s" s="2">
         <v>63</v>
       </c>
       <c r="E367" t="s" s="1">
-        <v>5303</v>
+        <v>5321</v>
       </c>
       <c r="F367" t="s" s="2">
         <v>63</v>
       </c>
       <c r="G367" t="s" s="1">
-        <v>5304</v>
+        <v>5322</v>
       </c>
       <c r="H367" t="s" s="2">
         <v>63</v>
       </c>
       <c r="I367" t="s" s="1">
-        <v>5305</v>
+        <v>5323</v>
       </c>
       <c r="J367" t="s" s="1">
-        <v>5306</v>
+        <v>5324</v>
       </c>
       <c r="K367" t="s" s="2">
         <v>63</v>
@@ -76135,19 +76189,19 @@
         <v>63</v>
       </c>
       <c r="S367" t="s" s="1">
-        <v>5307</v>
+        <v>5325</v>
       </c>
       <c r="T367" t="s" s="1">
-        <v>5308</v>
+        <v>5326</v>
       </c>
       <c r="U367" t="s" s="2">
         <v>63</v>
       </c>
       <c r="V367" t="s" s="1">
-        <v>5309</v>
+        <v>5327</v>
       </c>
       <c r="W367" t="s" s="1">
-        <v>5310</v>
+        <v>5328</v>
       </c>
       <c r="X367" t="s" s="2">
         <v>63</v>
@@ -76165,146 +76219,146 @@
         <v>63</v>
       </c>
       <c r="AC367" t="s" s="1">
-        <v>5311</v>
+        <v>5329</v>
       </c>
       <c r="AD367" t="s" s="2">
         <v>63</v>
       </c>
       <c r="AE367" t="s" s="1">
-        <v>5312</v>
+        <v>5330</v>
       </c>
       <c r="AF367" t="s" s="1">
-        <v>5313</v>
+        <v>5331</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="s" s="1">
-        <v>5314</v>
+        <v>5332</v>
       </c>
       <c r="B368" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C368" t="s" s="1">
-        <v>5315</v>
+        <v>5333</v>
       </c>
       <c r="D368" t="s" s="1">
-        <v>5316</v>
+        <v>5334</v>
       </c>
       <c r="E368" t="s" s="1">
-        <v>5317</v>
+        <v>5335</v>
       </c>
       <c r="F368" t="s" s="1">
-        <v>5318</v>
+        <v>5336</v>
       </c>
       <c r="G368" t="s" s="1">
-        <v>5318</v>
+        <v>5336</v>
       </c>
       <c r="H368" t="s" s="1">
-        <v>5319</v>
+        <v>5337</v>
       </c>
       <c r="I368" t="s" s="1">
-        <v>5320</v>
+        <v>5338</v>
       </c>
       <c r="J368" t="s" s="1">
-        <v>5321</v>
+        <v>5339</v>
       </c>
       <c r="K368" t="s" s="1">
-        <v>5322</v>
+        <v>5340</v>
       </c>
       <c r="L368" t="s" s="1">
-        <v>5323</v>
+        <v>5341</v>
       </c>
       <c r="M368" t="s" s="1">
-        <v>5324</v>
+        <v>5342</v>
       </c>
       <c r="N368" t="s" s="1">
-        <v>5325</v>
+        <v>5343</v>
       </c>
       <c r="O368" t="s" s="1">
-        <v>5326</v>
+        <v>5344</v>
       </c>
       <c r="P368" t="s" s="1">
-        <v>5327</v>
+        <v>5345</v>
       </c>
       <c r="Q368" t="s" s="1">
-        <v>5318</v>
+        <v>5336</v>
       </c>
       <c r="R368" t="s" s="1">
-        <v>5327</v>
+        <v>5345</v>
       </c>
       <c r="S368" t="s" s="1">
-        <v>5328</v>
+        <v>5346</v>
       </c>
       <c r="T368" t="s" s="1">
-        <v>5320</v>
+        <v>5338</v>
       </c>
       <c r="U368" t="s" s="1">
-        <v>5320</v>
+        <v>5338</v>
       </c>
       <c r="V368" t="s" s="1">
-        <v>5329</v>
+        <v>5347</v>
       </c>
       <c r="W368" t="s" s="1">
-        <v>5330</v>
+        <v>5348</v>
       </c>
       <c r="X368" t="s" s="1">
-        <v>5331</v>
+        <v>5349</v>
       </c>
       <c r="Y368" t="s" s="1">
-        <v>5332</v>
+        <v>5350</v>
       </c>
       <c r="Z368" t="s" s="1">
-        <v>5318</v>
+        <v>5336</v>
       </c>
       <c r="AA368" t="s" s="1">
-        <v>5333</v>
+        <v>5351</v>
       </c>
       <c r="AB368" t="s" s="1">
-        <v>5334</v>
+        <v>5352</v>
       </c>
       <c r="AC368" t="s" s="1">
-        <v>5335</v>
+        <v>5353</v>
       </c>
       <c r="AD368" t="s" s="1">
-        <v>5336</v>
+        <v>5354</v>
       </c>
       <c r="AE368" t="s" s="1">
-        <v>5337</v>
+        <v>5355</v>
       </c>
       <c r="AF368" t="s" s="1">
-        <v>5338</v>
+        <v>5356</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="s" s="1">
-        <v>5339</v>
+        <v>5357</v>
       </c>
       <c r="B369" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C369" t="s" s="1">
-        <v>5340</v>
+        <v>5358</v>
       </c>
       <c r="D369" t="s" s="2">
         <v>63</v>
       </c>
       <c r="E369" t="s" s="1">
-        <v>5341</v>
+        <v>5359</v>
       </c>
       <c r="F369" t="s" s="2">
         <v>63</v>
       </c>
       <c r="G369" t="s" s="1">
-        <v>5342</v>
+        <v>5360</v>
       </c>
       <c r="H369" t="s" s="2">
         <v>63</v>
       </c>
       <c r="I369" t="s" s="1">
-        <v>5343</v>
+        <v>5361</v>
       </c>
       <c r="J369" t="s" s="1">
-        <v>5344</v>
+        <v>5362</v>
       </c>
       <c r="K369" t="s" s="2">
         <v>63</v>
@@ -76313,7 +76367,7 @@
         <v>63</v>
       </c>
       <c r="M369" t="s" s="1">
-        <v>5345</v>
+        <v>5363</v>
       </c>
       <c r="N369" t="s" s="2">
         <v>63</v>
@@ -76325,25 +76379,25 @@
         <v>63</v>
       </c>
       <c r="Q369" t="s" s="1">
-        <v>5346</v>
+        <v>5364</v>
       </c>
       <c r="R369" t="s" s="2">
         <v>63</v>
       </c>
       <c r="S369" t="s" s="1">
-        <v>5347</v>
+        <v>5365</v>
       </c>
       <c r="T369" t="s" s="1">
-        <v>5348</v>
+        <v>5366</v>
       </c>
       <c r="U369" t="s" s="2">
         <v>63</v>
       </c>
       <c r="V369" t="s" s="1">
-        <v>5349</v>
+        <v>5367</v>
       </c>
       <c r="W369" t="s" s="1">
-        <v>5350</v>
+        <v>5368</v>
       </c>
       <c r="X369" t="s" s="2">
         <v>63</v>
@@ -76361,119 +76415,119 @@
         <v>63</v>
       </c>
       <c r="AC369" t="s" s="1">
-        <v>5351</v>
+        <v>5369</v>
       </c>
       <c r="AD369" t="s" s="2">
         <v>63</v>
       </c>
       <c r="AE369" t="s" s="1">
-        <v>5352</v>
+        <v>5370</v>
       </c>
       <c r="AF369" t="s" s="1">
-        <v>5353</v>
+        <v>5371</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="s" s="1">
-        <v>5354</v>
+        <v>5372</v>
       </c>
       <c r="B370" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C370" t="s" s="1">
-        <v>5355</v>
+        <v>5373</v>
       </c>
       <c r="D370" t="s" s="1">
-        <v>5356</v>
+        <v>5374</v>
       </c>
       <c r="E370" t="s" s="1">
-        <v>5357</v>
+        <v>5375</v>
       </c>
       <c r="F370" t="s" s="1">
-        <v>5358</v>
+        <v>5376</v>
       </c>
       <c r="G370" t="s" s="1">
-        <v>5359</v>
+        <v>5377</v>
       </c>
       <c r="H370" t="s" s="1">
-        <v>5360</v>
+        <v>5378</v>
       </c>
       <c r="I370" t="s" s="1">
-        <v>5361</v>
+        <v>5379</v>
       </c>
       <c r="J370" t="s" s="1">
         <v>4600</v>
       </c>
       <c r="K370" t="s" s="1">
-        <v>5362</v>
+        <v>5380</v>
       </c>
       <c r="L370" t="s" s="1">
-        <v>5363</v>
+        <v>5381</v>
       </c>
       <c r="M370" t="s" s="1">
-        <v>5364</v>
+        <v>5382</v>
       </c>
       <c r="N370" t="s" s="1">
-        <v>5365</v>
+        <v>5383</v>
       </c>
       <c r="O370" t="s" s="1">
-        <v>5366</v>
+        <v>5384</v>
       </c>
       <c r="P370" t="s" s="1">
-        <v>5367</v>
+        <v>5385</v>
       </c>
       <c r="Q370" t="s" s="1">
-        <v>5368</v>
+        <v>5386</v>
       </c>
       <c r="R370" t="s" s="1">
-        <v>5369</v>
+        <v>5387</v>
       </c>
       <c r="S370" t="s" s="1">
-        <v>5370</v>
+        <v>5388</v>
       </c>
       <c r="T370" t="s" s="1">
-        <v>5371</v>
+        <v>5389</v>
       </c>
       <c r="U370" t="s" s="1">
-        <v>5371</v>
+        <v>5389</v>
       </c>
       <c r="V370" t="s" s="1">
-        <v>5372</v>
+        <v>5390</v>
       </c>
       <c r="W370" t="s" s="1">
-        <v>5373</v>
+        <v>5391</v>
       </c>
       <c r="X370" t="s" s="1">
-        <v>5374</v>
+        <v>5392</v>
       </c>
       <c r="Y370" t="s" s="1">
-        <v>5375</v>
+        <v>5393</v>
       </c>
       <c r="Z370" t="s" s="1">
-        <v>5376</v>
+        <v>5394</v>
       </c>
       <c r="AA370" t="s" s="1">
-        <v>5377</v>
+        <v>5395</v>
       </c>
       <c r="AB370" t="s" s="1">
-        <v>5378</v>
+        <v>5396</v>
       </c>
       <c r="AC370" t="s" s="1">
-        <v>5379</v>
+        <v>5397</v>
       </c>
       <c r="AD370" t="s" s="1">
-        <v>5380</v>
+        <v>5398</v>
       </c>
       <c r="AE370" t="s" s="1">
-        <v>5381</v>
+        <v>5399</v>
       </c>
       <c r="AF370" t="s" s="1">
-        <v>5382</v>
+        <v>5400</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="s" s="1">
-        <v>5383</v>
+        <v>5401</v>
       </c>
       <c r="B371" t="s" s="1">
         <v>33</v>
@@ -76527,7 +76581,7 @@
         <v>63</v>
       </c>
       <c r="S371" t="s" s="1">
-        <v>5384</v>
+        <v>5402</v>
       </c>
       <c r="T371" t="s" s="3">
         <v>63</v>
@@ -76539,7 +76593,7 @@
         <v>63</v>
       </c>
       <c r="W371" t="s" s="1">
-        <v>5385</v>
+        <v>5403</v>
       </c>
       <c r="X371" t="s" s="3">
         <v>63</v>
@@ -76571,7 +76625,7 @@
     </row>
     <row r="372">
       <c r="A372" t="s" s="1">
-        <v>5386</v>
+        <v>5404</v>
       </c>
       <c r="B372" t="s" s="1">
         <v>33</v>
@@ -76625,7 +76679,7 @@
         <v>63</v>
       </c>
       <c r="S372" t="s" s="1">
-        <v>5387</v>
+        <v>5405</v>
       </c>
       <c r="T372" t="s" s="3">
         <v>63</v>
@@ -76669,13 +76723,13 @@
     </row>
     <row r="373">
       <c r="A373" t="s" s="1">
-        <v>5388</v>
+        <v>5406</v>
       </c>
       <c r="B373" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C373" t="s" s="1">
-        <v>5389</v>
+        <v>5407</v>
       </c>
       <c r="D373" t="s" s="2">
         <v>63</v>
@@ -76687,16 +76741,16 @@
         <v>63</v>
       </c>
       <c r="G373" t="s" s="1">
-        <v>5390</v>
+        <v>5408</v>
       </c>
       <c r="H373" t="s" s="2">
         <v>63</v>
       </c>
       <c r="I373" t="s" s="1">
-        <v>5391</v>
+        <v>5409</v>
       </c>
       <c r="J373" t="s" s="1">
-        <v>5392</v>
+        <v>5410</v>
       </c>
       <c r="K373" t="s" s="2">
         <v>63</v>
@@ -76705,7 +76759,7 @@
         <v>63</v>
       </c>
       <c r="M373" t="s" s="1">
-        <v>5393</v>
+        <v>5411</v>
       </c>
       <c r="N373" t="s" s="2">
         <v>63</v>
@@ -76717,25 +76771,25 @@
         <v>63</v>
       </c>
       <c r="Q373" t="s" s="1">
-        <v>5394</v>
+        <v>5412</v>
       </c>
       <c r="R373" t="s" s="2">
         <v>63</v>
       </c>
       <c r="S373" t="s" s="1">
-        <v>5395</v>
+        <v>5413</v>
       </c>
       <c r="T373" t="s" s="1">
-        <v>5396</v>
+        <v>5414</v>
       </c>
       <c r="U373" t="s" s="2">
         <v>63</v>
       </c>
       <c r="V373" t="s" s="1">
-        <v>5397</v>
+        <v>5415</v>
       </c>
       <c r="W373" t="s" s="1">
-        <v>5398</v>
+        <v>5416</v>
       </c>
       <c r="X373" t="s" s="2">
         <v>63</v>
@@ -76753,27 +76807,27 @@
         <v>63</v>
       </c>
       <c r="AC373" t="s" s="1">
-        <v>5399</v>
+        <v>5417</v>
       </c>
       <c r="AD373" t="s" s="2">
         <v>63</v>
       </c>
       <c r="AE373" t="s" s="1">
-        <v>5400</v>
+        <v>5418</v>
       </c>
       <c r="AF373" t="s" s="1">
-        <v>5401</v>
+        <v>5419</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="s" s="1">
-        <v>5402</v>
+        <v>5420</v>
       </c>
       <c r="B374" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C374" t="s" s="1">
-        <v>5403</v>
+        <v>5421</v>
       </c>
       <c r="D374" t="s" s="2">
         <v>63</v>
@@ -76785,55 +76839,55 @@
         <v>63</v>
       </c>
       <c r="G374" t="s" s="1">
-        <v>5404</v>
+        <v>5422</v>
       </c>
       <c r="H374" t="s" s="2">
         <v>63</v>
       </c>
       <c r="I374" t="s" s="1">
+        <v>5423</v>
+      </c>
+      <c r="J374" t="s" s="1">
+        <v>5424</v>
+      </c>
+      <c r="K374" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="L374" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="M374" t="s" s="1">
+        <v>5425</v>
+      </c>
+      <c r="N374" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="O374" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="P374" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="Q374" t="s" s="1">
+        <v>5426</v>
+      </c>
+      <c r="R374" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="S374" t="s" s="1">
         <v>5405</v>
       </c>
-      <c r="J374" t="s" s="1">
-        <v>5406</v>
-      </c>
-      <c r="K374" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="L374" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="M374" t="s" s="1">
-        <v>5407</v>
-      </c>
-      <c r="N374" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="O374" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="P374" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="Q374" t="s" s="1">
-        <v>5408</v>
-      </c>
-      <c r="R374" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="S374" t="s" s="1">
-        <v>5387</v>
-      </c>
       <c r="T374" t="s" s="1">
-        <v>5409</v>
+        <v>5427</v>
       </c>
       <c r="U374" t="s" s="2">
         <v>63</v>
       </c>
       <c r="V374" t="s" s="1">
-        <v>5410</v>
+        <v>5428</v>
       </c>
       <c r="W374" t="s" s="1">
-        <v>5411</v>
+        <v>5429</v>
       </c>
       <c r="X374" t="s" s="2">
         <v>63</v>
@@ -76851,21 +76905,21 @@
         <v>63</v>
       </c>
       <c r="AC374" t="s" s="1">
-        <v>5399</v>
+        <v>5417</v>
       </c>
       <c r="AD374" t="s" s="2">
         <v>63</v>
       </c>
       <c r="AE374" t="s" s="1">
-        <v>5400</v>
+        <v>5418</v>
       </c>
       <c r="AF374" t="s" s="1">
-        <v>5401</v>
+        <v>5419</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="s" s="1">
-        <v>5412</v>
+        <v>5430</v>
       </c>
       <c r="B375" t="s" s="1">
         <v>33</v>
@@ -76963,7 +77017,7 @@
     </row>
     <row r="376">
       <c r="A376" t="s" s="1">
-        <v>5413</v>
+        <v>5431</v>
       </c>
       <c r="B376" t="s" s="1">
         <v>33</v>
@@ -77061,34 +77115,34 @@
     </row>
     <row r="377">
       <c r="A377" t="s" s="1">
-        <v>5414</v>
+        <v>5432</v>
       </c>
       <c r="B377" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C377" t="s" s="1">
-        <v>5415</v>
+        <v>5433</v>
       </c>
       <c r="D377" t="s" s="2">
         <v>63</v>
       </c>
       <c r="E377" t="s" s="1">
-        <v>5416</v>
+        <v>5434</v>
       </c>
       <c r="F377" t="s" s="2">
         <v>63</v>
       </c>
       <c r="G377" t="s" s="1">
-        <v>5417</v>
+        <v>5435</v>
       </c>
       <c r="H377" t="s" s="2">
         <v>63</v>
       </c>
       <c r="I377" t="s" s="1">
-        <v>5418</v>
+        <v>5436</v>
       </c>
       <c r="J377" t="s" s="1">
-        <v>5419</v>
+        <v>5437</v>
       </c>
       <c r="K377" t="s" s="2">
         <v>63</v>
@@ -77097,7 +77151,7 @@
         <v>63</v>
       </c>
       <c r="M377" t="s" s="1">
-        <v>5420</v>
+        <v>5438</v>
       </c>
       <c r="N377" t="s" s="2">
         <v>63</v>
@@ -77109,25 +77163,25 @@
         <v>63</v>
       </c>
       <c r="Q377" t="s" s="1">
-        <v>5421</v>
+        <v>5439</v>
       </c>
       <c r="R377" t="s" s="2">
         <v>63</v>
       </c>
       <c r="S377" t="s" s="1">
-        <v>5422</v>
+        <v>5440</v>
       </c>
       <c r="T377" t="s" s="1">
-        <v>5423</v>
+        <v>5441</v>
       </c>
       <c r="U377" t="s" s="2">
         <v>63</v>
       </c>
       <c r="V377" t="s" s="1">
-        <v>5424</v>
+        <v>5442</v>
       </c>
       <c r="W377" t="s" s="1">
-        <v>5425</v>
+        <v>5443</v>
       </c>
       <c r="X377" t="s" s="2">
         <v>63</v>
@@ -77145,27 +77199,27 @@
         <v>63</v>
       </c>
       <c r="AC377" t="s" s="1">
-        <v>5426</v>
+        <v>5444</v>
       </c>
       <c r="AD377" t="s" s="2">
         <v>63</v>
       </c>
       <c r="AE377" t="s" s="1">
-        <v>5427</v>
+        <v>5445</v>
       </c>
       <c r="AF377" t="s" s="1">
-        <v>5428</v>
+        <v>5446</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="s" s="1">
-        <v>5429</v>
+        <v>5447</v>
       </c>
       <c r="B378" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C378" t="s" s="1">
-        <v>5430</v>
+        <v>5448</v>
       </c>
       <c r="D378" t="s" s="2">
         <v>63</v>
@@ -77177,13 +77231,13 @@
         <v>63</v>
       </c>
       <c r="G378" t="s" s="1">
-        <v>5431</v>
+        <v>5449</v>
       </c>
       <c r="H378" t="s" s="2">
         <v>63</v>
       </c>
       <c r="I378" t="s" s="1">
-        <v>5432</v>
+        <v>5450</v>
       </c>
       <c r="J378" t="s" s="1">
         <v>871</v>
@@ -77207,7 +77261,7 @@
         <v>63</v>
       </c>
       <c r="Q378" t="s" s="1">
-        <v>5433</v>
+        <v>5451</v>
       </c>
       <c r="R378" t="s" s="2">
         <v>63</v>
@@ -77216,13 +77270,13 @@
         <v>577</v>
       </c>
       <c r="T378" t="s" s="1">
-        <v>5434</v>
+        <v>5452</v>
       </c>
       <c r="U378" t="s" s="2">
         <v>63</v>
       </c>
       <c r="V378" t="s" s="1">
-        <v>5435</v>
+        <v>5453</v>
       </c>
       <c r="W378" t="s" s="1">
         <v>4417</v>
@@ -77243,48 +77297,48 @@
         <v>63</v>
       </c>
       <c r="AC378" t="s" s="1">
-        <v>5436</v>
+        <v>5454</v>
       </c>
       <c r="AD378" t="s" s="2">
         <v>63</v>
       </c>
       <c r="AE378" t="s" s="1">
-        <v>5437</v>
+        <v>5455</v>
       </c>
       <c r="AF378" t="s" s="1">
-        <v>5438</v>
+        <v>5456</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="s" s="1">
-        <v>5439</v>
+        <v>5457</v>
       </c>
       <c r="B379" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C379" t="s" s="1">
-        <v>5440</v>
+        <v>5458</v>
       </c>
       <c r="D379" t="s" s="2">
         <v>63</v>
       </c>
       <c r="E379" t="s" s="1">
-        <v>5441</v>
+        <v>5459</v>
       </c>
       <c r="F379" t="s" s="2">
         <v>63</v>
       </c>
       <c r="G379" t="s" s="1">
-        <v>5442</v>
+        <v>5460</v>
       </c>
       <c r="H379" t="s" s="2">
         <v>63</v>
       </c>
       <c r="I379" t="s" s="1">
-        <v>5443</v>
+        <v>5461</v>
       </c>
       <c r="J379" t="s" s="1">
-        <v>5444</v>
+        <v>5462</v>
       </c>
       <c r="K379" t="s" s="2">
         <v>63</v>
@@ -77293,7 +77347,7 @@
         <v>63</v>
       </c>
       <c r="M379" t="s" s="1">
-        <v>5445</v>
+        <v>5463</v>
       </c>
       <c r="N379" t="s" s="2">
         <v>63</v>
@@ -77302,34 +77356,34 @@
         <v>63</v>
       </c>
       <c r="P379" t="s" s="1">
-        <v>5446</v>
+        <v>5464</v>
       </c>
       <c r="Q379" t="s" s="1">
-        <v>5447</v>
+        <v>5465</v>
       </c>
       <c r="R379" t="s" s="1">
-        <v>5448</v>
+        <v>5466</v>
       </c>
       <c r="S379" t="s" s="1">
-        <v>5449</v>
+        <v>5467</v>
       </c>
       <c r="T379" t="s" s="1">
-        <v>5450</v>
+        <v>5468</v>
       </c>
       <c r="U379" t="s" s="2">
         <v>63</v>
       </c>
       <c r="V379" t="s" s="1">
-        <v>5451</v>
+        <v>5469</v>
       </c>
       <c r="W379" t="s" s="1">
-        <v>5452</v>
+        <v>5470</v>
       </c>
       <c r="X379" t="s" s="2">
         <v>63</v>
       </c>
       <c r="Y379" t="s" s="1">
-        <v>5453</v>
+        <v>5471</v>
       </c>
       <c r="Z379" t="s" s="2">
         <v>63</v>
@@ -77341,48 +77395,48 @@
         <v>63</v>
       </c>
       <c r="AC379" t="s" s="1">
-        <v>5454</v>
+        <v>5472</v>
       </c>
       <c r="AD379" t="s" s="1">
-        <v>5455</v>
+        <v>5473</v>
       </c>
       <c r="AE379" t="s" s="1">
-        <v>5456</v>
+        <v>5474</v>
       </c>
       <c r="AF379" t="s" s="1">
-        <v>5457</v>
+        <v>5475</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="s" s="1">
-        <v>5458</v>
+        <v>5476</v>
       </c>
       <c r="B380" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C380" t="s" s="1">
-        <v>5459</v>
+        <v>5477</v>
       </c>
       <c r="D380" t="s" s="2">
         <v>63</v>
       </c>
       <c r="E380" t="s" s="1">
-        <v>5460</v>
+        <v>5478</v>
       </c>
       <c r="F380" t="s" s="2">
         <v>63</v>
       </c>
       <c r="G380" t="s" s="1">
-        <v>5461</v>
+        <v>5479</v>
       </c>
       <c r="H380" t="s" s="2">
         <v>63</v>
       </c>
       <c r="I380" t="s" s="1">
-        <v>5462</v>
+        <v>5480</v>
       </c>
       <c r="J380" t="s" s="1">
-        <v>5463</v>
+        <v>5481</v>
       </c>
       <c r="K380" t="s" s="2">
         <v>63</v>
@@ -77391,7 +77445,7 @@
         <v>63</v>
       </c>
       <c r="M380" t="s" s="1">
-        <v>5464</v>
+        <v>5482</v>
       </c>
       <c r="N380" t="s" s="2">
         <v>63</v>
@@ -77400,34 +77454,34 @@
         <v>63</v>
       </c>
       <c r="P380" t="s" s="1">
-        <v>5465</v>
+        <v>5483</v>
       </c>
       <c r="Q380" t="s" s="1">
-        <v>5466</v>
+        <v>5484</v>
       </c>
       <c r="R380" t="s" s="1">
-        <v>5467</v>
+        <v>5485</v>
       </c>
       <c r="S380" t="s" s="1">
-        <v>5468</v>
+        <v>5486</v>
       </c>
       <c r="T380" t="s" s="1">
-        <v>5469</v>
+        <v>5487</v>
       </c>
       <c r="U380" t="s" s="2">
         <v>63</v>
       </c>
       <c r="V380" t="s" s="1">
-        <v>5470</v>
+        <v>5488</v>
       </c>
       <c r="W380" t="s" s="1">
-        <v>5471</v>
+        <v>5489</v>
       </c>
       <c r="X380" t="s" s="2">
         <v>63</v>
       </c>
       <c r="Y380" t="s" s="1">
-        <v>5472</v>
+        <v>5490</v>
       </c>
       <c r="Z380" t="s" s="2">
         <v>63</v>
@@ -77439,48 +77493,48 @@
         <v>63</v>
       </c>
       <c r="AC380" t="s" s="1">
-        <v>5473</v>
+        <v>5491</v>
       </c>
       <c r="AD380" t="s" s="1">
-        <v>5474</v>
+        <v>5492</v>
       </c>
       <c r="AE380" t="s" s="1">
-        <v>5475</v>
+        <v>5493</v>
       </c>
       <c r="AF380" t="s" s="1">
-        <v>5476</v>
+        <v>5494</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="s" s="1">
-        <v>5477</v>
+        <v>5495</v>
       </c>
       <c r="B381" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C381" t="s" s="1">
-        <v>5478</v>
+        <v>5496</v>
       </c>
       <c r="D381" t="s" s="2">
         <v>63</v>
       </c>
       <c r="E381" t="s" s="1">
-        <v>5479</v>
+        <v>5497</v>
       </c>
       <c r="F381" t="s" s="2">
         <v>63</v>
       </c>
       <c r="G381" t="s" s="1">
-        <v>5480</v>
+        <v>5498</v>
       </c>
       <c r="H381" t="s" s="2">
         <v>63</v>
       </c>
       <c r="I381" t="s" s="1">
-        <v>5481</v>
+        <v>5499</v>
       </c>
       <c r="J381" t="s" s="1">
-        <v>5482</v>
+        <v>5500</v>
       </c>
       <c r="K381" t="s" s="2">
         <v>63</v>
@@ -77489,7 +77543,7 @@
         <v>63</v>
       </c>
       <c r="M381" t="s" s="1">
-        <v>5483</v>
+        <v>5501</v>
       </c>
       <c r="N381" t="s" s="2">
         <v>63</v>
@@ -77507,19 +77561,19 @@
         <v>63</v>
       </c>
       <c r="S381" t="s" s="1">
-        <v>5484</v>
+        <v>5502</v>
       </c>
       <c r="T381" t="s" s="1">
-        <v>5485</v>
+        <v>5503</v>
       </c>
       <c r="U381" t="s" s="2">
         <v>63</v>
       </c>
       <c r="V381" t="s" s="1">
-        <v>5486</v>
+        <v>5504</v>
       </c>
       <c r="W381" t="s" s="1">
-        <v>5487</v>
+        <v>5505</v>
       </c>
       <c r="X381" t="s" s="2">
         <v>63</v>
@@ -77537,48 +77591,48 @@
         <v>63</v>
       </c>
       <c r="AC381" t="s" s="1">
-        <v>5488</v>
+        <v>5506</v>
       </c>
       <c r="AD381" t="s" s="2">
         <v>63</v>
       </c>
       <c r="AE381" t="s" s="1">
-        <v>5489</v>
+        <v>5507</v>
       </c>
       <c r="AF381" t="s" s="1">
-        <v>5490</v>
+        <v>5508</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="s" s="1">
-        <v>5491</v>
+        <v>5509</v>
       </c>
       <c r="B382" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C382" t="s" s="1">
-        <v>5492</v>
+        <v>5510</v>
       </c>
       <c r="D382" t="s" s="2">
         <v>63</v>
       </c>
       <c r="E382" t="s" s="1">
-        <v>5493</v>
+        <v>5511</v>
       </c>
       <c r="F382" t="s" s="2">
         <v>63</v>
       </c>
       <c r="G382" t="s" s="1">
-        <v>5494</v>
+        <v>5512</v>
       </c>
       <c r="H382" t="s" s="2">
         <v>63</v>
       </c>
       <c r="I382" t="s" s="1">
-        <v>5495</v>
+        <v>5513</v>
       </c>
       <c r="J382" t="s" s="1">
-        <v>5496</v>
+        <v>5514</v>
       </c>
       <c r="K382" t="s" s="2">
         <v>63</v>
@@ -77587,7 +77641,7 @@
         <v>63</v>
       </c>
       <c r="M382" t="s" s="1">
-        <v>5497</v>
+        <v>5515</v>
       </c>
       <c r="N382" t="s" s="2">
         <v>63</v>
@@ -77599,25 +77653,25 @@
         <v>63</v>
       </c>
       <c r="Q382" t="s" s="1">
-        <v>5498</v>
+        <v>5516</v>
       </c>
       <c r="R382" t="s" s="2">
         <v>63</v>
       </c>
       <c r="S382" t="s" s="1">
-        <v>5499</v>
+        <v>5517</v>
       </c>
       <c r="T382" t="s" s="1">
-        <v>5500</v>
+        <v>5518</v>
       </c>
       <c r="U382" t="s" s="2">
         <v>63</v>
       </c>
       <c r="V382" t="s" s="1">
-        <v>5501</v>
+        <v>5519</v>
       </c>
       <c r="W382" t="s" s="1">
-        <v>5502</v>
+        <v>5520</v>
       </c>
       <c r="X382" t="s" s="2">
         <v>63</v>
@@ -77635,48 +77689,48 @@
         <v>63</v>
       </c>
       <c r="AC382" t="s" s="1">
-        <v>5503</v>
+        <v>5521</v>
       </c>
       <c r="AD382" t="s" s="2">
         <v>63</v>
       </c>
       <c r="AE382" t="s" s="1">
-        <v>5504</v>
+        <v>5522</v>
       </c>
       <c r="AF382" t="s" s="1">
-        <v>5505</v>
+        <v>5523</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="s" s="1">
-        <v>5506</v>
+        <v>5524</v>
       </c>
       <c r="B383" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C383" t="s" s="1">
-        <v>5507</v>
+        <v>5525</v>
       </c>
       <c r="D383" t="s" s="2">
         <v>63</v>
       </c>
       <c r="E383" t="s" s="1">
-        <v>5508</v>
+        <v>5526</v>
       </c>
       <c r="F383" t="s" s="2">
         <v>63</v>
       </c>
       <c r="G383" t="s" s="1">
-        <v>5509</v>
+        <v>5527</v>
       </c>
       <c r="H383" t="s" s="2">
         <v>63</v>
       </c>
       <c r="I383" t="s" s="1">
-        <v>5510</v>
+        <v>5528</v>
       </c>
       <c r="J383" t="s" s="1">
-        <v>5511</v>
+        <v>5529</v>
       </c>
       <c r="K383" t="s" s="2">
         <v>63</v>
@@ -77685,7 +77739,7 @@
         <v>63</v>
       </c>
       <c r="M383" t="s" s="1">
-        <v>5512</v>
+        <v>5530</v>
       </c>
       <c r="N383" t="s" s="2">
         <v>63</v>
@@ -77703,19 +77757,19 @@
         <v>63</v>
       </c>
       <c r="S383" t="s" s="1">
-        <v>5513</v>
+        <v>5531</v>
       </c>
       <c r="T383" t="s" s="1">
-        <v>5514</v>
+        <v>5532</v>
       </c>
       <c r="U383" t="s" s="2">
         <v>63</v>
       </c>
       <c r="V383" t="s" s="1">
-        <v>5515</v>
+        <v>5533</v>
       </c>
       <c r="W383" t="s" s="1">
-        <v>5516</v>
+        <v>5534</v>
       </c>
       <c r="X383" t="s" s="2">
         <v>63</v>
@@ -77733,137 +77787,137 @@
         <v>63</v>
       </c>
       <c r="AC383" t="s" s="1">
-        <v>5517</v>
+        <v>5535</v>
       </c>
       <c r="AD383" t="s" s="2">
         <v>63</v>
       </c>
       <c r="AE383" t="s" s="1">
-        <v>5518</v>
+        <v>5536</v>
       </c>
       <c r="AF383" t="s" s="1">
-        <v>5519</v>
+        <v>5537</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="s" s="1">
-        <v>5520</v>
+        <v>5538</v>
       </c>
       <c r="B384" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C384" t="s" s="1">
-        <v>5521</v>
+        <v>5539</v>
       </c>
       <c r="D384" t="s" s="1">
-        <v>5522</v>
+        <v>5540</v>
       </c>
       <c r="E384" t="s" s="1">
-        <v>5523</v>
+        <v>5541</v>
       </c>
       <c r="F384" t="s" s="1">
-        <v>5524</v>
+        <v>5542</v>
       </c>
       <c r="G384" t="s" s="1">
-        <v>5525</v>
+        <v>5543</v>
       </c>
       <c r="H384" t="s" s="1">
-        <v>5526</v>
+        <v>5544</v>
       </c>
       <c r="I384" t="s" s="1">
-        <v>5527</v>
+        <v>5545</v>
       </c>
       <c r="J384" t="s" s="1">
-        <v>5528</v>
+        <v>5546</v>
       </c>
       <c r="K384" t="s" s="1">
-        <v>5529</v>
+        <v>5547</v>
       </c>
       <c r="L384" t="s" s="1">
-        <v>5530</v>
+        <v>5548</v>
       </c>
       <c r="M384" t="s" s="1">
-        <v>5531</v>
+        <v>5549</v>
       </c>
       <c r="N384" t="s" s="1">
-        <v>5532</v>
+        <v>5550</v>
       </c>
       <c r="O384" t="s" s="1">
-        <v>5533</v>
+        <v>5551</v>
       </c>
       <c r="P384" t="s" s="1">
-        <v>5534</v>
+        <v>5552</v>
       </c>
       <c r="Q384" t="s" s="1">
-        <v>5535</v>
+        <v>5553</v>
       </c>
       <c r="R384" t="s" s="1">
-        <v>5536</v>
+        <v>5554</v>
       </c>
       <c r="S384" t="s" s="1">
-        <v>5537</v>
+        <v>5555</v>
       </c>
       <c r="T384" t="s" s="1">
-        <v>5538</v>
+        <v>5556</v>
       </c>
       <c r="U384" t="s" s="1">
-        <v>5538</v>
+        <v>5556</v>
       </c>
       <c r="V384" t="s" s="1">
-        <v>5539</v>
+        <v>5557</v>
       </c>
       <c r="W384" t="s" s="1">
-        <v>5540</v>
+        <v>5558</v>
       </c>
       <c r="X384" t="s" s="1">
-        <v>5541</v>
+        <v>5559</v>
       </c>
       <c r="Y384" t="s" s="1">
-        <v>5542</v>
+        <v>5560</v>
       </c>
       <c r="Z384" t="s" s="1">
-        <v>5543</v>
+        <v>5561</v>
       </c>
       <c r="AA384" t="s" s="1">
-        <v>5544</v>
+        <v>5562</v>
       </c>
       <c r="AB384" t="s" s="1">
-        <v>5545</v>
+        <v>5563</v>
       </c>
       <c r="AC384" t="s" s="1">
-        <v>5546</v>
+        <v>5564</v>
       </c>
       <c r="AD384" t="s" s="1">
-        <v>5547</v>
+        <v>5565</v>
       </c>
       <c r="AE384" t="s" s="1">
-        <v>5548</v>
+        <v>5566</v>
       </c>
       <c r="AF384" t="s" s="1">
-        <v>5549</v>
+        <v>5567</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="s" s="1">
-        <v>5550</v>
+        <v>5568</v>
       </c>
       <c r="B385" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C385" t="s" s="1">
-        <v>5551</v>
+        <v>5569</v>
       </c>
       <c r="D385" t="s" s="2">
         <v>63</v>
       </c>
       <c r="E385" t="s" s="1">
-        <v>5552</v>
+        <v>5570</v>
       </c>
       <c r="F385" t="s" s="2">
         <v>63</v>
       </c>
       <c r="G385" t="s" s="1">
-        <v>5553</v>
+        <v>5571</v>
       </c>
       <c r="H385" t="s" s="2">
         <v>63</v>
@@ -77872,7 +77926,7 @@
         <v>3923</v>
       </c>
       <c r="J385" t="s" s="1">
-        <v>5554</v>
+        <v>5572</v>
       </c>
       <c r="K385" t="s" s="2">
         <v>63</v>
@@ -77899,19 +77953,19 @@
         <v>63</v>
       </c>
       <c r="S385" t="s" s="1">
-        <v>5555</v>
+        <v>5573</v>
       </c>
       <c r="T385" t="s" s="1">
-        <v>5556</v>
+        <v>5574</v>
       </c>
       <c r="U385" t="s" s="2">
         <v>63</v>
       </c>
       <c r="V385" t="s" s="1">
-        <v>5557</v>
+        <v>5575</v>
       </c>
       <c r="W385" t="s" s="1">
-        <v>5558</v>
+        <v>5576</v>
       </c>
       <c r="X385" t="s" s="2">
         <v>63</v>
@@ -77929,27 +77983,27 @@
         <v>63</v>
       </c>
       <c r="AC385" t="s" s="1">
-        <v>5559</v>
+        <v>5577</v>
       </c>
       <c r="AD385" t="s" s="2">
         <v>63</v>
       </c>
       <c r="AE385" t="s" s="1">
-        <v>5560</v>
+        <v>5578</v>
       </c>
       <c r="AF385" t="s" s="1">
-        <v>5561</v>
+        <v>5579</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="s" s="1">
-        <v>5562</v>
+        <v>5580</v>
       </c>
       <c r="B386" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C386" t="s" s="1">
-        <v>5563</v>
+        <v>5581</v>
       </c>
       <c r="D386" t="s" s="2">
         <v>63</v>
@@ -77961,16 +78015,16 @@
         <v>63</v>
       </c>
       <c r="G386" t="s" s="1">
-        <v>5564</v>
+        <v>5582</v>
       </c>
       <c r="H386" t="s" s="2">
         <v>63</v>
       </c>
       <c r="I386" t="s" s="1">
-        <v>5565</v>
+        <v>5583</v>
       </c>
       <c r="J386" t="s" s="1">
-        <v>5566</v>
+        <v>5584</v>
       </c>
       <c r="K386" t="s" s="2">
         <v>63</v>
@@ -77979,7 +78033,7 @@
         <v>63</v>
       </c>
       <c r="M386" t="s" s="1">
-        <v>5567</v>
+        <v>5585</v>
       </c>
       <c r="N386" t="s" s="2">
         <v>63</v>
@@ -77991,25 +78045,25 @@
         <v>63</v>
       </c>
       <c r="Q386" t="s" s="1">
-        <v>5568</v>
+        <v>5586</v>
       </c>
       <c r="R386" t="s" s="2">
         <v>63</v>
       </c>
       <c r="S386" t="s" s="1">
-        <v>5569</v>
+        <v>5587</v>
       </c>
       <c r="T386" t="s" s="1">
-        <v>5570</v>
+        <v>5588</v>
       </c>
       <c r="U386" t="s" s="2">
         <v>63</v>
       </c>
       <c r="V386" t="s" s="1">
-        <v>5571</v>
+        <v>5589</v>
       </c>
       <c r="W386" t="s" s="1">
-        <v>5572</v>
+        <v>5590</v>
       </c>
       <c r="X386" t="s" s="2">
         <v>63</v>
@@ -78027,191 +78081,191 @@
         <v>63</v>
       </c>
       <c r="AC386" t="s" s="1">
-        <v>5573</v>
+        <v>5591</v>
       </c>
       <c r="AD386" t="s" s="2">
         <v>63</v>
       </c>
       <c r="AE386" t="s" s="1">
-        <v>5574</v>
+        <v>5592</v>
       </c>
       <c r="AF386" t="s" s="1">
-        <v>5575</v>
+        <v>5593</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="s" s="1">
-        <v>5576</v>
+        <v>5594</v>
       </c>
       <c r="B387" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C387" t="s" s="1">
-        <v>5577</v>
+        <v>5595</v>
       </c>
       <c r="D387" t="s" s="1">
-        <v>5578</v>
+        <v>5596</v>
       </c>
       <c r="E387" t="s" s="1">
-        <v>5579</v>
+        <v>5597</v>
       </c>
       <c r="F387" t="s" s="1">
-        <v>5580</v>
+        <v>5598</v>
       </c>
       <c r="G387" t="s" s="1">
-        <v>5581</v>
+        <v>5599</v>
       </c>
       <c r="H387" t="s" s="1">
-        <v>5582</v>
+        <v>5600</v>
       </c>
       <c r="I387" t="s" s="1">
-        <v>5583</v>
+        <v>5601</v>
       </c>
       <c r="J387" t="s" s="1">
-        <v>5584</v>
+        <v>5602</v>
       </c>
       <c r="K387" t="s" s="1">
-        <v>5585</v>
+        <v>5603</v>
       </c>
       <c r="L387" t="s" s="1">
-        <v>5586</v>
+        <v>5604</v>
       </c>
       <c r="M387" t="s" s="1">
-        <v>5583</v>
+        <v>5601</v>
       </c>
       <c r="N387" t="s" s="1">
-        <v>5587</v>
+        <v>5605</v>
       </c>
       <c r="O387" t="s" s="1">
-        <v>5588</v>
+        <v>5606</v>
       </c>
       <c r="P387" t="s" s="1">
-        <v>5580</v>
+        <v>5598</v>
       </c>
       <c r="Q387" t="s" s="1">
-        <v>5589</v>
+        <v>5607</v>
       </c>
       <c r="R387" t="s" s="1">
-        <v>5580</v>
+        <v>5598</v>
       </c>
       <c r="S387" t="s" s="1">
-        <v>5590</v>
+        <v>5608</v>
       </c>
       <c r="T387" t="s" s="1">
-        <v>5591</v>
+        <v>5609</v>
       </c>
       <c r="U387" t="s" s="1">
-        <v>5591</v>
+        <v>5609</v>
       </c>
       <c r="V387" t="s" s="1">
-        <v>5592</v>
+        <v>5610</v>
       </c>
       <c r="W387" t="s" s="1">
-        <v>5593</v>
+        <v>5611</v>
       </c>
       <c r="X387" t="s" s="1">
-        <v>5594</v>
+        <v>5612</v>
       </c>
       <c r="Y387" t="s" s="1">
-        <v>5595</v>
+        <v>5613</v>
       </c>
       <c r="Z387" t="s" s="1">
-        <v>5596</v>
+        <v>5614</v>
       </c>
       <c r="AA387" t="s" s="1">
-        <v>5597</v>
+        <v>5615</v>
       </c>
       <c r="AB387" t="s" s="1">
-        <v>5598</v>
+        <v>5616</v>
       </c>
       <c r="AC387" t="s" s="1">
-        <v>5599</v>
+        <v>5617</v>
       </c>
       <c r="AD387" t="s" s="1">
-        <v>5600</v>
+        <v>5618</v>
       </c>
       <c r="AE387" t="s" s="1">
-        <v>5601</v>
+        <v>5619</v>
       </c>
       <c r="AF387" t="s" s="1">
-        <v>5602</v>
+        <v>5620</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="s" s="1">
-        <v>5603</v>
+        <v>5621</v>
       </c>
       <c r="B388" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C388" t="s" s="1">
-        <v>5604</v>
+        <v>5622</v>
       </c>
       <c r="D388" t="s" s="2">
         <v>63</v>
       </c>
       <c r="E388" t="s" s="1">
-        <v>5605</v>
+        <v>5623</v>
       </c>
       <c r="F388" t="s" s="1">
-        <v>5606</v>
+        <v>5624</v>
       </c>
       <c r="G388" t="s" s="1">
-        <v>5607</v>
+        <v>5625</v>
       </c>
       <c r="H388" t="s" s="1">
-        <v>5608</v>
+        <v>5626</v>
       </c>
       <c r="I388" t="s" s="1">
-        <v>5609</v>
+        <v>5627</v>
       </c>
       <c r="J388" t="s" s="1">
-        <v>5610</v>
+        <v>5628</v>
       </c>
       <c r="K388" t="s" s="2">
         <v>63</v>
       </c>
       <c r="L388" t="s" s="1">
-        <v>5611</v>
+        <v>5629</v>
       </c>
       <c r="M388" t="s" s="1">
-        <v>5612</v>
+        <v>5630</v>
       </c>
       <c r="N388" t="s" s="1">
-        <v>5613</v>
+        <v>5631</v>
       </c>
       <c r="O388" t="s" s="1">
-        <v>5614</v>
+        <v>5632</v>
       </c>
       <c r="P388" t="s" s="1">
-        <v>5606</v>
+        <v>5624</v>
       </c>
       <c r="Q388" t="s" s="1">
-        <v>5615</v>
+        <v>5633</v>
       </c>
       <c r="R388" t="s" s="1">
-        <v>5616</v>
+        <v>5634</v>
       </c>
       <c r="S388" t="s" s="1">
-        <v>5617</v>
+        <v>5635</v>
       </c>
       <c r="T388" t="s" s="1">
-        <v>5618</v>
+        <v>5636</v>
       </c>
       <c r="U388" t="s" s="1">
-        <v>5619</v>
+        <v>5637</v>
       </c>
       <c r="V388" t="s" s="1">
-        <v>5620</v>
+        <v>5638</v>
       </c>
       <c r="W388" t="s" s="1">
-        <v>5621</v>
+        <v>5639</v>
       </c>
       <c r="X388" t="s" s="2">
         <v>63</v>
       </c>
       <c r="Y388" t="s" s="1">
-        <v>5622</v>
+        <v>5640</v>
       </c>
       <c r="Z388" t="s" s="2">
         <v>63</v>
@@ -78220,51 +78274,51 @@
         <v>63</v>
       </c>
       <c r="AB388" t="s" s="1">
-        <v>5623</v>
+        <v>5641</v>
       </c>
       <c r="AC388" t="s" s="1">
-        <v>5624</v>
+        <v>5642</v>
       </c>
       <c r="AD388" t="s" s="1">
-        <v>5625</v>
+        <v>5643</v>
       </c>
       <c r="AE388" t="s" s="1">
-        <v>5626</v>
+        <v>5644</v>
       </c>
       <c r="AF388" t="s" s="1">
-        <v>5627</v>
+        <v>5645</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="s" s="1">
-        <v>5628</v>
+        <v>5646</v>
       </c>
       <c r="B389" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C389" t="s" s="1">
-        <v>5629</v>
+        <v>5647</v>
       </c>
       <c r="D389" t="s" s="2">
         <v>63</v>
       </c>
       <c r="E389" t="s" s="1">
-        <v>5630</v>
+        <v>5648</v>
       </c>
       <c r="F389" t="s" s="2">
         <v>63</v>
       </c>
       <c r="G389" t="s" s="1">
-        <v>5631</v>
+        <v>5649</v>
       </c>
       <c r="H389" t="s" s="2">
         <v>63</v>
       </c>
       <c r="I389" t="s" s="1">
-        <v>5632</v>
+        <v>5650</v>
       </c>
       <c r="J389" t="s" s="1">
-        <v>5633</v>
+        <v>5651</v>
       </c>
       <c r="K389" t="s" s="2">
         <v>63</v>
@@ -78294,7 +78348,7 @@
         <v>63</v>
       </c>
       <c r="T389" t="s" s="1">
-        <v>5634</v>
+        <v>5652</v>
       </c>
       <c r="U389" t="s" s="2">
         <v>63</v>
@@ -78321,13 +78375,13 @@
         <v>63</v>
       </c>
       <c r="AC389" t="s" s="1">
-        <v>5635</v>
+        <v>5653</v>
       </c>
       <c r="AD389" t="s" s="2">
         <v>63</v>
       </c>
       <c r="AE389" t="s" s="1">
-        <v>5636</v>
+        <v>5654</v>
       </c>
       <c r="AF389" t="s" s="2">
         <v>63</v>
@@ -78335,132 +78389,132 @@
     </row>
     <row r="390">
       <c r="A390" t="s" s="1">
-        <v>5637</v>
+        <v>5655</v>
       </c>
       <c r="B390" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C390" t="s" s="1">
-        <v>5638</v>
+        <v>5656</v>
       </c>
       <c r="D390" t="s" s="1">
-        <v>5639</v>
+        <v>5657</v>
       </c>
       <c r="E390" t="s" s="1">
-        <v>5640</v>
+        <v>5658</v>
       </c>
       <c r="F390" t="s" s="1">
-        <v>5641</v>
+        <v>5659</v>
       </c>
       <c r="G390" t="s" s="1">
-        <v>5642</v>
+        <v>5660</v>
       </c>
       <c r="H390" t="s" s="1">
-        <v>5643</v>
+        <v>5661</v>
       </c>
       <c r="I390" t="s" s="1">
-        <v>5644</v>
+        <v>5662</v>
       </c>
       <c r="J390" t="s" s="1">
-        <v>5645</v>
+        <v>5663</v>
       </c>
       <c r="K390" t="s" s="1">
-        <v>5646</v>
+        <v>5664</v>
       </c>
       <c r="L390" t="s" s="1">
-        <v>5647</v>
+        <v>5665</v>
       </c>
       <c r="M390" t="s" s="1">
-        <v>5648</v>
+        <v>5666</v>
       </c>
       <c r="N390" t="s" s="1">
-        <v>5649</v>
+        <v>5667</v>
       </c>
       <c r="O390" t="s" s="1">
-        <v>5650</v>
+        <v>5668</v>
       </c>
       <c r="P390" t="s" s="1">
-        <v>5651</v>
+        <v>5669</v>
       </c>
       <c r="Q390" t="s" s="1">
-        <v>5652</v>
+        <v>5670</v>
       </c>
       <c r="R390" t="s" s="1">
-        <v>5653</v>
+        <v>5671</v>
       </c>
       <c r="S390" t="s" s="1">
-        <v>5654</v>
+        <v>5672</v>
       </c>
       <c r="T390" t="s" s="1">
-        <v>5655</v>
+        <v>5673</v>
       </c>
       <c r="U390" t="s" s="1">
-        <v>5655</v>
+        <v>5673</v>
       </c>
       <c r="V390" t="s" s="1">
-        <v>5656</v>
+        <v>5674</v>
       </c>
       <c r="W390" t="s" s="1">
-        <v>5657</v>
+        <v>5675</v>
       </c>
       <c r="X390" t="s" s="1">
-        <v>5658</v>
+        <v>5676</v>
       </c>
       <c r="Y390" t="s" s="1">
-        <v>5659</v>
+        <v>5677</v>
       </c>
       <c r="Z390" t="s" s="1">
-        <v>5660</v>
+        <v>5678</v>
       </c>
       <c r="AA390" t="s" s="1">
-        <v>5661</v>
+        <v>5679</v>
       </c>
       <c r="AB390" t="s" s="1">
-        <v>5662</v>
+        <v>5680</v>
       </c>
       <c r="AC390" t="s" s="1">
-        <v>5663</v>
+        <v>5681</v>
       </c>
       <c r="AD390" t="s" s="1">
-        <v>5664</v>
+        <v>5682</v>
       </c>
       <c r="AE390" t="s" s="1">
-        <v>5665</v>
+        <v>5683</v>
       </c>
       <c r="AF390" t="s" s="1">
-        <v>5666</v>
+        <v>5684</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="s" s="1">
-        <v>5667</v>
+        <v>5685</v>
       </c>
       <c r="B391" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C391" t="s" s="1">
-        <v>5668</v>
+        <v>5686</v>
       </c>
       <c r="D391" t="s" s="2">
         <v>63</v>
       </c>
       <c r="E391" t="s" s="1">
-        <v>5669</v>
+        <v>5687</v>
       </c>
       <c r="F391" t="s" s="2">
         <v>63</v>
       </c>
       <c r="G391" t="s" s="1">
-        <v>5670</v>
+        <v>5688</v>
       </c>
       <c r="H391" t="s" s="2">
         <v>63</v>
       </c>
       <c r="I391" t="s" s="1">
-        <v>5671</v>
+        <v>5689</v>
       </c>
       <c r="J391" t="s" s="1">
-        <v>5672</v>
+        <v>5690</v>
       </c>
       <c r="K391" t="s" s="2">
         <v>63</v>
@@ -78469,7 +78523,7 @@
         <v>63</v>
       </c>
       <c r="M391" t="s" s="1">
-        <v>5673</v>
+        <v>5691</v>
       </c>
       <c r="N391" t="s" s="2">
         <v>63</v>
@@ -78481,25 +78535,25 @@
         <v>63</v>
       </c>
       <c r="Q391" t="s" s="1">
-        <v>5674</v>
+        <v>5692</v>
       </c>
       <c r="R391" t="s" s="2">
         <v>63</v>
       </c>
       <c r="S391" t="s" s="1">
-        <v>5675</v>
+        <v>5693</v>
       </c>
       <c r="T391" t="s" s="1">
-        <v>5676</v>
+        <v>5694</v>
       </c>
       <c r="U391" t="s" s="2">
         <v>63</v>
       </c>
       <c r="V391" t="s" s="1">
-        <v>5677</v>
+        <v>5695</v>
       </c>
       <c r="W391" t="s" s="1">
-        <v>5678</v>
+        <v>5696</v>
       </c>
       <c r="X391" t="s" s="2">
         <v>63</v>
@@ -78517,48 +78571,48 @@
         <v>63</v>
       </c>
       <c r="AC391" t="s" s="1">
-        <v>5679</v>
+        <v>5697</v>
       </c>
       <c r="AD391" t="s" s="2">
         <v>63</v>
       </c>
       <c r="AE391" t="s" s="1">
-        <v>5680</v>
+        <v>5698</v>
       </c>
       <c r="AF391" t="s" s="1">
-        <v>5681</v>
+        <v>5699</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="s" s="1">
-        <v>5682</v>
+        <v>5700</v>
       </c>
       <c r="B392" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C392" t="s" s="1">
-        <v>5683</v>
+        <v>5701</v>
       </c>
       <c r="D392" t="s" s="2">
         <v>63</v>
       </c>
       <c r="E392" t="s" s="1">
-        <v>5684</v>
+        <v>5702</v>
       </c>
       <c r="F392" t="s" s="2">
         <v>63</v>
       </c>
       <c r="G392" t="s" s="1">
-        <v>5685</v>
+        <v>5703</v>
       </c>
       <c r="H392" t="s" s="2">
         <v>63</v>
       </c>
       <c r="I392" t="s" s="1">
-        <v>5686</v>
+        <v>5704</v>
       </c>
       <c r="J392" t="s" s="1">
-        <v>5687</v>
+        <v>5705</v>
       </c>
       <c r="K392" t="s" s="2">
         <v>63</v>
@@ -78567,7 +78621,7 @@
         <v>63</v>
       </c>
       <c r="M392" t="s" s="1">
-        <v>5688</v>
+        <v>5706</v>
       </c>
       <c r="N392" t="s" s="2">
         <v>63</v>
@@ -78585,19 +78639,19 @@
         <v>63</v>
       </c>
       <c r="S392" t="s" s="1">
-        <v>5689</v>
+        <v>5707</v>
       </c>
       <c r="T392" t="s" s="1">
-        <v>5686</v>
+        <v>5704</v>
       </c>
       <c r="U392" t="s" s="2">
         <v>63</v>
       </c>
       <c r="V392" t="s" s="1">
-        <v>5690</v>
+        <v>5708</v>
       </c>
       <c r="W392" t="s" s="1">
-        <v>5691</v>
+        <v>5709</v>
       </c>
       <c r="X392" t="s" s="2">
         <v>63</v>
@@ -78615,48 +78669,48 @@
         <v>63</v>
       </c>
       <c r="AC392" t="s" s="1">
-        <v>5692</v>
+        <v>5710</v>
       </c>
       <c r="AD392" t="s" s="2">
         <v>63</v>
       </c>
       <c r="AE392" t="s" s="1">
-        <v>5693</v>
+        <v>5711</v>
       </c>
       <c r="AF392" t="s" s="1">
-        <v>5694</v>
+        <v>5712</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="s" s="1">
-        <v>5695</v>
+        <v>5713</v>
       </c>
       <c r="B393" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C393" t="s" s="1">
-        <v>5696</v>
+        <v>5714</v>
       </c>
       <c r="D393" t="s" s="2">
         <v>63</v>
       </c>
       <c r="E393" t="s" s="1">
-        <v>5697</v>
+        <v>5715</v>
       </c>
       <c r="F393" t="s" s="2">
         <v>63</v>
       </c>
       <c r="G393" t="s" s="1">
-        <v>5698</v>
+        <v>5716</v>
       </c>
       <c r="H393" t="s" s="2">
         <v>63</v>
       </c>
       <c r="I393" t="s" s="1">
-        <v>5699</v>
+        <v>5717</v>
       </c>
       <c r="J393" t="s" s="1">
-        <v>5700</v>
+        <v>5718</v>
       </c>
       <c r="K393" t="s" s="2">
         <v>63</v>
@@ -78665,7 +78719,7 @@
         <v>63</v>
       </c>
       <c r="M393" t="s" s="1">
-        <v>5701</v>
+        <v>5719</v>
       </c>
       <c r="N393" t="s" s="2">
         <v>63</v>
@@ -78677,25 +78731,25 @@
         <v>63</v>
       </c>
       <c r="Q393" t="s" s="1">
-        <v>5702</v>
+        <v>5720</v>
       </c>
       <c r="R393" t="s" s="2">
         <v>63</v>
       </c>
       <c r="S393" t="s" s="1">
-        <v>5703</v>
+        <v>5721</v>
       </c>
       <c r="T393" t="s" s="1">
-        <v>5704</v>
+        <v>5722</v>
       </c>
       <c r="U393" t="s" s="2">
         <v>63</v>
       </c>
       <c r="V393" t="s" s="1">
-        <v>5705</v>
+        <v>5723</v>
       </c>
       <c r="W393" t="s" s="1">
-        <v>5706</v>
+        <v>5724</v>
       </c>
       <c r="X393" t="s" s="2">
         <v>63</v>
@@ -78713,48 +78767,48 @@
         <v>63</v>
       </c>
       <c r="AC393" t="s" s="1">
-        <v>5707</v>
+        <v>5725</v>
       </c>
       <c r="AD393" t="s" s="2">
         <v>63</v>
       </c>
       <c r="AE393" t="s" s="1">
-        <v>5708</v>
+        <v>5726</v>
       </c>
       <c r="AF393" t="s" s="1">
-        <v>5709</v>
+        <v>5727</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="s" s="1">
-        <v>5710</v>
+        <v>5728</v>
       </c>
       <c r="B394" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C394" t="s" s="1">
-        <v>5711</v>
+        <v>5729</v>
       </c>
       <c r="D394" t="s" s="2">
         <v>63</v>
       </c>
       <c r="E394" t="s" s="1">
-        <v>5712</v>
+        <v>5730</v>
       </c>
       <c r="F394" t="s" s="2">
         <v>63</v>
       </c>
       <c r="G394" t="s" s="1">
-        <v>5713</v>
+        <v>5731</v>
       </c>
       <c r="H394" t="s" s="2">
         <v>63</v>
       </c>
       <c r="I394" t="s" s="1">
-        <v>5714</v>
+        <v>5732</v>
       </c>
       <c r="J394" t="s" s="1">
-        <v>5715</v>
+        <v>5733</v>
       </c>
       <c r="K394" t="s" s="2">
         <v>63</v>
@@ -78763,7 +78817,7 @@
         <v>63</v>
       </c>
       <c r="M394" t="s" s="1">
-        <v>5716</v>
+        <v>5734</v>
       </c>
       <c r="N394" t="s" s="2">
         <v>63</v>
@@ -78781,19 +78835,19 @@
         <v>63</v>
       </c>
       <c r="S394" t="s" s="1">
-        <v>5717</v>
+        <v>5735</v>
       </c>
       <c r="T394" t="s" s="1">
-        <v>5718</v>
+        <v>5736</v>
       </c>
       <c r="U394" t="s" s="2">
         <v>63</v>
       </c>
       <c r="V394" t="s" s="1">
-        <v>5714</v>
+        <v>5732</v>
       </c>
       <c r="W394" t="s" s="1">
-        <v>5719</v>
+        <v>5737</v>
       </c>
       <c r="X394" t="s" s="2">
         <v>63</v>
@@ -78811,48 +78865,48 @@
         <v>63</v>
       </c>
       <c r="AC394" t="s" s="1">
-        <v>5720</v>
+        <v>5738</v>
       </c>
       <c r="AD394" t="s" s="2">
         <v>63</v>
       </c>
       <c r="AE394" t="s" s="1">
-        <v>5721</v>
+        <v>5739</v>
       </c>
       <c r="AF394" t="s" s="1">
-        <v>5722</v>
+        <v>5740</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="s" s="1">
-        <v>5723</v>
+        <v>5741</v>
       </c>
       <c r="B395" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C395" t="s" s="1">
-        <v>5724</v>
+        <v>5742</v>
       </c>
       <c r="D395" t="s" s="2">
         <v>63</v>
       </c>
       <c r="E395" t="s" s="1">
-        <v>5725</v>
+        <v>5743</v>
       </c>
       <c r="F395" t="s" s="2">
         <v>63</v>
       </c>
       <c r="G395" t="s" s="1">
-        <v>5726</v>
+        <v>5744</v>
       </c>
       <c r="H395" t="s" s="2">
         <v>63</v>
       </c>
       <c r="I395" t="s" s="1">
-        <v>5727</v>
+        <v>5745</v>
       </c>
       <c r="J395" t="s" s="1">
-        <v>5728</v>
+        <v>5746</v>
       </c>
       <c r="K395" t="s" s="2">
         <v>63</v>
@@ -78861,7 +78915,7 @@
         <v>63</v>
       </c>
       <c r="M395" t="s" s="1">
-        <v>5729</v>
+        <v>5747</v>
       </c>
       <c r="N395" t="s" s="2">
         <v>63</v>
@@ -78879,19 +78933,19 @@
         <v>63</v>
       </c>
       <c r="S395" t="s" s="1">
-        <v>5730</v>
+        <v>5748</v>
       </c>
       <c r="T395" t="s" s="1">
-        <v>5731</v>
+        <v>5749</v>
       </c>
       <c r="U395" t="s" s="2">
         <v>63</v>
       </c>
       <c r="V395" t="s" s="1">
-        <v>5732</v>
+        <v>5750</v>
       </c>
       <c r="W395" t="s" s="1">
-        <v>5733</v>
+        <v>5751</v>
       </c>
       <c r="X395" t="s" s="2">
         <v>63</v>
@@ -78909,114 +78963,114 @@
         <v>63</v>
       </c>
       <c r="AC395" t="s" s="1">
-        <v>5734</v>
+        <v>5752</v>
       </c>
       <c r="AD395" t="s" s="2">
         <v>63</v>
       </c>
       <c r="AE395" t="s" s="1">
-        <v>5735</v>
+        <v>5753</v>
       </c>
       <c r="AF395" t="s" s="1">
-        <v>5736</v>
+        <v>5754</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="s" s="1">
-        <v>5737</v>
+        <v>5755</v>
       </c>
       <c r="B396" t="s" s="1">
         <v>33</v>
       </c>
       <c r="C396" t="s" s="1">
-        <v>5738</v>
+        <v>5756</v>
       </c>
       <c r="D396" t="s" s="1">
-        <v>5739</v>
+        <v>5757</v>
       </c>
       <c r="E396" t="s" s="1">
-        <v>5740</v>
+        <v>5758</v>
       </c>
       <c r="F396" t="s" s="1">
-        <v>5741</v>
+        <v>5759</v>
       </c>
       <c r="G396" t="s" s="1">
-        <v>5742</v>
+        <v>5760</v>
       </c>
       <c r="H396" t="s" s="1">
-        <v>5743</v>
+        <v>5761</v>
       </c>
       <c r="I396" t="s" s="1">
-        <v>5744</v>
+        <v>5762</v>
       </c>
       <c r="J396" t="s" s="1">
-        <v>5745</v>
+        <v>5763</v>
       </c>
       <c r="K396" t="s" s="1">
-        <v>5746</v>
+        <v>5764</v>
       </c>
       <c r="L396" t="s" s="1">
-        <v>5747</v>
+        <v>5765</v>
       </c>
       <c r="M396" t="s" s="1">
-        <v>5748</v>
+        <v>5766</v>
       </c>
       <c r="N396" t="s" s="1">
-        <v>5749</v>
+        <v>5767</v>
       </c>
       <c r="O396" t="s" s="1">
-        <v>5750</v>
+        <v>5768</v>
       </c>
       <c r="P396" t="s" s="1">
-        <v>5751</v>
+        <v>5769</v>
       </c>
       <c r="Q396" t="s" s="1">
-        <v>5752</v>
+        <v>5770</v>
       </c>
       <c r="R396" t="s" s="1">
-        <v>5753</v>
+        <v>5771</v>
       </c>
       <c r="S396" t="s" s="1">
-        <v>5754</v>
+        <v>5772</v>
       </c>
       <c r="T396" t="s" s="1">
-        <v>5755</v>
+        <v>5773</v>
       </c>
       <c r="U396" t="s" s="1">
-        <v>5756</v>
+        <v>5774</v>
       </c>
       <c r="V396" t="s" s="1">
-        <v>5757</v>
+        <v>5775</v>
       </c>
       <c r="W396" t="s" s="1">
-        <v>5758</v>
+        <v>5776</v>
       </c>
       <c r="X396" t="s" s="1">
-        <v>5759</v>
+        <v>5777</v>
       </c>
       <c r="Y396" t="s" s="1">
-        <v>5760</v>
+        <v>5778</v>
       </c>
       <c r="Z396" t="s" s="1">
-        <v>5761</v>
+        <v>5779</v>
       </c>
       <c r="AA396" t="s" s="1">
-        <v>5762</v>
+        <v>5780</v>
       </c>
       <c r="AB396" t="s" s="1">
-        <v>5763</v>
+        <v>5781</v>
       </c>
       <c r="AC396" t="s" s="1">
-        <v>5764</v>
+        <v>5782</v>
       </c>
       <c r="AD396" t="s" s="1">
-        <v>5765</v>
+        <v>5783</v>
       </c>
       <c r="AE396" t="s" s="1">
-        <v>5766</v>
+        <v>5784</v>
       </c>
       <c r="AF396" t="s" s="1">
-        <v>5767</v>
+        <v>5785</v>
       </c>
     </row>
   </sheetData>
